--- a/owlcms/src/main/resources/templates/registration/SBDE.xlsx
+++ b/owlcms/src/main/resources/templates/registration/SBDE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\registration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD68300-3437-4B1B-829D-7933A5A3B409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5253F05-AB1C-46AB-9C4F-7A0B818BD76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26175" yWindow="780" windowWidth="23850" windowHeight="13980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Athletes" sheetId="1" r:id="rId1"/>
@@ -151,7 +151,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>jx:area(lastCell="V10")</t>
+          <t>jx:area(lastCell="W10")</t>
         </r>
         <r>
           <rPr>
@@ -185,7 +185,7 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-jx:each(items="athletes" var="l" lastCell="V10")</t>
+jx:each(items="athletes" var="l" lastCell="W10")</t>
         </r>
       </text>
     </comment>
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="118">
   <si>
     <t>M/F</t>
   </si>
@@ -627,6 +627,12 @@
   </si>
   <si>
     <t>${l.isoBirth}</t>
+  </si>
+  <si>
+    <t>${l.eligibleForIndividualRanking ? "" : "true"}</t>
+  </si>
+  <si>
+    <t>${t.get("Competition.Invited/Extra")}</t>
   </si>
 </sst>
 </file>
@@ -1354,7 +1360,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1527,6 +1533,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2270,7 +2279,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Jean-François Lamy" refreshedDate="45532.984339236114" createdVersion="8" refreshedVersion="8" recordCount="18" xr:uid="{00000000-000A-0000-FFFF-FFFF09000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Jean-François Lamy" refreshedDate="45686.671195601855" createdVersion="8" refreshedVersion="8" recordCount="18" xr:uid="{00000000-000A-0000-FFFF-FFFF09000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:G598" sheet="Group Data"/>
   </cacheSource>
@@ -3381,7 +3390,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V157"/>
+  <dimension ref="A1:W157"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" customWidth="1"/>
@@ -3398,10 +3407,10 @@
     <col min="12" max="12" width="8" style="1" customWidth="1"/>
     <col min="13" max="16" width="26.5703125" customWidth="1"/>
     <col min="17" max="19" width="14" customWidth="1"/>
-    <col min="22" max="22" width="14" customWidth="1"/>
+    <col min="22" max="23" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>28</v>
       </c>
@@ -3429,7 +3438,7 @@
       <c r="R1" s="22"/>
       <c r="S1" s="22"/>
     </row>
-    <row r="2" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>29</v>
       </c>
@@ -3446,7 +3455,7 @@
       <c r="J2" s="13"/>
       <c r="K2" s="11"/>
     </row>
-    <row r="3" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>30</v>
       </c>
@@ -3464,7 +3473,7 @@
       <c r="K3" s="11"/>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
         <v>31</v>
       </c>
@@ -3482,46 +3491,46 @@
       <c r="K4" s="11"/>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:22" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="68" t="s">
+    <row r="5" spans="1:23" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:23" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
       <c r="N6" s="66"/>
       <c r="O6" s="66"/>
     </row>
-    <row r="7" spans="1:22" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="68" t="s">
+    <row r="7" spans="1:23" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68"/>
-      <c r="L7" s="68"/>
-      <c r="M7" s="68"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="69"/>
+      <c r="L7" s="69"/>
+      <c r="M7" s="69"/>
       <c r="N7" s="66"/>
       <c r="O7" s="66"/>
     </row>
-    <row r="8" spans="1:22" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="65"/>
       <c r="B8" s="65"/>
       <c r="C8" s="65"/>
@@ -3538,7 +3547,7 @@
       <c r="N8" s="65"/>
       <c r="O8" s="65"/>
     </row>
-    <row r="9" spans="1:22" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>11</v>
       </c>
@@ -3605,8 +3614,11 @@
       <c r="V9" s="12" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" s="40" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W9" s="68" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" s="40" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>20</v>
       </c>
@@ -3673,8 +3685,11 @@
       <c r="V10" s="42" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W10" s="42" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="15"/>
       <c r="B11" s="15"/>
       <c r="C11" s="16"/>
@@ -3697,8 +3712,9 @@
       <c r="T11" s="33"/>
       <c r="U11" s="33"/>
       <c r="V11" s="8"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W11" s="8"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="15"/>
       <c r="B12" s="15"/>
       <c r="C12" s="16"/>
@@ -3721,8 +3737,9 @@
       <c r="T12" s="33"/>
       <c r="U12" s="33"/>
       <c r="V12" s="8"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W12" s="8"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="16"/>
@@ -3745,8 +3762,9 @@
       <c r="T13" s="33"/>
       <c r="U13" s="33"/>
       <c r="V13" s="8"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W13" s="8"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="15"/>
       <c r="B14" s="15"/>
       <c r="C14" s="16"/>
@@ -3769,8 +3787,9 @@
       <c r="T14" s="33"/>
       <c r="U14" s="33"/>
       <c r="V14" s="8"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W14" s="8"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="15"/>
       <c r="B15" s="15"/>
       <c r="C15" s="16"/>
@@ -3793,8 +3812,9 @@
       <c r="T15" s="33"/>
       <c r="U15" s="33"/>
       <c r="V15" s="8"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W15" s="8"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="15"/>
       <c r="B16" s="15"/>
       <c r="C16" s="16"/>
@@ -3817,8 +3837,9 @@
       <c r="T16" s="33"/>
       <c r="U16" s="33"/>
       <c r="V16" s="8"/>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W16" s="8"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="15"/>
       <c r="B17" s="15"/>
       <c r="C17" s="16"/>
@@ -3841,8 +3862,9 @@
       <c r="T17" s="33"/>
       <c r="U17" s="33"/>
       <c r="V17" s="8"/>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W17" s="8"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="15"/>
       <c r="B18" s="15"/>
       <c r="C18" s="16"/>
@@ -3865,8 +3887,9 @@
       <c r="T18" s="33"/>
       <c r="U18" s="33"/>
       <c r="V18" s="8"/>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W18" s="8"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="15"/>
       <c r="B19" s="15"/>
       <c r="C19" s="16"/>
@@ -3889,8 +3912,9 @@
       <c r="T19" s="33"/>
       <c r="U19" s="33"/>
       <c r="V19" s="8"/>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W19" s="8"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="15"/>
       <c r="B20" s="15"/>
       <c r="C20" s="16"/>
@@ -3913,8 +3937,9 @@
       <c r="T20" s="33"/>
       <c r="U20" s="33"/>
       <c r="V20" s="8"/>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W20" s="8"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="15"/>
       <c r="B21" s="15"/>
       <c r="C21" s="16"/>
@@ -3937,8 +3962,9 @@
       <c r="T21" s="33"/>
       <c r="U21" s="33"/>
       <c r="V21" s="8"/>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W21" s="8"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="15"/>
       <c r="B22" s="15"/>
       <c r="C22" s="16"/>
@@ -3961,8 +3987,9 @@
       <c r="T22" s="33"/>
       <c r="U22" s="33"/>
       <c r="V22" s="8"/>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W22" s="8"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="15"/>
       <c r="B23" s="15"/>
       <c r="C23" s="16"/>
@@ -3985,8 +4012,9 @@
       <c r="T23" s="33"/>
       <c r="U23" s="33"/>
       <c r="V23" s="8"/>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W23" s="8"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="16"/>
@@ -4009,8 +4037,9 @@
       <c r="T24" s="33"/>
       <c r="U24" s="33"/>
       <c r="V24" s="8"/>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W24" s="8"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="15"/>
       <c r="B25" s="15"/>
       <c r="C25" s="16"/>
@@ -4033,8 +4062,9 @@
       <c r="T25" s="33"/>
       <c r="U25" s="33"/>
       <c r="V25" s="8"/>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W25" s="8"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="15"/>
       <c r="B26" s="15"/>
       <c r="C26" s="16"/>
@@ -4057,8 +4087,9 @@
       <c r="T26" s="33"/>
       <c r="U26" s="33"/>
       <c r="V26" s="8"/>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W26" s="8"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="15"/>
       <c r="B27" s="15"/>
       <c r="C27" s="16"/>
@@ -4081,8 +4112,9 @@
       <c r="T27" s="33"/>
       <c r="U27" s="33"/>
       <c r="V27" s="8"/>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W27" s="8"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="15"/>
       <c r="C28" s="16"/>
@@ -4105,8 +4137,9 @@
       <c r="T28" s="33"/>
       <c r="U28" s="33"/>
       <c r="V28" s="8"/>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W28" s="8"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="15"/>
       <c r="B29" s="15"/>
       <c r="C29" s="16"/>
@@ -4129,8 +4162,9 @@
       <c r="T29" s="33"/>
       <c r="U29" s="33"/>
       <c r="V29" s="8"/>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W29" s="8"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="15"/>
       <c r="B30" s="15"/>
       <c r="C30" s="16"/>
@@ -4153,8 +4187,9 @@
       <c r="T30" s="33"/>
       <c r="U30" s="33"/>
       <c r="V30" s="8"/>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W30" s="8"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="15"/>
       <c r="B31" s="15"/>
       <c r="C31" s="16"/>
@@ -4177,8 +4212,9 @@
       <c r="T31" s="33"/>
       <c r="U31" s="33"/>
       <c r="V31" s="8"/>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W31" s="8"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="15"/>
       <c r="B32" s="15"/>
       <c r="C32" s="16"/>
@@ -4201,8 +4237,9 @@
       <c r="T32" s="33"/>
       <c r="U32" s="33"/>
       <c r="V32" s="8"/>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W32" s="8"/>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" s="15"/>
       <c r="B33" s="15"/>
       <c r="C33" s="16"/>
@@ -4225,8 +4262,9 @@
       <c r="T33" s="33"/>
       <c r="U33" s="33"/>
       <c r="V33" s="8"/>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W33" s="8"/>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" s="15"/>
       <c r="B34" s="15"/>
       <c r="C34" s="16"/>
@@ -4249,8 +4287,9 @@
       <c r="T34" s="33"/>
       <c r="U34" s="33"/>
       <c r="V34" s="8"/>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W34" s="8"/>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" s="15"/>
       <c r="B35" s="15"/>
       <c r="C35" s="16"/>
@@ -4273,8 +4312,9 @@
       <c r="T35" s="33"/>
       <c r="U35" s="33"/>
       <c r="V35" s="8"/>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W35" s="8"/>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" s="15"/>
       <c r="B36" s="15"/>
       <c r="C36" s="16"/>
@@ -4297,8 +4337,9 @@
       <c r="T36" s="33"/>
       <c r="U36" s="33"/>
       <c r="V36" s="8"/>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W36" s="8"/>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" s="15"/>
       <c r="B37" s="15"/>
       <c r="C37" s="16"/>
@@ -4321,8 +4362,9 @@
       <c r="T37" s="33"/>
       <c r="U37" s="33"/>
       <c r="V37" s="8"/>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W37" s="8"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" s="15"/>
       <c r="B38" s="15"/>
       <c r="C38" s="16"/>
@@ -4345,8 +4387,9 @@
       <c r="T38" s="33"/>
       <c r="U38" s="33"/>
       <c r="V38" s="8"/>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W38" s="8"/>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" s="15"/>
       <c r="B39" s="15"/>
       <c r="C39" s="16"/>
@@ -4369,8 +4412,9 @@
       <c r="T39" s="33"/>
       <c r="U39" s="33"/>
       <c r="V39" s="8"/>
-    </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W39" s="8"/>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" s="15"/>
       <c r="B40" s="15"/>
       <c r="C40" s="16"/>
@@ -4393,8 +4437,9 @@
       <c r="T40" s="33"/>
       <c r="U40" s="33"/>
       <c r="V40" s="8"/>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W40" s="8"/>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" s="15"/>
       <c r="B41" s="15"/>
       <c r="C41" s="16"/>
@@ -4417,8 +4462,9 @@
       <c r="T41" s="33"/>
       <c r="U41" s="33"/>
       <c r="V41" s="8"/>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W41" s="8"/>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42" s="15"/>
       <c r="B42" s="15"/>
       <c r="C42" s="16"/>
@@ -4441,8 +4487,9 @@
       <c r="T42" s="33"/>
       <c r="U42" s="33"/>
       <c r="V42" s="8"/>
-    </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W42" s="8"/>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43" s="15"/>
       <c r="B43" s="15"/>
       <c r="C43" s="16"/>
@@ -4465,8 +4512,9 @@
       <c r="T43" s="33"/>
       <c r="U43" s="33"/>
       <c r="V43" s="8"/>
-    </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W43" s="8"/>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44" s="15"/>
       <c r="B44" s="15"/>
       <c r="C44" s="16"/>
@@ -4489,8 +4537,9 @@
       <c r="T44" s="33"/>
       <c r="U44" s="33"/>
       <c r="V44" s="8"/>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W44" s="8"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" s="15"/>
       <c r="B45" s="15"/>
       <c r="C45" s="16"/>
@@ -4513,8 +4562,9 @@
       <c r="T45" s="33"/>
       <c r="U45" s="33"/>
       <c r="V45" s="8"/>
-    </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W45" s="8"/>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46" s="15"/>
       <c r="B46" s="15"/>
       <c r="C46" s="16"/>
@@ -4537,8 +4587,9 @@
       <c r="T46" s="33"/>
       <c r="U46" s="33"/>
       <c r="V46" s="8"/>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W46" s="8"/>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" s="15"/>
       <c r="B47" s="15"/>
       <c r="C47" s="16"/>
@@ -4561,8 +4612,9 @@
       <c r="T47" s="33"/>
       <c r="U47" s="33"/>
       <c r="V47" s="8"/>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W47" s="8"/>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" s="15"/>
       <c r="B48" s="15"/>
       <c r="C48" s="16"/>
@@ -4585,8 +4637,9 @@
       <c r="T48" s="33"/>
       <c r="U48" s="33"/>
       <c r="V48" s="8"/>
-    </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W48" s="8"/>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" s="15"/>
       <c r="B49" s="15"/>
       <c r="C49" s="16"/>
@@ -4609,8 +4662,9 @@
       <c r="T49" s="33"/>
       <c r="U49" s="33"/>
       <c r="V49" s="8"/>
-    </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W49" s="8"/>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" s="15"/>
       <c r="B50" s="15"/>
       <c r="C50" s="16"/>
@@ -4633,8 +4687,9 @@
       <c r="T50" s="33"/>
       <c r="U50" s="33"/>
       <c r="V50" s="8"/>
-    </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W50" s="8"/>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" s="15"/>
       <c r="B51" s="15"/>
       <c r="C51" s="16"/>
@@ -4657,8 +4712,9 @@
       <c r="T51" s="33"/>
       <c r="U51" s="33"/>
       <c r="V51" s="8"/>
-    </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W51" s="8"/>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A52" s="15"/>
       <c r="B52" s="15"/>
       <c r="C52" s="16"/>
@@ -4681,8 +4737,9 @@
       <c r="T52" s="33"/>
       <c r="U52" s="33"/>
       <c r="V52" s="8"/>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W52" s="8"/>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53" s="15"/>
       <c r="B53" s="15"/>
       <c r="C53" s="16"/>
@@ -4705,8 +4762,9 @@
       <c r="T53" s="33"/>
       <c r="U53" s="33"/>
       <c r="V53" s="8"/>
-    </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W53" s="8"/>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A54" s="15"/>
       <c r="B54" s="15"/>
       <c r="C54" s="16"/>
@@ -4729,8 +4787,9 @@
       <c r="T54" s="33"/>
       <c r="U54" s="33"/>
       <c r="V54" s="8"/>
-    </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W54" s="8"/>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A55" s="15"/>
       <c r="B55" s="15"/>
       <c r="C55" s="16"/>
@@ -4753,8 +4812,9 @@
       <c r="T55" s="33"/>
       <c r="U55" s="33"/>
       <c r="V55" s="8"/>
-    </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W55" s="8"/>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56" s="15"/>
       <c r="B56" s="15"/>
       <c r="C56" s="16"/>
@@ -4777,8 +4837,9 @@
       <c r="T56" s="33"/>
       <c r="U56" s="33"/>
       <c r="V56" s="8"/>
-    </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W56" s="8"/>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57" s="15"/>
       <c r="B57" s="15"/>
       <c r="C57" s="16"/>
@@ -4801,8 +4862,9 @@
       <c r="T57" s="33"/>
       <c r="U57" s="33"/>
       <c r="V57" s="8"/>
-    </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W57" s="8"/>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58" s="15"/>
       <c r="B58" s="15"/>
       <c r="C58" s="16"/>
@@ -4825,8 +4887,9 @@
       <c r="T58" s="33"/>
       <c r="U58" s="33"/>
       <c r="V58" s="8"/>
-    </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W58" s="8"/>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" s="15"/>
       <c r="B59" s="15"/>
       <c r="C59" s="16"/>
@@ -4849,8 +4912,9 @@
       <c r="T59" s="33"/>
       <c r="U59" s="33"/>
       <c r="V59" s="8"/>
-    </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W59" s="8"/>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" s="15"/>
       <c r="B60" s="15"/>
       <c r="C60" s="16"/>
@@ -4873,8 +4937,9 @@
       <c r="T60" s="33"/>
       <c r="U60" s="33"/>
       <c r="V60" s="8"/>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W60" s="8"/>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" s="15"/>
       <c r="B61" s="15"/>
       <c r="C61" s="16"/>
@@ -4897,8 +4962,9 @@
       <c r="T61" s="33"/>
       <c r="U61" s="33"/>
       <c r="V61" s="8"/>
-    </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W61" s="8"/>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62" s="15"/>
       <c r="B62" s="15"/>
       <c r="C62" s="16"/>
@@ -4921,8 +4987,9 @@
       <c r="T62" s="33"/>
       <c r="U62" s="33"/>
       <c r="V62" s="8"/>
-    </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W62" s="8"/>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A63" s="15"/>
       <c r="B63" s="15"/>
       <c r="C63" s="16"/>
@@ -4945,8 +5012,9 @@
       <c r="T63" s="33"/>
       <c r="U63" s="33"/>
       <c r="V63" s="8"/>
-    </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W63" s="8"/>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A64" s="15"/>
       <c r="B64" s="15"/>
       <c r="C64" s="16"/>
@@ -4969,8 +5037,9 @@
       <c r="T64" s="33"/>
       <c r="U64" s="33"/>
       <c r="V64" s="8"/>
-    </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W64" s="8"/>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" s="15"/>
       <c r="B65" s="15"/>
       <c r="C65" s="16"/>
@@ -4993,8 +5062,9 @@
       <c r="T65" s="33"/>
       <c r="U65" s="33"/>
       <c r="V65" s="8"/>
-    </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W65" s="8"/>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" s="15"/>
       <c r="B66" s="15"/>
       <c r="C66" s="16"/>
@@ -5017,8 +5087,9 @@
       <c r="T66" s="33"/>
       <c r="U66" s="33"/>
       <c r="V66" s="8"/>
-    </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W66" s="8"/>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" s="15"/>
       <c r="B67" s="15"/>
       <c r="C67" s="16"/>
@@ -5041,8 +5112,9 @@
       <c r="T67" s="33"/>
       <c r="U67" s="33"/>
       <c r="V67" s="8"/>
-    </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W67" s="8"/>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" s="15"/>
       <c r="B68" s="15"/>
       <c r="C68" s="16"/>
@@ -5065,8 +5137,9 @@
       <c r="T68" s="33"/>
       <c r="U68" s="33"/>
       <c r="V68" s="8"/>
-    </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W68" s="8"/>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" s="15"/>
       <c r="B69" s="15"/>
       <c r="C69" s="16"/>
@@ -5089,8 +5162,9 @@
       <c r="T69" s="33"/>
       <c r="U69" s="33"/>
       <c r="V69" s="8"/>
-    </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W69" s="8"/>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" s="15"/>
       <c r="B70" s="15"/>
       <c r="C70" s="16"/>
@@ -5113,8 +5187,9 @@
       <c r="T70" s="33"/>
       <c r="U70" s="33"/>
       <c r="V70" s="8"/>
-    </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W70" s="8"/>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" s="15"/>
       <c r="B71" s="15"/>
       <c r="C71" s="16"/>
@@ -5137,8 +5212,9 @@
       <c r="T71" s="33"/>
       <c r="U71" s="33"/>
       <c r="V71" s="8"/>
-    </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W71" s="8"/>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" s="15"/>
       <c r="B72" s="15"/>
       <c r="C72" s="16"/>
@@ -5161,8 +5237,9 @@
       <c r="T72" s="33"/>
       <c r="U72" s="33"/>
       <c r="V72" s="8"/>
-    </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W72" s="8"/>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" s="15"/>
       <c r="B73" s="15"/>
       <c r="C73" s="16"/>
@@ -5185,8 +5262,9 @@
       <c r="T73" s="33"/>
       <c r="U73" s="33"/>
       <c r="V73" s="8"/>
-    </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W73" s="8"/>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74" s="15"/>
       <c r="B74" s="15"/>
       <c r="C74" s="16"/>
@@ -5209,8 +5287,9 @@
       <c r="T74" s="33"/>
       <c r="U74" s="33"/>
       <c r="V74" s="8"/>
-    </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W74" s="8"/>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75" s="15"/>
       <c r="B75" s="15"/>
       <c r="C75" s="16"/>
@@ -5233,8 +5312,9 @@
       <c r="T75" s="33"/>
       <c r="U75" s="33"/>
       <c r="V75" s="8"/>
-    </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W75" s="8"/>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76" s="15"/>
       <c r="B76" s="15"/>
       <c r="C76" s="16"/>
@@ -5257,8 +5337,9 @@
       <c r="T76" s="33"/>
       <c r="U76" s="33"/>
       <c r="V76" s="8"/>
-    </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W76" s="8"/>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77" s="15"/>
       <c r="B77" s="15"/>
       <c r="C77" s="16"/>
@@ -5281,8 +5362,9 @@
       <c r="T77" s="33"/>
       <c r="U77" s="33"/>
       <c r="V77" s="8"/>
-    </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W77" s="8"/>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" s="15"/>
       <c r="B78" s="15"/>
       <c r="C78" s="16"/>
@@ -5305,8 +5387,9 @@
       <c r="T78" s="33"/>
       <c r="U78" s="33"/>
       <c r="V78" s="8"/>
-    </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W78" s="8"/>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" s="15"/>
       <c r="B79" s="15"/>
       <c r="C79" s="16"/>
@@ -5329,8 +5412,9 @@
       <c r="T79" s="33"/>
       <c r="U79" s="33"/>
       <c r="V79" s="8"/>
-    </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W79" s="8"/>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" s="15"/>
       <c r="B80" s="15"/>
       <c r="C80" s="16"/>
@@ -5353,8 +5437,9 @@
       <c r="T80" s="33"/>
       <c r="U80" s="33"/>
       <c r="V80" s="8"/>
-    </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W80" s="8"/>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" s="15"/>
       <c r="B81" s="15"/>
       <c r="C81" s="16"/>
@@ -5377,8 +5462,9 @@
       <c r="T81" s="33"/>
       <c r="U81" s="33"/>
       <c r="V81" s="8"/>
-    </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W81" s="8"/>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" s="15"/>
       <c r="B82" s="15"/>
       <c r="C82" s="16"/>
@@ -5401,8 +5487,9 @@
       <c r="T82" s="33"/>
       <c r="U82" s="33"/>
       <c r="V82" s="8"/>
-    </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W82" s="8"/>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" s="15"/>
       <c r="B83" s="15"/>
       <c r="C83" s="16"/>
@@ -5425,8 +5512,9 @@
       <c r="T83" s="33"/>
       <c r="U83" s="33"/>
       <c r="V83" s="8"/>
-    </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W83" s="8"/>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" s="15"/>
       <c r="B84" s="15"/>
       <c r="C84" s="16"/>
@@ -5449,8 +5537,9 @@
       <c r="T84" s="33"/>
       <c r="U84" s="33"/>
       <c r="V84" s="8"/>
-    </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W84" s="8"/>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" s="15"/>
       <c r="B85" s="15"/>
       <c r="C85" s="16"/>
@@ -5473,8 +5562,9 @@
       <c r="T85" s="33"/>
       <c r="U85" s="33"/>
       <c r="V85" s="8"/>
-    </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W85" s="8"/>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" s="15"/>
       <c r="B86" s="15"/>
       <c r="C86" s="16"/>
@@ -5497,8 +5587,9 @@
       <c r="T86" s="33"/>
       <c r="U86" s="33"/>
       <c r="V86" s="8"/>
-    </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W86" s="8"/>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" s="15"/>
       <c r="B87" s="15"/>
       <c r="C87" s="16"/>
@@ -5521,8 +5612,9 @@
       <c r="T87" s="33"/>
       <c r="U87" s="33"/>
       <c r="V87" s="8"/>
-    </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W87" s="8"/>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" s="15"/>
       <c r="B88" s="15"/>
       <c r="C88" s="16"/>
@@ -5545,8 +5637,9 @@
       <c r="T88" s="33"/>
       <c r="U88" s="33"/>
       <c r="V88" s="8"/>
-    </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W88" s="8"/>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" s="15"/>
       <c r="B89" s="15"/>
       <c r="C89" s="16"/>
@@ -5569,8 +5662,9 @@
       <c r="T89" s="33"/>
       <c r="U89" s="33"/>
       <c r="V89" s="8"/>
-    </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W89" s="8"/>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" s="15"/>
       <c r="B90" s="15"/>
       <c r="C90" s="16"/>
@@ -5593,8 +5687,9 @@
       <c r="T90" s="33"/>
       <c r="U90" s="33"/>
       <c r="V90" s="8"/>
-    </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W90" s="8"/>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" s="15"/>
       <c r="B91" s="15"/>
       <c r="C91" s="16"/>
@@ -5617,8 +5712,9 @@
       <c r="T91" s="33"/>
       <c r="U91" s="33"/>
       <c r="V91" s="8"/>
-    </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W91" s="8"/>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92" s="15"/>
       <c r="B92" s="15"/>
       <c r="C92" s="16"/>
@@ -5641,8 +5737,9 @@
       <c r="T92" s="33"/>
       <c r="U92" s="33"/>
       <c r="V92" s="8"/>
-    </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W92" s="8"/>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" s="15"/>
       <c r="B93" s="15"/>
       <c r="C93" s="16"/>
@@ -5665,8 +5762,9 @@
       <c r="T93" s="33"/>
       <c r="U93" s="33"/>
       <c r="V93" s="8"/>
-    </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W93" s="8"/>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" s="15"/>
       <c r="B94" s="15"/>
       <c r="C94" s="16"/>
@@ -5689,8 +5787,9 @@
       <c r="T94" s="33"/>
       <c r="U94" s="33"/>
       <c r="V94" s="8"/>
-    </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W94" s="8"/>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" s="15"/>
       <c r="B95" s="15"/>
       <c r="C95" s="16"/>
@@ -5713,8 +5812,9 @@
       <c r="T95" s="33"/>
       <c r="U95" s="33"/>
       <c r="V95" s="8"/>
-    </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W95" s="8"/>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" s="15"/>
       <c r="B96" s="15"/>
       <c r="C96" s="16"/>
@@ -5737,8 +5837,9 @@
       <c r="T96" s="33"/>
       <c r="U96" s="33"/>
       <c r="V96" s="8"/>
-    </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W96" s="8"/>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" s="15"/>
       <c r="B97" s="15"/>
       <c r="C97" s="16"/>
@@ -5761,8 +5862,9 @@
       <c r="T97" s="33"/>
       <c r="U97" s="33"/>
       <c r="V97" s="8"/>
-    </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W97" s="8"/>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A98" s="15"/>
       <c r="B98" s="15"/>
       <c r="C98" s="16"/>
@@ -5785,8 +5887,9 @@
       <c r="T98" s="33"/>
       <c r="U98" s="33"/>
       <c r="V98" s="8"/>
-    </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W98" s="8"/>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" s="15"/>
       <c r="B99" s="15"/>
       <c r="C99" s="16"/>
@@ -5809,8 +5912,9 @@
       <c r="T99" s="33"/>
       <c r="U99" s="33"/>
       <c r="V99" s="8"/>
-    </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W99" s="8"/>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A100" s="15"/>
       <c r="B100" s="15"/>
       <c r="C100" s="16"/>
@@ -5833,8 +5937,9 @@
       <c r="T100" s="33"/>
       <c r="U100" s="33"/>
       <c r="V100" s="8"/>
-    </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W100" s="8"/>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A101" s="15"/>
       <c r="B101" s="15"/>
       <c r="C101" s="16"/>
@@ -5857,8 +5962,9 @@
       <c r="T101" s="33"/>
       <c r="U101" s="33"/>
       <c r="V101" s="8"/>
-    </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W101" s="8"/>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A102" s="15"/>
       <c r="B102" s="15"/>
       <c r="C102" s="16"/>
@@ -5881,8 +5987,9 @@
       <c r="T102" s="33"/>
       <c r="U102" s="33"/>
       <c r="V102" s="8"/>
-    </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W102" s="8"/>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A103" s="15"/>
       <c r="B103" s="15"/>
       <c r="C103" s="16"/>
@@ -5905,8 +6012,9 @@
       <c r="T103" s="33"/>
       <c r="U103" s="33"/>
       <c r="V103" s="8"/>
-    </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W103" s="8"/>
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A104" s="15"/>
       <c r="B104" s="15"/>
       <c r="C104" s="16"/>
@@ -5929,8 +6037,9 @@
       <c r="T104" s="33"/>
       <c r="U104" s="33"/>
       <c r="V104" s="8"/>
-    </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W104" s="8"/>
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A105" s="15"/>
       <c r="B105" s="15"/>
       <c r="C105" s="16"/>
@@ -5953,8 +6062,9 @@
       <c r="T105" s="33"/>
       <c r="U105" s="33"/>
       <c r="V105" s="8"/>
-    </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W105" s="8"/>
+    </row>
+    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A106" s="15"/>
       <c r="B106" s="15"/>
       <c r="C106" s="16"/>
@@ -5977,8 +6087,9 @@
       <c r="T106" s="33"/>
       <c r="U106" s="33"/>
       <c r="V106" s="8"/>
-    </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W106" s="8"/>
+    </row>
+    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A107" s="15"/>
       <c r="B107" s="15"/>
       <c r="C107" s="16"/>
@@ -6001,8 +6112,9 @@
       <c r="T107" s="33"/>
       <c r="U107" s="33"/>
       <c r="V107" s="8"/>
-    </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W107" s="8"/>
+    </row>
+    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A108" s="15"/>
       <c r="B108" s="15"/>
       <c r="C108" s="16"/>
@@ -6025,8 +6137,9 @@
       <c r="T108" s="33"/>
       <c r="U108" s="33"/>
       <c r="V108" s="8"/>
-    </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W108" s="8"/>
+    </row>
+    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A109" s="15"/>
       <c r="B109" s="15"/>
       <c r="C109" s="16"/>
@@ -6049,8 +6162,9 @@
       <c r="T109" s="33"/>
       <c r="U109" s="33"/>
       <c r="V109" s="8"/>
-    </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W109" s="8"/>
+    </row>
+    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A110" s="15"/>
       <c r="B110" s="15"/>
       <c r="C110" s="16"/>
@@ -6073,8 +6187,9 @@
       <c r="T110" s="33"/>
       <c r="U110" s="33"/>
       <c r="V110" s="8"/>
-    </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W110" s="8"/>
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A111" s="15"/>
       <c r="B111" s="15"/>
       <c r="C111" s="16"/>
@@ -6097,8 +6212,9 @@
       <c r="T111" s="33"/>
       <c r="U111" s="33"/>
       <c r="V111" s="8"/>
-    </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W111" s="8"/>
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A112" s="15"/>
       <c r="B112" s="15"/>
       <c r="C112" s="16"/>
@@ -6121,8 +6237,9 @@
       <c r="T112" s="33"/>
       <c r="U112" s="33"/>
       <c r="V112" s="8"/>
-    </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W112" s="8"/>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A113" s="15"/>
       <c r="B113" s="15"/>
       <c r="C113" s="16"/>
@@ -6145,8 +6262,9 @@
       <c r="T113" s="33"/>
       <c r="U113" s="33"/>
       <c r="V113" s="8"/>
-    </row>
-    <row r="114" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W113" s="8"/>
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A114" s="15"/>
       <c r="B114" s="15"/>
       <c r="C114" s="16"/>
@@ -6169,8 +6287,9 @@
       <c r="T114" s="33"/>
       <c r="U114" s="33"/>
       <c r="V114" s="8"/>
-    </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W114" s="8"/>
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A115" s="15"/>
       <c r="B115" s="15"/>
       <c r="C115" s="16"/>
@@ -6193,8 +6312,9 @@
       <c r="T115" s="33"/>
       <c r="U115" s="33"/>
       <c r="V115" s="8"/>
-    </row>
-    <row r="116" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W115" s="8"/>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A116" s="15"/>
       <c r="B116" s="15"/>
       <c r="C116" s="16"/>
@@ -6217,8 +6337,9 @@
       <c r="T116" s="33"/>
       <c r="U116" s="33"/>
       <c r="V116" s="8"/>
-    </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W116" s="8"/>
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A117" s="15"/>
       <c r="B117" s="15"/>
       <c r="C117" s="16"/>
@@ -6241,8 +6362,9 @@
       <c r="T117" s="33"/>
       <c r="U117" s="33"/>
       <c r="V117" s="8"/>
-    </row>
-    <row r="118" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W117" s="8"/>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A118" s="15"/>
       <c r="B118" s="15"/>
       <c r="C118" s="16"/>
@@ -6265,8 +6387,9 @@
       <c r="T118" s="33"/>
       <c r="U118" s="33"/>
       <c r="V118" s="8"/>
-    </row>
-    <row r="119" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W118" s="8"/>
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A119" s="15"/>
       <c r="B119" s="15"/>
       <c r="C119" s="16"/>
@@ -6289,8 +6412,9 @@
       <c r="T119" s="33"/>
       <c r="U119" s="33"/>
       <c r="V119" s="8"/>
-    </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W119" s="8"/>
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A120" s="15"/>
       <c r="B120" s="15"/>
       <c r="C120" s="16"/>
@@ -6313,8 +6437,9 @@
       <c r="T120" s="33"/>
       <c r="U120" s="33"/>
       <c r="V120" s="8"/>
-    </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W120" s="8"/>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" s="15"/>
       <c r="B121" s="15"/>
       <c r="C121" s="16"/>
@@ -6337,8 +6462,9 @@
       <c r="T121" s="33"/>
       <c r="U121" s="33"/>
       <c r="V121" s="8"/>
-    </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W121" s="8"/>
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A122" s="15"/>
       <c r="B122" s="15"/>
       <c r="C122" s="16"/>
@@ -6361,8 +6487,9 @@
       <c r="T122" s="33"/>
       <c r="U122" s="33"/>
       <c r="V122" s="8"/>
-    </row>
-    <row r="123" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W122" s="8"/>
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A123" s="15"/>
       <c r="B123" s="15"/>
       <c r="C123" s="16"/>
@@ -6385,8 +6512,9 @@
       <c r="T123" s="33"/>
       <c r="U123" s="33"/>
       <c r="V123" s="8"/>
-    </row>
-    <row r="124" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W123" s="8"/>
+    </row>
+    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A124" s="15"/>
       <c r="B124" s="15"/>
       <c r="C124" s="16"/>
@@ -6409,8 +6537,9 @@
       <c r="T124" s="33"/>
       <c r="U124" s="33"/>
       <c r="V124" s="8"/>
-    </row>
-    <row r="125" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W124" s="8"/>
+    </row>
+    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A125" s="15"/>
       <c r="B125" s="15"/>
       <c r="C125" s="16"/>
@@ -6433,8 +6562,9 @@
       <c r="T125" s="33"/>
       <c r="U125" s="33"/>
       <c r="V125" s="8"/>
-    </row>
-    <row r="126" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W125" s="8"/>
+    </row>
+    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A126" s="15"/>
       <c r="B126" s="15"/>
       <c r="C126" s="16"/>
@@ -6457,8 +6587,9 @@
       <c r="T126" s="33"/>
       <c r="U126" s="33"/>
       <c r="V126" s="8"/>
-    </row>
-    <row r="127" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W126" s="8"/>
+    </row>
+    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A127" s="15"/>
       <c r="B127" s="15"/>
       <c r="C127" s="16"/>
@@ -6481,8 +6612,9 @@
       <c r="T127" s="33"/>
       <c r="U127" s="33"/>
       <c r="V127" s="8"/>
-    </row>
-    <row r="128" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W127" s="8"/>
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A128" s="15"/>
       <c r="B128" s="15"/>
       <c r="C128" s="16"/>
@@ -6505,8 +6637,9 @@
       <c r="T128" s="33"/>
       <c r="U128" s="33"/>
       <c r="V128" s="8"/>
-    </row>
-    <row r="129" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W128" s="8"/>
+    </row>
+    <row r="129" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A129" s="15"/>
       <c r="B129" s="15"/>
       <c r="C129" s="16"/>
@@ -6529,8 +6662,9 @@
       <c r="T129" s="33"/>
       <c r="U129" s="33"/>
       <c r="V129" s="8"/>
-    </row>
-    <row r="130" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W129" s="8"/>
+    </row>
+    <row r="130" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A130" s="15"/>
       <c r="B130" s="15"/>
       <c r="C130" s="16"/>
@@ -6553,8 +6687,9 @@
       <c r="T130" s="33"/>
       <c r="U130" s="33"/>
       <c r="V130" s="8"/>
-    </row>
-    <row r="131" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W130" s="8"/>
+    </row>
+    <row r="131" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A131" s="15"/>
       <c r="B131" s="15"/>
       <c r="C131" s="16"/>
@@ -6577,8 +6712,9 @@
       <c r="T131" s="33"/>
       <c r="U131" s="33"/>
       <c r="V131" s="8"/>
-    </row>
-    <row r="132" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W131" s="8"/>
+    </row>
+    <row r="132" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A132" s="15"/>
       <c r="B132" s="15"/>
       <c r="C132" s="16"/>
@@ -6601,8 +6737,9 @@
       <c r="T132" s="33"/>
       <c r="U132" s="33"/>
       <c r="V132" s="8"/>
-    </row>
-    <row r="133" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W132" s="8"/>
+    </row>
+    <row r="133" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A133" s="15"/>
       <c r="B133" s="15"/>
       <c r="C133" s="16"/>
@@ -6625,8 +6762,9 @@
       <c r="T133" s="33"/>
       <c r="U133" s="33"/>
       <c r="V133" s="8"/>
-    </row>
-    <row r="134" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W133" s="8"/>
+    </row>
+    <row r="134" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A134" s="15"/>
       <c r="B134" s="15"/>
       <c r="C134" s="16"/>
@@ -6649,8 +6787,9 @@
       <c r="T134" s="33"/>
       <c r="U134" s="33"/>
       <c r="V134" s="8"/>
-    </row>
-    <row r="135" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W134" s="8"/>
+    </row>
+    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A135" s="15"/>
       <c r="B135" s="15"/>
       <c r="C135" s="16"/>
@@ -6673,8 +6812,9 @@
       <c r="T135" s="33"/>
       <c r="U135" s="33"/>
       <c r="V135" s="8"/>
-    </row>
-    <row r="136" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W135" s="8"/>
+    </row>
+    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A136" s="15"/>
       <c r="B136" s="15"/>
       <c r="C136" s="16"/>
@@ -6697,8 +6837,9 @@
       <c r="T136" s="33"/>
       <c r="U136" s="33"/>
       <c r="V136" s="8"/>
-    </row>
-    <row r="137" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W136" s="8"/>
+    </row>
+    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A137" s="15"/>
       <c r="B137" s="15"/>
       <c r="C137" s="16"/>
@@ -6721,8 +6862,9 @@
       <c r="T137" s="33"/>
       <c r="U137" s="33"/>
       <c r="V137" s="8"/>
-    </row>
-    <row r="138" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W137" s="8"/>
+    </row>
+    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A138" s="15"/>
       <c r="B138" s="15"/>
       <c r="C138" s="16"/>
@@ -6745,8 +6887,9 @@
       <c r="T138" s="33"/>
       <c r="U138" s="33"/>
       <c r="V138" s="8"/>
-    </row>
-    <row r="139" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W138" s="8"/>
+    </row>
+    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A139" s="15"/>
       <c r="B139" s="15"/>
       <c r="C139" s="16"/>
@@ -6769,8 +6912,9 @@
       <c r="T139" s="33"/>
       <c r="U139" s="33"/>
       <c r="V139" s="8"/>
-    </row>
-    <row r="140" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W139" s="8"/>
+    </row>
+    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A140" s="15"/>
       <c r="B140" s="15"/>
       <c r="C140" s="16"/>
@@ -6793,8 +6937,9 @@
       <c r="T140" s="33"/>
       <c r="U140" s="33"/>
       <c r="V140" s="8"/>
-    </row>
-    <row r="141" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W140" s="8"/>
+    </row>
+    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A141" s="15"/>
       <c r="B141" s="15"/>
       <c r="C141" s="16"/>
@@ -6817,8 +6962,9 @@
       <c r="T141" s="33"/>
       <c r="U141" s="33"/>
       <c r="V141" s="8"/>
-    </row>
-    <row r="142" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W141" s="8"/>
+    </row>
+    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A142" s="15"/>
       <c r="B142" s="15"/>
       <c r="C142" s="16"/>
@@ -6841,8 +6987,9 @@
       <c r="T142" s="33"/>
       <c r="U142" s="33"/>
       <c r="V142" s="8"/>
-    </row>
-    <row r="143" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W142" s="8"/>
+    </row>
+    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A143" s="15"/>
       <c r="B143" s="15"/>
       <c r="C143" s="16"/>
@@ -6865,8 +7012,9 @@
       <c r="T143" s="33"/>
       <c r="U143" s="33"/>
       <c r="V143" s="8"/>
-    </row>
-    <row r="144" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W143" s="8"/>
+    </row>
+    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A144" s="15"/>
       <c r="B144" s="15"/>
       <c r="C144" s="16"/>
@@ -6889,8 +7037,9 @@
       <c r="T144" s="33"/>
       <c r="U144" s="33"/>
       <c r="V144" s="8"/>
-    </row>
-    <row r="145" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W144" s="8"/>
+    </row>
+    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A145" s="15"/>
       <c r="B145" s="15"/>
       <c r="C145" s="16"/>
@@ -6913,8 +7062,9 @@
       <c r="T145" s="33"/>
       <c r="U145" s="33"/>
       <c r="V145" s="8"/>
-    </row>
-    <row r="146" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W145" s="8"/>
+    </row>
+    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A146" s="15"/>
       <c r="B146" s="15"/>
       <c r="C146" s="16"/>
@@ -6937,8 +7087,9 @@
       <c r="T146" s="33"/>
       <c r="U146" s="33"/>
       <c r="V146" s="8"/>
-    </row>
-    <row r="147" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W146" s="8"/>
+    </row>
+    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A147" s="15"/>
       <c r="B147" s="15"/>
       <c r="C147" s="16"/>
@@ -6961,8 +7112,9 @@
       <c r="T147" s="33"/>
       <c r="U147" s="33"/>
       <c r="V147" s="8"/>
-    </row>
-    <row r="148" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W147" s="8"/>
+    </row>
+    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A148" s="15"/>
       <c r="B148" s="15"/>
       <c r="C148" s="16"/>
@@ -6985,8 +7137,9 @@
       <c r="T148" s="33"/>
       <c r="U148" s="33"/>
       <c r="V148" s="8"/>
-    </row>
-    <row r="149" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W148" s="8"/>
+    </row>
+    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A149" s="15"/>
       <c r="B149" s="15"/>
       <c r="C149" s="16"/>
@@ -7009,8 +7162,9 @@
       <c r="T149" s="33"/>
       <c r="U149" s="33"/>
       <c r="V149" s="8"/>
-    </row>
-    <row r="150" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W149" s="8"/>
+    </row>
+    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A150" s="15"/>
       <c r="B150" s="15"/>
       <c r="C150" s="16"/>
@@ -7033,8 +7187,9 @@
       <c r="T150" s="33"/>
       <c r="U150" s="33"/>
       <c r="V150" s="8"/>
-    </row>
-    <row r="151" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W150" s="8"/>
+    </row>
+    <row r="151" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A151" s="15"/>
       <c r="B151" s="15"/>
       <c r="C151" s="16"/>
@@ -7057,8 +7212,9 @@
       <c r="T151" s="33"/>
       <c r="U151" s="33"/>
       <c r="V151" s="8"/>
-    </row>
-    <row r="152" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W151" s="8"/>
+    </row>
+    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A152" s="15"/>
       <c r="B152" s="15"/>
       <c r="C152" s="16"/>
@@ -7081,8 +7237,9 @@
       <c r="T152" s="33"/>
       <c r="U152" s="33"/>
       <c r="V152" s="8"/>
-    </row>
-    <row r="153" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W152" s="8"/>
+    </row>
+    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A153" s="15"/>
       <c r="B153" s="15"/>
       <c r="C153" s="16"/>
@@ -7105,8 +7262,9 @@
       <c r="T153" s="33"/>
       <c r="U153" s="33"/>
       <c r="V153" s="8"/>
-    </row>
-    <row r="154" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W153" s="8"/>
+    </row>
+    <row r="154" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A154" s="15"/>
       <c r="B154" s="15"/>
       <c r="C154" s="16"/>
@@ -7129,8 +7287,9 @@
       <c r="T154" s="33"/>
       <c r="U154" s="33"/>
       <c r="V154" s="8"/>
-    </row>
-    <row r="155" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W154" s="8"/>
+    </row>
+    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A155" s="15"/>
       <c r="B155" s="15"/>
       <c r="C155" s="16"/>
@@ -7153,8 +7312,9 @@
       <c r="T155" s="33"/>
       <c r="U155" s="33"/>
       <c r="V155" s="8"/>
-    </row>
-    <row r="156" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W155" s="8"/>
+    </row>
+    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A156" s="15"/>
       <c r="B156" s="15"/>
       <c r="C156" s="16"/>
@@ -7177,8 +7337,9 @@
       <c r="T156" s="33"/>
       <c r="U156" s="33"/>
       <c r="V156" s="8"/>
-    </row>
-    <row r="157" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W156" s="8"/>
+    </row>
+    <row r="157" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A157" s="15"/>
       <c r="B157" s="15"/>
       <c r="C157" s="16"/>
@@ -7201,6 +7362,7 @@
       <c r="T157" s="33"/>
       <c r="U157" s="33"/>
       <c r="V157" s="8"/>
+      <c r="W157" s="8"/>
     </row>
   </sheetData>
   <sheetProtection insertRows="0"/>
@@ -7245,7 +7407,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="I10:J10 I11:J157" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="I10:J157" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="records@federation.org" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -7269,13 +7431,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
     </row>
     <row r="2" spans="1:22" s="36" customFormat="1" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="36" t="s">
@@ -7447,7 +7609,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="70"/>
+      <c r="A3" s="71"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>

--- a/owlcms/src/main/resources/templates/registration/SBDE.xlsx
+++ b/owlcms/src/main/resources/templates/registration/SBDE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\registration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5253F05-AB1C-46AB-9C4F-7A0B818BD76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88CF81EC-69F4-4E76-9B7C-9B45EEEFD981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26175" yWindow="780" windowWidth="23850" windowHeight="13980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Athletes" sheetId="1" r:id="rId1"/>
@@ -208,7 +208,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>jx:area(lastCell="V3")</t>
+          <t>jx:area(lastCell="W3")</t>
         </r>
       </text>
     </comment>
@@ -222,7 +222,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>jx:each(items="groups" var="g" lastCell="V3")</t>
+          <t>jx:each(items="groups" var="g" lastCell="W3")</t>
         </r>
         <r>
           <rPr>
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="120">
   <si>
     <t>M/F</t>
   </si>
@@ -633,6 +633,12 @@
   </si>
   <si>
     <t>${t.get("Competition.Invited/Extra")}</t>
+  </si>
+  <si>
+    <t>${t.get("Competition.masters")}</t>
+  </si>
+  <si>
+    <t>${g.masters}</t>
   </si>
 </sst>
 </file>
@@ -1583,7 +1589,7 @@
     <cellStyle name="Title" xfId="34" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="35" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="89">
+  <dxfs count="83">
     <dxf>
       <font>
         <b/>
@@ -1852,54 +1858,6 @@
           <color theme="4" tint="0.499984740745262"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -2279,7 +2237,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Jean-François Lamy" refreshedDate="45686.671195601855" createdVersion="8" refreshedVersion="8" recordCount="18" xr:uid="{00000000-000A-0000-FFFF-FFFF09000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Jean-François Lamy" refreshedDate="45736.622832986111" createdVersion="8" refreshedVersion="8" recordCount="18" xr:uid="{00000000-000A-0000-FFFF-FFFF09000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:G598" sheet="Group Data"/>
   </cacheSource>
@@ -2762,13 +2720,13 @@
     <i/>
   </colItems>
   <formats count="41">
-    <format dxfId="88">
+    <format dxfId="82">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="87">
+    <format dxfId="81">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="86">
+    <format dxfId="80">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2777,7 +2735,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="85">
+    <format dxfId="79">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2786,7 +2744,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="84">
+    <format dxfId="78">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2795,7 +2753,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="83">
+    <format dxfId="77">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2804,7 +2762,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="82">
+    <format dxfId="76">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2813,7 +2771,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="81">
+    <format dxfId="75">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2822,7 +2780,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="80">
+    <format dxfId="74">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2831,7 +2789,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="79">
+    <format dxfId="73">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2840,7 +2798,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="78">
+    <format dxfId="72">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2849,7 +2807,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="77">
+    <format dxfId="71">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2858,7 +2816,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="76">
+    <format dxfId="70">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2867,7 +2825,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="75">
+    <format dxfId="69">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2876,7 +2834,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="74">
+    <format dxfId="68">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2885,7 +2843,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="73">
+    <format dxfId="67">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2894,7 +2852,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="72">
+    <format dxfId="66">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2903,7 +2861,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="71">
+    <format dxfId="65">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2912,7 +2870,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="70">
+    <format dxfId="64">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2921,7 +2879,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="69">
+    <format dxfId="63">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2930,7 +2888,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="68">
+    <format dxfId="62">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2939,7 +2897,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="67">
+    <format dxfId="61">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2948,7 +2906,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="66">
+    <format dxfId="60">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2957,7 +2915,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="65">
+    <format dxfId="59">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2966,7 +2924,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="64">
+    <format dxfId="58">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2975,7 +2933,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="63">
+    <format dxfId="57">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2984,7 +2942,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="62">
+    <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2993,7 +2951,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="61">
+    <format dxfId="55">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -3002,7 +2960,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="60">
+    <format dxfId="54">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -3011,7 +2969,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="59">
+    <format dxfId="53">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -3020,7 +2978,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="58">
+    <format dxfId="52">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -3029,7 +2987,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="57">
+    <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -3038,7 +2996,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="56">
+    <format dxfId="50">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -3047,7 +3005,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="55">
+    <format dxfId="49">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -3056,7 +3014,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="54">
+    <format dxfId="48">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -3065,7 +3023,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="53">
+    <format dxfId="47">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -3074,19 +3032,19 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="52">
+    <format dxfId="46">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="51">
+    <format dxfId="45">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" offset="A1" fieldPosition="0"/>
     </format>
-    <format dxfId="50">
+    <format dxfId="44">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" offset="A1" fieldPosition="0"/>
     </format>
-    <format dxfId="49">
+    <format dxfId="43">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" offset="A1" fieldPosition="0"/>
     </format>
-    <format dxfId="48">
+    <format dxfId="42">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -7371,38 +7329,8 @@
     <mergeCell ref="A7:M7"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="C10:F10">
-    <cfRule type="expression" dxfId="47" priority="10" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C11:F31">
-    <cfRule type="expression" dxfId="46" priority="8" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C32:F52">
-    <cfRule type="expression" dxfId="45" priority="6" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C53:F73">
-    <cfRule type="expression" dxfId="44" priority="5" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C74:F157">
-    <cfRule type="expression" dxfId="43" priority="1" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G10">
-    <cfRule type="expression" dxfId="42" priority="9" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11:G157">
-    <cfRule type="expression" dxfId="41" priority="7" stopIfTrue="1">
+  <conditionalFormatting sqref="C10:G157">
+    <cfRule type="expression" dxfId="41" priority="1" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7422,7 +7350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="25.42578125" customWidth="1"/>
@@ -7430,7 +7358,7 @@
     <col min="6" max="21" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="70" t="s">
         <v>19</v>
       </c>
@@ -7439,7 +7367,7 @@
       <c r="D1" s="70"/>
       <c r="E1" s="70"/>
     </row>
-    <row r="2" spans="1:22" s="36" customFormat="1" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" s="36" customFormat="1" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="36" t="s">
         <v>3</v>
       </c>
@@ -7506,8 +7434,11 @@
       <c r="V2" s="36" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="W2" s="36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>40</v>
       </c>
@@ -7573,6 +7504,9 @@
       </c>
       <c r="V3" s="1" t="s">
         <v>54</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/owlcms/src/main/resources/templates/registration/SBDE.xlsx
+++ b/owlcms/src/main/resources/templates/registration/SBDE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\registration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88CF81EC-69F4-4E76-9B7C-9B45EEEFD981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB27CE53-43BA-462B-AF57-B8A839FDC7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26520" yWindow="3615" windowWidth="25215" windowHeight="7455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Athletes" sheetId="1" r:id="rId1"/>
@@ -2237,7 +2237,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Jean-François Lamy" refreshedDate="45736.622832986111" createdVersion="8" refreshedVersion="8" recordCount="18" xr:uid="{00000000-000A-0000-FFFF-FFFF09000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Jean-François Lamy" refreshedDate="45743.458344791667" createdVersion="8" refreshedVersion="8" recordCount="18" xr:uid="{00000000-000A-0000-FFFF-FFFF09000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:G598" sheet="Group Data"/>
   </cacheSource>

--- a/owlcms/src/main/resources/templates/registration/SBDE.xlsx
+++ b/owlcms/src/main/resources/templates/registration/SBDE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\registration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB27CE53-43BA-462B-AF57-B8A839FDC7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523DFECB-C61B-4CC6-89D2-9AEED9DAE477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26520" yWindow="3615" windowWidth="25215" windowHeight="7455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24390" yWindow="1905" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Athletes" sheetId="1" r:id="rId1"/>
@@ -121,7 +121,7 @@
   </definedNames>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId6"/>
+    <pivotCache cacheId="19" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1366,7 +1366,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1442,9 +1442,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1494,10 +1491,6 @@
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1550,6 +1543,19 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="36">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -2237,7 +2243,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Jean-François Lamy" refreshedDate="45743.458344791667" createdVersion="8" refreshedVersion="8" recordCount="18" xr:uid="{00000000-000A-0000-FFFF-FFFF09000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Jean-François Lamy" refreshedDate="45755.444146296293" createdVersion="8" refreshedVersion="8" recordCount="18" xr:uid="{00000000-000A-0000-FFFF-FFFF09000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:G598" sheet="Group Data"/>
   </cacheSource>
@@ -2492,7 +2498,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable2" cacheId="9" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" minRefreshableVersion="3" showMemberPropertyTips="0" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable2" cacheId="19" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" minRefreshableVersion="3" showMemberPropertyTips="0" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1">
   <location ref="A3:L22" firstHeaderRow="2" firstDataRow="2" firstDataCol="6"/>
   <pivotFields count="7">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" includeNewItemsInFilter="1" defaultSubtotal="0">
@@ -3356,10 +3362,10 @@
     <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="19.5703125" customWidth="1"/>
     <col min="5" max="5" width="19.5703125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" style="44" customWidth="1"/>
     <col min="7" max="7" width="4.140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="9" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.140625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="11.5703125" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="11.5703125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="10" max="10" width="8" style="1" customWidth="1"/>
     <col min="11" max="11" width="6.85546875" style="1" customWidth="1"/>
     <col min="12" max="12" width="8" style="1" customWidth="1"/>
@@ -3377,7 +3383,7 @@
       <c r="E1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="70" t="s">
         <v>32</v>
       </c>
       <c r="G1" s="13"/>
@@ -3387,10 +3393,10 @@
       <c r="L1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="64" t="s">
+      <c r="M1" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="67"/>
+      <c r="N1" s="65"/>
       <c r="P1" s="22"/>
       <c r="Q1" s="22"/>
       <c r="R1" s="22"/>
@@ -3404,7 +3410,7 @@
       <c r="E2" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="70" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="13"/>
@@ -3421,7 +3427,7 @@
       <c r="E3" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="70" t="s">
         <v>33</v>
       </c>
       <c r="G3" s="13"/>
@@ -3439,7 +3445,7 @@
       <c r="E4" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="70" t="s">
         <v>34</v>
       </c>
       <c r="G4" s="13"/>
@@ -3451,59 +3457,59 @@
     </row>
     <row r="5" spans="1:23" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:23" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="69" t="s">
+      <c r="A6" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="66"/>
-      <c r="O6" s="66"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="64"/>
     </row>
     <row r="7" spans="1:23" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="69" t="s">
+      <c r="A7" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="69"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="69"/>
-      <c r="M7" s="69"/>
-      <c r="N7" s="66"/>
-      <c r="O7" s="66"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="67"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="67"/>
+      <c r="M7" s="67"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
     </row>
     <row r="8" spans="1:23" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="65"/>
-      <c r="B8" s="65"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="65"/>
-      <c r="H8" s="65"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="65"/>
-      <c r="K8" s="65"/>
-      <c r="L8" s="65"/>
-      <c r="M8" s="65"/>
-      <c r="N8" s="65"/>
-      <c r="O8" s="65"/>
+      <c r="A8" s="63"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="63"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="63"/>
+      <c r="O8" s="63"/>
     </row>
     <row r="9" spans="1:23" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
@@ -3521,7 +3527,7 @@
       <c r="E9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="72" t="s">
         <v>5</v>
       </c>
       <c r="G9" s="5" t="s">
@@ -3572,78 +3578,78 @@
       <c r="V9" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="W9" s="68" t="s">
+      <c r="W9" s="66" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:23" s="40" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+    <row r="10" spans="1:23" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="29" t="s">
         <v>23</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="43" t="s">
+      <c r="F10" s="73" t="s">
         <v>115</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="G10" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="34" t="s">
+      <c r="H10" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="I10" s="38" t="s">
+      <c r="I10" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="41" t="s">
+      <c r="J10" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="K10" s="39" t="s">
+      <c r="K10" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="L10" s="41" t="s">
+      <c r="L10" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="M10" s="42" t="s">
+      <c r="M10" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="N10" s="42" t="s">
+      <c r="N10" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="O10" s="42" t="s">
+      <c r="O10" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="P10" s="42" t="s">
+      <c r="P10" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="Q10" s="42" t="s">
+      <c r="Q10" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="R10" s="42" t="s">
+      <c r="R10" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="S10" s="42" t="s">
+      <c r="S10" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="T10" s="32" t="s">
+      <c r="T10" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="U10" s="32" t="s">
+      <c r="U10" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="V10" s="42" t="s">
+      <c r="V10" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="W10" s="42" t="s">
+      <c r="W10" s="41" t="s">
         <v>116</v>
       </c>
     </row>
@@ -3653,10 +3659,10 @@
       <c r="C11" s="16"/>
       <c r="D11" s="23"/>
       <c r="E11" s="17"/>
-      <c r="F11" s="43"/>
+      <c r="F11" s="73"/>
       <c r="G11" s="23"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="31"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="30"/>
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
@@ -3667,8 +3673,8 @@
       <c r="Q11" s="8"/>
       <c r="R11" s="8"/>
       <c r="S11" s="8"/>
-      <c r="T11" s="33"/>
-      <c r="U11" s="33"/>
+      <c r="T11" s="32"/>
+      <c r="U11" s="32"/>
       <c r="V11" s="8"/>
       <c r="W11" s="8"/>
     </row>
@@ -3678,10 +3684,10 @@
       <c r="C12" s="16"/>
       <c r="D12" s="23"/>
       <c r="E12" s="17"/>
-      <c r="F12" s="43"/>
+      <c r="F12" s="73"/>
       <c r="G12" s="23"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="31"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="30"/>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
@@ -3692,8 +3698,8 @@
       <c r="Q12" s="8"/>
       <c r="R12" s="8"/>
       <c r="S12" s="8"/>
-      <c r="T12" s="33"/>
-      <c r="U12" s="33"/>
+      <c r="T12" s="32"/>
+      <c r="U12" s="32"/>
       <c r="V12" s="8"/>
       <c r="W12" s="8"/>
     </row>
@@ -3703,10 +3709,10 @@
       <c r="C13" s="16"/>
       <c r="D13" s="23"/>
       <c r="E13" s="17"/>
-      <c r="F13" s="43"/>
+      <c r="F13" s="73"/>
       <c r="G13" s="23"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="31"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="30"/>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
@@ -3717,8 +3723,8 @@
       <c r="Q13" s="8"/>
       <c r="R13" s="8"/>
       <c r="S13" s="8"/>
-      <c r="T13" s="33"/>
-      <c r="U13" s="33"/>
+      <c r="T13" s="32"/>
+      <c r="U13" s="32"/>
       <c r="V13" s="8"/>
       <c r="W13" s="8"/>
     </row>
@@ -3728,10 +3734,10 @@
       <c r="C14" s="16"/>
       <c r="D14" s="23"/>
       <c r="E14" s="17"/>
-      <c r="F14" s="43"/>
+      <c r="F14" s="73"/>
       <c r="G14" s="23"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="31"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="30"/>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -3742,8 +3748,8 @@
       <c r="Q14" s="8"/>
       <c r="R14" s="8"/>
       <c r="S14" s="8"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="33"/>
+      <c r="T14" s="32"/>
+      <c r="U14" s="32"/>
       <c r="V14" s="8"/>
       <c r="W14" s="8"/>
     </row>
@@ -3753,10 +3759,10 @@
       <c r="C15" s="16"/>
       <c r="D15" s="23"/>
       <c r="E15" s="17"/>
-      <c r="F15" s="43"/>
+      <c r="F15" s="73"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="31"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="30"/>
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
@@ -3767,8 +3773,8 @@
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
       <c r="S15" s="8"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="33"/>
+      <c r="T15" s="32"/>
+      <c r="U15" s="32"/>
       <c r="V15" s="8"/>
       <c r="W15" s="8"/>
     </row>
@@ -3778,10 +3784,10 @@
       <c r="C16" s="16"/>
       <c r="D16" s="23"/>
       <c r="E16" s="17"/>
-      <c r="F16" s="43"/>
+      <c r="F16" s="73"/>
       <c r="G16" s="23"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="31"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="30"/>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -3792,8 +3798,8 @@
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
       <c r="S16" s="8"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="33"/>
+      <c r="T16" s="32"/>
+      <c r="U16" s="32"/>
       <c r="V16" s="8"/>
       <c r="W16" s="8"/>
     </row>
@@ -3803,10 +3809,10 @@
       <c r="C17" s="16"/>
       <c r="D17" s="23"/>
       <c r="E17" s="17"/>
-      <c r="F17" s="43"/>
+      <c r="F17" s="73"/>
       <c r="G17" s="23"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="31"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="30"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
@@ -3817,8 +3823,8 @@
       <c r="Q17" s="8"/>
       <c r="R17" s="8"/>
       <c r="S17" s="8"/>
-      <c r="T17" s="33"/>
-      <c r="U17" s="33"/>
+      <c r="T17" s="32"/>
+      <c r="U17" s="32"/>
       <c r="V17" s="8"/>
       <c r="W17" s="8"/>
     </row>
@@ -3828,10 +3834,10 @@
       <c r="C18" s="16"/>
       <c r="D18" s="23"/>
       <c r="E18" s="17"/>
-      <c r="F18" s="43"/>
+      <c r="F18" s="73"/>
       <c r="G18" s="23"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="31"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="30"/>
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
@@ -3842,8 +3848,8 @@
       <c r="Q18" s="8"/>
       <c r="R18" s="8"/>
       <c r="S18" s="8"/>
-      <c r="T18" s="33"/>
-      <c r="U18" s="33"/>
+      <c r="T18" s="32"/>
+      <c r="U18" s="32"/>
       <c r="V18" s="8"/>
       <c r="W18" s="8"/>
     </row>
@@ -3853,10 +3859,10 @@
       <c r="C19" s="16"/>
       <c r="D19" s="23"/>
       <c r="E19" s="17"/>
-      <c r="F19" s="43"/>
+      <c r="F19" s="73"/>
       <c r="G19" s="23"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="31"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="30"/>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
@@ -3867,8 +3873,8 @@
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
       <c r="S19" s="8"/>
-      <c r="T19" s="33"/>
-      <c r="U19" s="33"/>
+      <c r="T19" s="32"/>
+      <c r="U19" s="32"/>
       <c r="V19" s="8"/>
       <c r="W19" s="8"/>
     </row>
@@ -3878,10 +3884,10 @@
       <c r="C20" s="16"/>
       <c r="D20" s="23"/>
       <c r="E20" s="17"/>
-      <c r="F20" s="43"/>
+      <c r="F20" s="73"/>
       <c r="G20" s="23"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="31"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="30"/>
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
@@ -3892,8 +3898,8 @@
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
       <c r="S20" s="8"/>
-      <c r="T20" s="33"/>
-      <c r="U20" s="33"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
       <c r="V20" s="8"/>
       <c r="W20" s="8"/>
     </row>
@@ -3903,10 +3909,10 @@
       <c r="C21" s="16"/>
       <c r="D21" s="23"/>
       <c r="E21" s="17"/>
-      <c r="F21" s="43"/>
+      <c r="F21" s="73"/>
       <c r="G21" s="23"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="31"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="30"/>
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
@@ -3917,8 +3923,8 @@
       <c r="Q21" s="8"/>
       <c r="R21" s="8"/>
       <c r="S21" s="8"/>
-      <c r="T21" s="33"/>
-      <c r="U21" s="33"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="32"/>
       <c r="V21" s="8"/>
       <c r="W21" s="8"/>
     </row>
@@ -3928,10 +3934,10 @@
       <c r="C22" s="16"/>
       <c r="D22" s="23"/>
       <c r="E22" s="17"/>
-      <c r="F22" s="43"/>
+      <c r="F22" s="73"/>
       <c r="G22" s="23"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="31"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="30"/>
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
@@ -3942,8 +3948,8 @@
       <c r="Q22" s="8"/>
       <c r="R22" s="8"/>
       <c r="S22" s="8"/>
-      <c r="T22" s="33"/>
-      <c r="U22" s="33"/>
+      <c r="T22" s="32"/>
+      <c r="U22" s="32"/>
       <c r="V22" s="8"/>
       <c r="W22" s="8"/>
     </row>
@@ -3953,10 +3959,10 @@
       <c r="C23" s="16"/>
       <c r="D23" s="23"/>
       <c r="E23" s="17"/>
-      <c r="F23" s="43"/>
+      <c r="F23" s="73"/>
       <c r="G23" s="23"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="31"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="30"/>
       <c r="J23" s="8"/>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
@@ -3967,8 +3973,8 @@
       <c r="Q23" s="8"/>
       <c r="R23" s="8"/>
       <c r="S23" s="8"/>
-      <c r="T23" s="33"/>
-      <c r="U23" s="33"/>
+      <c r="T23" s="32"/>
+      <c r="U23" s="32"/>
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
     </row>
@@ -3978,10 +3984,10 @@
       <c r="C24" s="16"/>
       <c r="D24" s="23"/>
       <c r="E24" s="17"/>
-      <c r="F24" s="43"/>
+      <c r="F24" s="73"/>
       <c r="G24" s="23"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="31"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="30"/>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
@@ -3992,8 +3998,8 @@
       <c r="Q24" s="8"/>
       <c r="R24" s="8"/>
       <c r="S24" s="8"/>
-      <c r="T24" s="33"/>
-      <c r="U24" s="33"/>
+      <c r="T24" s="32"/>
+      <c r="U24" s="32"/>
       <c r="V24" s="8"/>
       <c r="W24" s="8"/>
     </row>
@@ -4003,10 +4009,10 @@
       <c r="C25" s="16"/>
       <c r="D25" s="23"/>
       <c r="E25" s="17"/>
-      <c r="F25" s="43"/>
+      <c r="F25" s="73"/>
       <c r="G25" s="23"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="31"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="30"/>
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
@@ -4017,8 +4023,8 @@
       <c r="Q25" s="8"/>
       <c r="R25" s="8"/>
       <c r="S25" s="8"/>
-      <c r="T25" s="33"/>
-      <c r="U25" s="33"/>
+      <c r="T25" s="32"/>
+      <c r="U25" s="32"/>
       <c r="V25" s="8"/>
       <c r="W25" s="8"/>
     </row>
@@ -4028,10 +4034,10 @@
       <c r="C26" s="16"/>
       <c r="D26" s="23"/>
       <c r="E26" s="17"/>
-      <c r="F26" s="43"/>
+      <c r="F26" s="73"/>
       <c r="G26" s="23"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="31"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="30"/>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
@@ -4042,8 +4048,8 @@
       <c r="Q26" s="8"/>
       <c r="R26" s="8"/>
       <c r="S26" s="8"/>
-      <c r="T26" s="33"/>
-      <c r="U26" s="33"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="32"/>
       <c r="V26" s="8"/>
       <c r="W26" s="8"/>
     </row>
@@ -4053,10 +4059,10 @@
       <c r="C27" s="16"/>
       <c r="D27" s="23"/>
       <c r="E27" s="17"/>
-      <c r="F27" s="43"/>
+      <c r="F27" s="73"/>
       <c r="G27" s="23"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="31"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="30"/>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
@@ -4067,8 +4073,8 @@
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
       <c r="S27" s="8"/>
-      <c r="T27" s="33"/>
-      <c r="U27" s="33"/>
+      <c r="T27" s="32"/>
+      <c r="U27" s="32"/>
       <c r="V27" s="8"/>
       <c r="W27" s="8"/>
     </row>
@@ -4078,10 +4084,10 @@
       <c r="C28" s="16"/>
       <c r="D28" s="23"/>
       <c r="E28" s="17"/>
-      <c r="F28" s="43"/>
+      <c r="F28" s="73"/>
       <c r="G28" s="23"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="31"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="30"/>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
@@ -4092,8 +4098,8 @@
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
       <c r="S28" s="8"/>
-      <c r="T28" s="33"/>
-      <c r="U28" s="33"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="32"/>
       <c r="V28" s="8"/>
       <c r="W28" s="8"/>
     </row>
@@ -4103,10 +4109,10 @@
       <c r="C29" s="16"/>
       <c r="D29" s="23"/>
       <c r="E29" s="17"/>
-      <c r="F29" s="43"/>
+      <c r="F29" s="73"/>
       <c r="G29" s="23"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="31"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="30"/>
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
@@ -4117,8 +4123,8 @@
       <c r="Q29" s="8"/>
       <c r="R29" s="8"/>
       <c r="S29" s="8"/>
-      <c r="T29" s="33"/>
-      <c r="U29" s="33"/>
+      <c r="T29" s="32"/>
+      <c r="U29" s="32"/>
       <c r="V29" s="8"/>
       <c r="W29" s="8"/>
     </row>
@@ -4128,10 +4134,10 @@
       <c r="C30" s="16"/>
       <c r="D30" s="23"/>
       <c r="E30" s="17"/>
-      <c r="F30" s="43"/>
+      <c r="F30" s="73"/>
       <c r="G30" s="23"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="31"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="30"/>
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
@@ -4142,8 +4148,8 @@
       <c r="Q30" s="8"/>
       <c r="R30" s="8"/>
       <c r="S30" s="8"/>
-      <c r="T30" s="33"/>
-      <c r="U30" s="33"/>
+      <c r="T30" s="32"/>
+      <c r="U30" s="32"/>
       <c r="V30" s="8"/>
       <c r="W30" s="8"/>
     </row>
@@ -4153,10 +4159,10 @@
       <c r="C31" s="16"/>
       <c r="D31" s="23"/>
       <c r="E31" s="17"/>
-      <c r="F31" s="43"/>
+      <c r="F31" s="73"/>
       <c r="G31" s="23"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="31"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="30"/>
       <c r="J31" s="8"/>
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
@@ -4167,8 +4173,8 @@
       <c r="Q31" s="8"/>
       <c r="R31" s="8"/>
       <c r="S31" s="8"/>
-      <c r="T31" s="33"/>
-      <c r="U31" s="33"/>
+      <c r="T31" s="32"/>
+      <c r="U31" s="32"/>
       <c r="V31" s="8"/>
       <c r="W31" s="8"/>
     </row>
@@ -4178,10 +4184,10 @@
       <c r="C32" s="16"/>
       <c r="D32" s="23"/>
       <c r="E32" s="17"/>
-      <c r="F32" s="43"/>
+      <c r="F32" s="73"/>
       <c r="G32" s="23"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="31"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="30"/>
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
       <c r="L32" s="8"/>
@@ -4192,8 +4198,8 @@
       <c r="Q32" s="8"/>
       <c r="R32" s="8"/>
       <c r="S32" s="8"/>
-      <c r="T32" s="33"/>
-      <c r="U32" s="33"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
       <c r="V32" s="8"/>
       <c r="W32" s="8"/>
     </row>
@@ -4203,10 +4209,10 @@
       <c r="C33" s="16"/>
       <c r="D33" s="23"/>
       <c r="E33" s="17"/>
-      <c r="F33" s="43"/>
+      <c r="F33" s="73"/>
       <c r="G33" s="23"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="31"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="30"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
@@ -4217,8 +4223,8 @@
       <c r="Q33" s="8"/>
       <c r="R33" s="8"/>
       <c r="S33" s="8"/>
-      <c r="T33" s="33"/>
-      <c r="U33" s="33"/>
+      <c r="T33" s="32"/>
+      <c r="U33" s="32"/>
       <c r="V33" s="8"/>
       <c r="W33" s="8"/>
     </row>
@@ -4228,10 +4234,10 @@
       <c r="C34" s="16"/>
       <c r="D34" s="23"/>
       <c r="E34" s="17"/>
-      <c r="F34" s="43"/>
+      <c r="F34" s="73"/>
       <c r="G34" s="23"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="31"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="30"/>
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
       <c r="L34" s="8"/>
@@ -4242,8 +4248,8 @@
       <c r="Q34" s="8"/>
       <c r="R34" s="8"/>
       <c r="S34" s="8"/>
-      <c r="T34" s="33"/>
-      <c r="U34" s="33"/>
+      <c r="T34" s="32"/>
+      <c r="U34" s="32"/>
       <c r="V34" s="8"/>
       <c r="W34" s="8"/>
     </row>
@@ -4253,10 +4259,10 @@
       <c r="C35" s="16"/>
       <c r="D35" s="23"/>
       <c r="E35" s="17"/>
-      <c r="F35" s="43"/>
+      <c r="F35" s="73"/>
       <c r="G35" s="23"/>
-      <c r="H35" s="35"/>
-      <c r="I35" s="31"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="30"/>
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
@@ -4267,8 +4273,8 @@
       <c r="Q35" s="8"/>
       <c r="R35" s="8"/>
       <c r="S35" s="8"/>
-      <c r="T35" s="33"/>
-      <c r="U35" s="33"/>
+      <c r="T35" s="32"/>
+      <c r="U35" s="32"/>
       <c r="V35" s="8"/>
       <c r="W35" s="8"/>
     </row>
@@ -4278,10 +4284,10 @@
       <c r="C36" s="16"/>
       <c r="D36" s="23"/>
       <c r="E36" s="17"/>
-      <c r="F36" s="43"/>
+      <c r="F36" s="73"/>
       <c r="G36" s="23"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="31"/>
+      <c r="H36" s="34"/>
+      <c r="I36" s="30"/>
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
       <c r="L36" s="8"/>
@@ -4292,8 +4298,8 @@
       <c r="Q36" s="8"/>
       <c r="R36" s="8"/>
       <c r="S36" s="8"/>
-      <c r="T36" s="33"/>
-      <c r="U36" s="33"/>
+      <c r="T36" s="32"/>
+      <c r="U36" s="32"/>
       <c r="V36" s="8"/>
       <c r="W36" s="8"/>
     </row>
@@ -4303,10 +4309,10 @@
       <c r="C37" s="16"/>
       <c r="D37" s="23"/>
       <c r="E37" s="17"/>
-      <c r="F37" s="43"/>
+      <c r="F37" s="73"/>
       <c r="G37" s="23"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="31"/>
+      <c r="H37" s="34"/>
+      <c r="I37" s="30"/>
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
       <c r="L37" s="8"/>
@@ -4317,8 +4323,8 @@
       <c r="Q37" s="8"/>
       <c r="R37" s="8"/>
       <c r="S37" s="8"/>
-      <c r="T37" s="33"/>
-      <c r="U37" s="33"/>
+      <c r="T37" s="32"/>
+      <c r="U37" s="32"/>
       <c r="V37" s="8"/>
       <c r="W37" s="8"/>
     </row>
@@ -4328,10 +4334,10 @@
       <c r="C38" s="16"/>
       <c r="D38" s="23"/>
       <c r="E38" s="17"/>
-      <c r="F38" s="43"/>
+      <c r="F38" s="73"/>
       <c r="G38" s="23"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="31"/>
+      <c r="H38" s="34"/>
+      <c r="I38" s="30"/>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
@@ -4342,8 +4348,8 @@
       <c r="Q38" s="8"/>
       <c r="R38" s="8"/>
       <c r="S38" s="8"/>
-      <c r="T38" s="33"/>
-      <c r="U38" s="33"/>
+      <c r="T38" s="32"/>
+      <c r="U38" s="32"/>
       <c r="V38" s="8"/>
       <c r="W38" s="8"/>
     </row>
@@ -4353,10 +4359,10 @@
       <c r="C39" s="16"/>
       <c r="D39" s="23"/>
       <c r="E39" s="17"/>
-      <c r="F39" s="43"/>
+      <c r="F39" s="73"/>
       <c r="G39" s="23"/>
-      <c r="H39" s="35"/>
-      <c r="I39" s="31"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="30"/>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
@@ -4367,8 +4373,8 @@
       <c r="Q39" s="8"/>
       <c r="R39" s="8"/>
       <c r="S39" s="8"/>
-      <c r="T39" s="33"/>
-      <c r="U39" s="33"/>
+      <c r="T39" s="32"/>
+      <c r="U39" s="32"/>
       <c r="V39" s="8"/>
       <c r="W39" s="8"/>
     </row>
@@ -4378,10 +4384,10 @@
       <c r="C40" s="16"/>
       <c r="D40" s="23"/>
       <c r="E40" s="17"/>
-      <c r="F40" s="43"/>
+      <c r="F40" s="73"/>
       <c r="G40" s="23"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="31"/>
+      <c r="H40" s="34"/>
+      <c r="I40" s="30"/>
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
       <c r="L40" s="8"/>
@@ -4392,8 +4398,8 @@
       <c r="Q40" s="8"/>
       <c r="R40" s="8"/>
       <c r="S40" s="8"/>
-      <c r="T40" s="33"/>
-      <c r="U40" s="33"/>
+      <c r="T40" s="32"/>
+      <c r="U40" s="32"/>
       <c r="V40" s="8"/>
       <c r="W40" s="8"/>
     </row>
@@ -4403,10 +4409,10 @@
       <c r="C41" s="16"/>
       <c r="D41" s="23"/>
       <c r="E41" s="17"/>
-      <c r="F41" s="43"/>
+      <c r="F41" s="73"/>
       <c r="G41" s="23"/>
-      <c r="H41" s="35"/>
-      <c r="I41" s="31"/>
+      <c r="H41" s="34"/>
+      <c r="I41" s="30"/>
       <c r="J41" s="8"/>
       <c r="K41" s="8"/>
       <c r="L41" s="8"/>
@@ -4417,8 +4423,8 @@
       <c r="Q41" s="8"/>
       <c r="R41" s="8"/>
       <c r="S41" s="8"/>
-      <c r="T41" s="33"/>
-      <c r="U41" s="33"/>
+      <c r="T41" s="32"/>
+      <c r="U41" s="32"/>
       <c r="V41" s="8"/>
       <c r="W41" s="8"/>
     </row>
@@ -4428,10 +4434,10 @@
       <c r="C42" s="16"/>
       <c r="D42" s="23"/>
       <c r="E42" s="17"/>
-      <c r="F42" s="43"/>
+      <c r="F42" s="73"/>
       <c r="G42" s="23"/>
-      <c r="H42" s="35"/>
-      <c r="I42" s="31"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="30"/>
       <c r="J42" s="8"/>
       <c r="K42" s="8"/>
       <c r="L42" s="8"/>
@@ -4442,8 +4448,8 @@
       <c r="Q42" s="8"/>
       <c r="R42" s="8"/>
       <c r="S42" s="8"/>
-      <c r="T42" s="33"/>
-      <c r="U42" s="33"/>
+      <c r="T42" s="32"/>
+      <c r="U42" s="32"/>
       <c r="V42" s="8"/>
       <c r="W42" s="8"/>
     </row>
@@ -4453,10 +4459,10 @@
       <c r="C43" s="16"/>
       <c r="D43" s="23"/>
       <c r="E43" s="17"/>
-      <c r="F43" s="43"/>
+      <c r="F43" s="73"/>
       <c r="G43" s="23"/>
-      <c r="H43" s="35"/>
-      <c r="I43" s="31"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="30"/>
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
       <c r="L43" s="8"/>
@@ -4467,8 +4473,8 @@
       <c r="Q43" s="8"/>
       <c r="R43" s="8"/>
       <c r="S43" s="8"/>
-      <c r="T43" s="33"/>
-      <c r="U43" s="33"/>
+      <c r="T43" s="32"/>
+      <c r="U43" s="32"/>
       <c r="V43" s="8"/>
       <c r="W43" s="8"/>
     </row>
@@ -4478,10 +4484,10 @@
       <c r="C44" s="16"/>
       <c r="D44" s="23"/>
       <c r="E44" s="17"/>
-      <c r="F44" s="43"/>
+      <c r="F44" s="73"/>
       <c r="G44" s="23"/>
-      <c r="H44" s="35"/>
-      <c r="I44" s="31"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="30"/>
       <c r="J44" s="8"/>
       <c r="K44" s="8"/>
       <c r="L44" s="8"/>
@@ -4492,8 +4498,8 @@
       <c r="Q44" s="8"/>
       <c r="R44" s="8"/>
       <c r="S44" s="8"/>
-      <c r="T44" s="33"/>
-      <c r="U44" s="33"/>
+      <c r="T44" s="32"/>
+      <c r="U44" s="32"/>
       <c r="V44" s="8"/>
       <c r="W44" s="8"/>
     </row>
@@ -4503,10 +4509,10 @@
       <c r="C45" s="16"/>
       <c r="D45" s="23"/>
       <c r="E45" s="17"/>
-      <c r="F45" s="43"/>
+      <c r="F45" s="73"/>
       <c r="G45" s="23"/>
-      <c r="H45" s="35"/>
-      <c r="I45" s="31"/>
+      <c r="H45" s="34"/>
+      <c r="I45" s="30"/>
       <c r="J45" s="8"/>
       <c r="K45" s="8"/>
       <c r="L45" s="8"/>
@@ -4517,8 +4523,8 @@
       <c r="Q45" s="8"/>
       <c r="R45" s="8"/>
       <c r="S45" s="8"/>
-      <c r="T45" s="33"/>
-      <c r="U45" s="33"/>
+      <c r="T45" s="32"/>
+      <c r="U45" s="32"/>
       <c r="V45" s="8"/>
       <c r="W45" s="8"/>
     </row>
@@ -4528,10 +4534,10 @@
       <c r="C46" s="16"/>
       <c r="D46" s="23"/>
       <c r="E46" s="17"/>
-      <c r="F46" s="43"/>
+      <c r="F46" s="73"/>
       <c r="G46" s="23"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="31"/>
+      <c r="H46" s="34"/>
+      <c r="I46" s="30"/>
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
       <c r="L46" s="8"/>
@@ -4542,8 +4548,8 @@
       <c r="Q46" s="8"/>
       <c r="R46" s="8"/>
       <c r="S46" s="8"/>
-      <c r="T46" s="33"/>
-      <c r="U46" s="33"/>
+      <c r="T46" s="32"/>
+      <c r="U46" s="32"/>
       <c r="V46" s="8"/>
       <c r="W46" s="8"/>
     </row>
@@ -4553,10 +4559,10 @@
       <c r="C47" s="16"/>
       <c r="D47" s="23"/>
       <c r="E47" s="17"/>
-      <c r="F47" s="43"/>
+      <c r="F47" s="73"/>
       <c r="G47" s="23"/>
-      <c r="H47" s="35"/>
-      <c r="I47" s="31"/>
+      <c r="H47" s="34"/>
+      <c r="I47" s="30"/>
       <c r="J47" s="8"/>
       <c r="K47" s="8"/>
       <c r="L47" s="8"/>
@@ -4567,8 +4573,8 @@
       <c r="Q47" s="8"/>
       <c r="R47" s="8"/>
       <c r="S47" s="8"/>
-      <c r="T47" s="33"/>
-      <c r="U47" s="33"/>
+      <c r="T47" s="32"/>
+      <c r="U47" s="32"/>
       <c r="V47" s="8"/>
       <c r="W47" s="8"/>
     </row>
@@ -4578,10 +4584,10 @@
       <c r="C48" s="16"/>
       <c r="D48" s="23"/>
       <c r="E48" s="17"/>
-      <c r="F48" s="43"/>
+      <c r="F48" s="73"/>
       <c r="G48" s="23"/>
-      <c r="H48" s="35"/>
-      <c r="I48" s="31"/>
+      <c r="H48" s="34"/>
+      <c r="I48" s="30"/>
       <c r="J48" s="8"/>
       <c r="K48" s="8"/>
       <c r="L48" s="8"/>
@@ -4592,8 +4598,8 @@
       <c r="Q48" s="8"/>
       <c r="R48" s="8"/>
       <c r="S48" s="8"/>
-      <c r="T48" s="33"/>
-      <c r="U48" s="33"/>
+      <c r="T48" s="32"/>
+      <c r="U48" s="32"/>
       <c r="V48" s="8"/>
       <c r="W48" s="8"/>
     </row>
@@ -4603,10 +4609,10 @@
       <c r="C49" s="16"/>
       <c r="D49" s="23"/>
       <c r="E49" s="17"/>
-      <c r="F49" s="43"/>
+      <c r="F49" s="73"/>
       <c r="G49" s="23"/>
-      <c r="H49" s="35"/>
-      <c r="I49" s="31"/>
+      <c r="H49" s="34"/>
+      <c r="I49" s="30"/>
       <c r="J49" s="8"/>
       <c r="K49" s="8"/>
       <c r="L49" s="8"/>
@@ -4617,8 +4623,8 @@
       <c r="Q49" s="8"/>
       <c r="R49" s="8"/>
       <c r="S49" s="8"/>
-      <c r="T49" s="33"/>
-      <c r="U49" s="33"/>
+      <c r="T49" s="32"/>
+      <c r="U49" s="32"/>
       <c r="V49" s="8"/>
       <c r="W49" s="8"/>
     </row>
@@ -4628,10 +4634,10 @@
       <c r="C50" s="16"/>
       <c r="D50" s="23"/>
       <c r="E50" s="17"/>
-      <c r="F50" s="43"/>
+      <c r="F50" s="73"/>
       <c r="G50" s="23"/>
-      <c r="H50" s="35"/>
-      <c r="I50" s="31"/>
+      <c r="H50" s="34"/>
+      <c r="I50" s="30"/>
       <c r="J50" s="8"/>
       <c r="K50" s="8"/>
       <c r="L50" s="8"/>
@@ -4642,8 +4648,8 @@
       <c r="Q50" s="8"/>
       <c r="R50" s="8"/>
       <c r="S50" s="8"/>
-      <c r="T50" s="33"/>
-      <c r="U50" s="33"/>
+      <c r="T50" s="32"/>
+      <c r="U50" s="32"/>
       <c r="V50" s="8"/>
       <c r="W50" s="8"/>
     </row>
@@ -4653,10 +4659,10 @@
       <c r="C51" s="16"/>
       <c r="D51" s="23"/>
       <c r="E51" s="17"/>
-      <c r="F51" s="43"/>
+      <c r="F51" s="73"/>
       <c r="G51" s="23"/>
-      <c r="H51" s="35"/>
-      <c r="I51" s="31"/>
+      <c r="H51" s="34"/>
+      <c r="I51" s="30"/>
       <c r="J51" s="8"/>
       <c r="K51" s="8"/>
       <c r="L51" s="8"/>
@@ -4667,8 +4673,8 @@
       <c r="Q51" s="8"/>
       <c r="R51" s="8"/>
       <c r="S51" s="8"/>
-      <c r="T51" s="33"/>
-      <c r="U51" s="33"/>
+      <c r="T51" s="32"/>
+      <c r="U51" s="32"/>
       <c r="V51" s="8"/>
       <c r="W51" s="8"/>
     </row>
@@ -4678,10 +4684,10 @@
       <c r="C52" s="16"/>
       <c r="D52" s="23"/>
       <c r="E52" s="17"/>
-      <c r="F52" s="43"/>
+      <c r="F52" s="73"/>
       <c r="G52" s="23"/>
-      <c r="H52" s="35"/>
-      <c r="I52" s="31"/>
+      <c r="H52" s="34"/>
+      <c r="I52" s="30"/>
       <c r="J52" s="8"/>
       <c r="K52" s="8"/>
       <c r="L52" s="8"/>
@@ -4692,8 +4698,8 @@
       <c r="Q52" s="8"/>
       <c r="R52" s="8"/>
       <c r="S52" s="8"/>
-      <c r="T52" s="33"/>
-      <c r="U52" s="33"/>
+      <c r="T52" s="32"/>
+      <c r="U52" s="32"/>
       <c r="V52" s="8"/>
       <c r="W52" s="8"/>
     </row>
@@ -4703,10 +4709,10 @@
       <c r="C53" s="16"/>
       <c r="D53" s="23"/>
       <c r="E53" s="17"/>
-      <c r="F53" s="43"/>
+      <c r="F53" s="73"/>
       <c r="G53" s="23"/>
-      <c r="H53" s="35"/>
-      <c r="I53" s="31"/>
+      <c r="H53" s="34"/>
+      <c r="I53" s="30"/>
       <c r="J53" s="8"/>
       <c r="K53" s="8"/>
       <c r="L53" s="8"/>
@@ -4717,8 +4723,8 @@
       <c r="Q53" s="8"/>
       <c r="R53" s="8"/>
       <c r="S53" s="8"/>
-      <c r="T53" s="33"/>
-      <c r="U53" s="33"/>
+      <c r="T53" s="32"/>
+      <c r="U53" s="32"/>
       <c r="V53" s="8"/>
       <c r="W53" s="8"/>
     </row>
@@ -4728,10 +4734,10 @@
       <c r="C54" s="16"/>
       <c r="D54" s="23"/>
       <c r="E54" s="17"/>
-      <c r="F54" s="43"/>
+      <c r="F54" s="73"/>
       <c r="G54" s="23"/>
-      <c r="H54" s="35"/>
-      <c r="I54" s="31"/>
+      <c r="H54" s="34"/>
+      <c r="I54" s="30"/>
       <c r="J54" s="8"/>
       <c r="K54" s="8"/>
       <c r="L54" s="8"/>
@@ -4742,8 +4748,8 @@
       <c r="Q54" s="8"/>
       <c r="R54" s="8"/>
       <c r="S54" s="8"/>
-      <c r="T54" s="33"/>
-      <c r="U54" s="33"/>
+      <c r="T54" s="32"/>
+      <c r="U54" s="32"/>
       <c r="V54" s="8"/>
       <c r="W54" s="8"/>
     </row>
@@ -4753,10 +4759,10 @@
       <c r="C55" s="16"/>
       <c r="D55" s="23"/>
       <c r="E55" s="17"/>
-      <c r="F55" s="43"/>
+      <c r="F55" s="73"/>
       <c r="G55" s="23"/>
-      <c r="H55" s="35"/>
-      <c r="I55" s="31"/>
+      <c r="H55" s="34"/>
+      <c r="I55" s="30"/>
       <c r="J55" s="8"/>
       <c r="K55" s="8"/>
       <c r="L55" s="8"/>
@@ -4767,8 +4773,8 @@
       <c r="Q55" s="8"/>
       <c r="R55" s="8"/>
       <c r="S55" s="8"/>
-      <c r="T55" s="33"/>
-      <c r="U55" s="33"/>
+      <c r="T55" s="32"/>
+      <c r="U55" s="32"/>
       <c r="V55" s="8"/>
       <c r="W55" s="8"/>
     </row>
@@ -4778,10 +4784,10 @@
       <c r="C56" s="16"/>
       <c r="D56" s="23"/>
       <c r="E56" s="17"/>
-      <c r="F56" s="43"/>
+      <c r="F56" s="73"/>
       <c r="G56" s="23"/>
-      <c r="H56" s="35"/>
-      <c r="I56" s="31"/>
+      <c r="H56" s="34"/>
+      <c r="I56" s="30"/>
       <c r="J56" s="8"/>
       <c r="K56" s="8"/>
       <c r="L56" s="8"/>
@@ -4792,8 +4798,8 @@
       <c r="Q56" s="8"/>
       <c r="R56" s="8"/>
       <c r="S56" s="8"/>
-      <c r="T56" s="33"/>
-      <c r="U56" s="33"/>
+      <c r="T56" s="32"/>
+      <c r="U56" s="32"/>
       <c r="V56" s="8"/>
       <c r="W56" s="8"/>
     </row>
@@ -4803,10 +4809,10 @@
       <c r="C57" s="16"/>
       <c r="D57" s="23"/>
       <c r="E57" s="17"/>
-      <c r="F57" s="43"/>
+      <c r="F57" s="73"/>
       <c r="G57" s="23"/>
-      <c r="H57" s="35"/>
-      <c r="I57" s="31"/>
+      <c r="H57" s="34"/>
+      <c r="I57" s="30"/>
       <c r="J57" s="8"/>
       <c r="K57" s="8"/>
       <c r="L57" s="8"/>
@@ -4817,8 +4823,8 @@
       <c r="Q57" s="8"/>
       <c r="R57" s="8"/>
       <c r="S57" s="8"/>
-      <c r="T57" s="33"/>
-      <c r="U57" s="33"/>
+      <c r="T57" s="32"/>
+      <c r="U57" s="32"/>
       <c r="V57" s="8"/>
       <c r="W57" s="8"/>
     </row>
@@ -4828,10 +4834,10 @@
       <c r="C58" s="16"/>
       <c r="D58" s="23"/>
       <c r="E58" s="17"/>
-      <c r="F58" s="43"/>
+      <c r="F58" s="73"/>
       <c r="G58" s="23"/>
-      <c r="H58" s="35"/>
-      <c r="I58" s="31"/>
+      <c r="H58" s="34"/>
+      <c r="I58" s="30"/>
       <c r="J58" s="8"/>
       <c r="K58" s="8"/>
       <c r="L58" s="8"/>
@@ -4842,8 +4848,8 @@
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
       <c r="S58" s="8"/>
-      <c r="T58" s="33"/>
-      <c r="U58" s="33"/>
+      <c r="T58" s="32"/>
+      <c r="U58" s="32"/>
       <c r="V58" s="8"/>
       <c r="W58" s="8"/>
     </row>
@@ -4853,10 +4859,10 @@
       <c r="C59" s="16"/>
       <c r="D59" s="23"/>
       <c r="E59" s="17"/>
-      <c r="F59" s="43"/>
+      <c r="F59" s="73"/>
       <c r="G59" s="23"/>
-      <c r="H59" s="35"/>
-      <c r="I59" s="31"/>
+      <c r="H59" s="34"/>
+      <c r="I59" s="30"/>
       <c r="J59" s="8"/>
       <c r="K59" s="8"/>
       <c r="L59" s="8"/>
@@ -4867,8 +4873,8 @@
       <c r="Q59" s="8"/>
       <c r="R59" s="8"/>
       <c r="S59" s="8"/>
-      <c r="T59" s="33"/>
-      <c r="U59" s="33"/>
+      <c r="T59" s="32"/>
+      <c r="U59" s="32"/>
       <c r="V59" s="8"/>
       <c r="W59" s="8"/>
     </row>
@@ -4878,10 +4884,10 @@
       <c r="C60" s="16"/>
       <c r="D60" s="23"/>
       <c r="E60" s="17"/>
-      <c r="F60" s="43"/>
+      <c r="F60" s="73"/>
       <c r="G60" s="23"/>
-      <c r="H60" s="35"/>
-      <c r="I60" s="31"/>
+      <c r="H60" s="34"/>
+      <c r="I60" s="30"/>
       <c r="J60" s="8"/>
       <c r="K60" s="8"/>
       <c r="L60" s="8"/>
@@ -4892,8 +4898,8 @@
       <c r="Q60" s="8"/>
       <c r="R60" s="8"/>
       <c r="S60" s="8"/>
-      <c r="T60" s="33"/>
-      <c r="U60" s="33"/>
+      <c r="T60" s="32"/>
+      <c r="U60" s="32"/>
       <c r="V60" s="8"/>
       <c r="W60" s="8"/>
     </row>
@@ -4903,10 +4909,10 @@
       <c r="C61" s="16"/>
       <c r="D61" s="23"/>
       <c r="E61" s="17"/>
-      <c r="F61" s="43"/>
+      <c r="F61" s="73"/>
       <c r="G61" s="23"/>
-      <c r="H61" s="35"/>
-      <c r="I61" s="31"/>
+      <c r="H61" s="34"/>
+      <c r="I61" s="30"/>
       <c r="J61" s="8"/>
       <c r="K61" s="8"/>
       <c r="L61" s="8"/>
@@ -4917,8 +4923,8 @@
       <c r="Q61" s="8"/>
       <c r="R61" s="8"/>
       <c r="S61" s="8"/>
-      <c r="T61" s="33"/>
-      <c r="U61" s="33"/>
+      <c r="T61" s="32"/>
+      <c r="U61" s="32"/>
       <c r="V61" s="8"/>
       <c r="W61" s="8"/>
     </row>
@@ -4928,10 +4934,10 @@
       <c r="C62" s="16"/>
       <c r="D62" s="23"/>
       <c r="E62" s="17"/>
-      <c r="F62" s="43"/>
+      <c r="F62" s="73"/>
       <c r="G62" s="23"/>
-      <c r="H62" s="35"/>
-      <c r="I62" s="31"/>
+      <c r="H62" s="34"/>
+      <c r="I62" s="30"/>
       <c r="J62" s="8"/>
       <c r="K62" s="8"/>
       <c r="L62" s="8"/>
@@ -4942,8 +4948,8 @@
       <c r="Q62" s="8"/>
       <c r="R62" s="8"/>
       <c r="S62" s="8"/>
-      <c r="T62" s="33"/>
-      <c r="U62" s="33"/>
+      <c r="T62" s="32"/>
+      <c r="U62" s="32"/>
       <c r="V62" s="8"/>
       <c r="W62" s="8"/>
     </row>
@@ -4953,10 +4959,10 @@
       <c r="C63" s="16"/>
       <c r="D63" s="23"/>
       <c r="E63" s="17"/>
-      <c r="F63" s="43"/>
+      <c r="F63" s="73"/>
       <c r="G63" s="23"/>
-      <c r="H63" s="35"/>
-      <c r="I63" s="31"/>
+      <c r="H63" s="34"/>
+      <c r="I63" s="30"/>
       <c r="J63" s="8"/>
       <c r="K63" s="8"/>
       <c r="L63" s="8"/>
@@ -4967,8 +4973,8 @@
       <c r="Q63" s="8"/>
       <c r="R63" s="8"/>
       <c r="S63" s="8"/>
-      <c r="T63" s="33"/>
-      <c r="U63" s="33"/>
+      <c r="T63" s="32"/>
+      <c r="U63" s="32"/>
       <c r="V63" s="8"/>
       <c r="W63" s="8"/>
     </row>
@@ -4978,10 +4984,10 @@
       <c r="C64" s="16"/>
       <c r="D64" s="23"/>
       <c r="E64" s="17"/>
-      <c r="F64" s="43"/>
+      <c r="F64" s="73"/>
       <c r="G64" s="23"/>
-      <c r="H64" s="35"/>
-      <c r="I64" s="31"/>
+      <c r="H64" s="34"/>
+      <c r="I64" s="30"/>
       <c r="J64" s="8"/>
       <c r="K64" s="8"/>
       <c r="L64" s="8"/>
@@ -4992,8 +4998,8 @@
       <c r="Q64" s="8"/>
       <c r="R64" s="8"/>
       <c r="S64" s="8"/>
-      <c r="T64" s="33"/>
-      <c r="U64" s="33"/>
+      <c r="T64" s="32"/>
+      <c r="U64" s="32"/>
       <c r="V64" s="8"/>
       <c r="W64" s="8"/>
     </row>
@@ -5003,10 +5009,10 @@
       <c r="C65" s="16"/>
       <c r="D65" s="23"/>
       <c r="E65" s="17"/>
-      <c r="F65" s="43"/>
+      <c r="F65" s="73"/>
       <c r="G65" s="23"/>
-      <c r="H65" s="35"/>
-      <c r="I65" s="31"/>
+      <c r="H65" s="34"/>
+      <c r="I65" s="30"/>
       <c r="J65" s="8"/>
       <c r="K65" s="8"/>
       <c r="L65" s="8"/>
@@ -5017,8 +5023,8 @@
       <c r="Q65" s="8"/>
       <c r="R65" s="8"/>
       <c r="S65" s="8"/>
-      <c r="T65" s="33"/>
-      <c r="U65" s="33"/>
+      <c r="T65" s="32"/>
+      <c r="U65" s="32"/>
       <c r="V65" s="8"/>
       <c r="W65" s="8"/>
     </row>
@@ -5028,10 +5034,10 @@
       <c r="C66" s="16"/>
       <c r="D66" s="23"/>
       <c r="E66" s="17"/>
-      <c r="F66" s="43"/>
+      <c r="F66" s="73"/>
       <c r="G66" s="23"/>
-      <c r="H66" s="35"/>
-      <c r="I66" s="31"/>
+      <c r="H66" s="34"/>
+      <c r="I66" s="30"/>
       <c r="J66" s="8"/>
       <c r="K66" s="8"/>
       <c r="L66" s="8"/>
@@ -5042,8 +5048,8 @@
       <c r="Q66" s="8"/>
       <c r="R66" s="8"/>
       <c r="S66" s="8"/>
-      <c r="T66" s="33"/>
-      <c r="U66" s="33"/>
+      <c r="T66" s="32"/>
+      <c r="U66" s="32"/>
       <c r="V66" s="8"/>
       <c r="W66" s="8"/>
     </row>
@@ -5053,10 +5059,10 @@
       <c r="C67" s="16"/>
       <c r="D67" s="23"/>
       <c r="E67" s="17"/>
-      <c r="F67" s="43"/>
+      <c r="F67" s="73"/>
       <c r="G67" s="23"/>
-      <c r="H67" s="35"/>
-      <c r="I67" s="31"/>
+      <c r="H67" s="34"/>
+      <c r="I67" s="30"/>
       <c r="J67" s="8"/>
       <c r="K67" s="8"/>
       <c r="L67" s="8"/>
@@ -5067,8 +5073,8 @@
       <c r="Q67" s="8"/>
       <c r="R67" s="8"/>
       <c r="S67" s="8"/>
-      <c r="T67" s="33"/>
-      <c r="U67" s="33"/>
+      <c r="T67" s="32"/>
+      <c r="U67" s="32"/>
       <c r="V67" s="8"/>
       <c r="W67" s="8"/>
     </row>
@@ -5078,10 +5084,10 @@
       <c r="C68" s="16"/>
       <c r="D68" s="23"/>
       <c r="E68" s="17"/>
-      <c r="F68" s="43"/>
+      <c r="F68" s="73"/>
       <c r="G68" s="23"/>
-      <c r="H68" s="35"/>
-      <c r="I68" s="31"/>
+      <c r="H68" s="34"/>
+      <c r="I68" s="30"/>
       <c r="J68" s="8"/>
       <c r="K68" s="8"/>
       <c r="L68" s="8"/>
@@ -5092,8 +5098,8 @@
       <c r="Q68" s="8"/>
       <c r="R68" s="8"/>
       <c r="S68" s="8"/>
-      <c r="T68" s="33"/>
-      <c r="U68" s="33"/>
+      <c r="T68" s="32"/>
+      <c r="U68" s="32"/>
       <c r="V68" s="8"/>
       <c r="W68" s="8"/>
     </row>
@@ -5103,10 +5109,10 @@
       <c r="C69" s="16"/>
       <c r="D69" s="23"/>
       <c r="E69" s="17"/>
-      <c r="F69" s="43"/>
+      <c r="F69" s="73"/>
       <c r="G69" s="23"/>
-      <c r="H69" s="35"/>
-      <c r="I69" s="31"/>
+      <c r="H69" s="34"/>
+      <c r="I69" s="30"/>
       <c r="J69" s="8"/>
       <c r="K69" s="8"/>
       <c r="L69" s="8"/>
@@ -5117,8 +5123,8 @@
       <c r="Q69" s="8"/>
       <c r="R69" s="8"/>
       <c r="S69" s="8"/>
-      <c r="T69" s="33"/>
-      <c r="U69" s="33"/>
+      <c r="T69" s="32"/>
+      <c r="U69" s="32"/>
       <c r="V69" s="8"/>
       <c r="W69" s="8"/>
     </row>
@@ -5128,10 +5134,10 @@
       <c r="C70" s="16"/>
       <c r="D70" s="23"/>
       <c r="E70" s="17"/>
-      <c r="F70" s="43"/>
+      <c r="F70" s="73"/>
       <c r="G70" s="23"/>
-      <c r="H70" s="35"/>
-      <c r="I70" s="31"/>
+      <c r="H70" s="34"/>
+      <c r="I70" s="30"/>
       <c r="J70" s="8"/>
       <c r="K70" s="8"/>
       <c r="L70" s="8"/>
@@ -5142,8 +5148,8 @@
       <c r="Q70" s="8"/>
       <c r="R70" s="8"/>
       <c r="S70" s="8"/>
-      <c r="T70" s="33"/>
-      <c r="U70" s="33"/>
+      <c r="T70" s="32"/>
+      <c r="U70" s="32"/>
       <c r="V70" s="8"/>
       <c r="W70" s="8"/>
     </row>
@@ -5153,10 +5159,10 @@
       <c r="C71" s="16"/>
       <c r="D71" s="23"/>
       <c r="E71" s="17"/>
-      <c r="F71" s="43"/>
+      <c r="F71" s="73"/>
       <c r="G71" s="23"/>
-      <c r="H71" s="35"/>
-      <c r="I71" s="31"/>
+      <c r="H71" s="34"/>
+      <c r="I71" s="30"/>
       <c r="J71" s="8"/>
       <c r="K71" s="8"/>
       <c r="L71" s="8"/>
@@ -5167,8 +5173,8 @@
       <c r="Q71" s="8"/>
       <c r="R71" s="8"/>
       <c r="S71" s="8"/>
-      <c r="T71" s="33"/>
-      <c r="U71" s="33"/>
+      <c r="T71" s="32"/>
+      <c r="U71" s="32"/>
       <c r="V71" s="8"/>
       <c r="W71" s="8"/>
     </row>
@@ -5178,10 +5184,10 @@
       <c r="C72" s="16"/>
       <c r="D72" s="23"/>
       <c r="E72" s="17"/>
-      <c r="F72" s="43"/>
+      <c r="F72" s="73"/>
       <c r="G72" s="23"/>
-      <c r="H72" s="35"/>
-      <c r="I72" s="31"/>
+      <c r="H72" s="34"/>
+      <c r="I72" s="30"/>
       <c r="J72" s="8"/>
       <c r="K72" s="8"/>
       <c r="L72" s="8"/>
@@ -5192,8 +5198,8 @@
       <c r="Q72" s="8"/>
       <c r="R72" s="8"/>
       <c r="S72" s="8"/>
-      <c r="T72" s="33"/>
-      <c r="U72" s="33"/>
+      <c r="T72" s="32"/>
+      <c r="U72" s="32"/>
       <c r="V72" s="8"/>
       <c r="W72" s="8"/>
     </row>
@@ -5203,10 +5209,10 @@
       <c r="C73" s="16"/>
       <c r="D73" s="23"/>
       <c r="E73" s="17"/>
-      <c r="F73" s="43"/>
+      <c r="F73" s="73"/>
       <c r="G73" s="23"/>
-      <c r="H73" s="35"/>
-      <c r="I73" s="31"/>
+      <c r="H73" s="34"/>
+      <c r="I73" s="30"/>
       <c r="J73" s="8"/>
       <c r="K73" s="8"/>
       <c r="L73" s="8"/>
@@ -5217,8 +5223,8 @@
       <c r="Q73" s="8"/>
       <c r="R73" s="8"/>
       <c r="S73" s="8"/>
-      <c r="T73" s="33"/>
-      <c r="U73" s="33"/>
+      <c r="T73" s="32"/>
+      <c r="U73" s="32"/>
       <c r="V73" s="8"/>
       <c r="W73" s="8"/>
     </row>
@@ -5228,10 +5234,10 @@
       <c r="C74" s="16"/>
       <c r="D74" s="23"/>
       <c r="E74" s="17"/>
-      <c r="F74" s="43"/>
+      <c r="F74" s="73"/>
       <c r="G74" s="23"/>
-      <c r="H74" s="35"/>
-      <c r="I74" s="31"/>
+      <c r="H74" s="34"/>
+      <c r="I74" s="30"/>
       <c r="J74" s="8"/>
       <c r="K74" s="8"/>
       <c r="L74" s="8"/>
@@ -5242,8 +5248,8 @@
       <c r="Q74" s="8"/>
       <c r="R74" s="8"/>
       <c r="S74" s="8"/>
-      <c r="T74" s="33"/>
-      <c r="U74" s="33"/>
+      <c r="T74" s="32"/>
+      <c r="U74" s="32"/>
       <c r="V74" s="8"/>
       <c r="W74" s="8"/>
     </row>
@@ -5253,10 +5259,10 @@
       <c r="C75" s="16"/>
       <c r="D75" s="23"/>
       <c r="E75" s="17"/>
-      <c r="F75" s="43"/>
+      <c r="F75" s="73"/>
       <c r="G75" s="23"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="31"/>
+      <c r="H75" s="34"/>
+      <c r="I75" s="30"/>
       <c r="J75" s="8"/>
       <c r="K75" s="8"/>
       <c r="L75" s="8"/>
@@ -5267,8 +5273,8 @@
       <c r="Q75" s="8"/>
       <c r="R75" s="8"/>
       <c r="S75" s="8"/>
-      <c r="T75" s="33"/>
-      <c r="U75" s="33"/>
+      <c r="T75" s="32"/>
+      <c r="U75" s="32"/>
       <c r="V75" s="8"/>
       <c r="W75" s="8"/>
     </row>
@@ -5278,10 +5284,10 @@
       <c r="C76" s="16"/>
       <c r="D76" s="23"/>
       <c r="E76" s="17"/>
-      <c r="F76" s="43"/>
+      <c r="F76" s="73"/>
       <c r="G76" s="23"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="31"/>
+      <c r="H76" s="34"/>
+      <c r="I76" s="30"/>
       <c r="J76" s="8"/>
       <c r="K76" s="8"/>
       <c r="L76" s="8"/>
@@ -5292,8 +5298,8 @@
       <c r="Q76" s="8"/>
       <c r="R76" s="8"/>
       <c r="S76" s="8"/>
-      <c r="T76" s="33"/>
-      <c r="U76" s="33"/>
+      <c r="T76" s="32"/>
+      <c r="U76" s="32"/>
       <c r="V76" s="8"/>
       <c r="W76" s="8"/>
     </row>
@@ -5303,10 +5309,10 @@
       <c r="C77" s="16"/>
       <c r="D77" s="23"/>
       <c r="E77" s="17"/>
-      <c r="F77" s="43"/>
+      <c r="F77" s="73"/>
       <c r="G77" s="23"/>
-      <c r="H77" s="35"/>
-      <c r="I77" s="31"/>
+      <c r="H77" s="34"/>
+      <c r="I77" s="30"/>
       <c r="J77" s="8"/>
       <c r="K77" s="8"/>
       <c r="L77" s="8"/>
@@ -5317,8 +5323,8 @@
       <c r="Q77" s="8"/>
       <c r="R77" s="8"/>
       <c r="S77" s="8"/>
-      <c r="T77" s="33"/>
-      <c r="U77" s="33"/>
+      <c r="T77" s="32"/>
+      <c r="U77" s="32"/>
       <c r="V77" s="8"/>
       <c r="W77" s="8"/>
     </row>
@@ -5328,10 +5334,10 @@
       <c r="C78" s="16"/>
       <c r="D78" s="23"/>
       <c r="E78" s="17"/>
-      <c r="F78" s="43"/>
+      <c r="F78" s="73"/>
       <c r="G78" s="23"/>
-      <c r="H78" s="35"/>
-      <c r="I78" s="31"/>
+      <c r="H78" s="34"/>
+      <c r="I78" s="30"/>
       <c r="J78" s="8"/>
       <c r="K78" s="8"/>
       <c r="L78" s="8"/>
@@ -5342,8 +5348,8 @@
       <c r="Q78" s="8"/>
       <c r="R78" s="8"/>
       <c r="S78" s="8"/>
-      <c r="T78" s="33"/>
-      <c r="U78" s="33"/>
+      <c r="T78" s="32"/>
+      <c r="U78" s="32"/>
       <c r="V78" s="8"/>
       <c r="W78" s="8"/>
     </row>
@@ -5353,10 +5359,10 @@
       <c r="C79" s="16"/>
       <c r="D79" s="23"/>
       <c r="E79" s="17"/>
-      <c r="F79" s="43"/>
+      <c r="F79" s="73"/>
       <c r="G79" s="23"/>
-      <c r="H79" s="35"/>
-      <c r="I79" s="31"/>
+      <c r="H79" s="34"/>
+      <c r="I79" s="30"/>
       <c r="J79" s="8"/>
       <c r="K79" s="8"/>
       <c r="L79" s="8"/>
@@ -5367,8 +5373,8 @@
       <c r="Q79" s="8"/>
       <c r="R79" s="8"/>
       <c r="S79" s="8"/>
-      <c r="T79" s="33"/>
-      <c r="U79" s="33"/>
+      <c r="T79" s="32"/>
+      <c r="U79" s="32"/>
       <c r="V79" s="8"/>
       <c r="W79" s="8"/>
     </row>
@@ -5378,10 +5384,10 @@
       <c r="C80" s="16"/>
       <c r="D80" s="23"/>
       <c r="E80" s="17"/>
-      <c r="F80" s="43"/>
+      <c r="F80" s="73"/>
       <c r="G80" s="23"/>
-      <c r="H80" s="35"/>
-      <c r="I80" s="31"/>
+      <c r="H80" s="34"/>
+      <c r="I80" s="30"/>
       <c r="J80" s="8"/>
       <c r="K80" s="8"/>
       <c r="L80" s="8"/>
@@ -5392,8 +5398,8 @@
       <c r="Q80" s="8"/>
       <c r="R80" s="8"/>
       <c r="S80" s="8"/>
-      <c r="T80" s="33"/>
-      <c r="U80" s="33"/>
+      <c r="T80" s="32"/>
+      <c r="U80" s="32"/>
       <c r="V80" s="8"/>
       <c r="W80" s="8"/>
     </row>
@@ -5403,10 +5409,10 @@
       <c r="C81" s="16"/>
       <c r="D81" s="23"/>
       <c r="E81" s="17"/>
-      <c r="F81" s="43"/>
+      <c r="F81" s="73"/>
       <c r="G81" s="23"/>
-      <c r="H81" s="35"/>
-      <c r="I81" s="31"/>
+      <c r="H81" s="34"/>
+      <c r="I81" s="30"/>
       <c r="J81" s="8"/>
       <c r="K81" s="8"/>
       <c r="L81" s="8"/>
@@ -5417,8 +5423,8 @@
       <c r="Q81" s="8"/>
       <c r="R81" s="8"/>
       <c r="S81" s="8"/>
-      <c r="T81" s="33"/>
-      <c r="U81" s="33"/>
+      <c r="T81" s="32"/>
+      <c r="U81" s="32"/>
       <c r="V81" s="8"/>
       <c r="W81" s="8"/>
     </row>
@@ -5428,10 +5434,10 @@
       <c r="C82" s="16"/>
       <c r="D82" s="23"/>
       <c r="E82" s="17"/>
-      <c r="F82" s="43"/>
+      <c r="F82" s="73"/>
       <c r="G82" s="23"/>
-      <c r="H82" s="35"/>
-      <c r="I82" s="31"/>
+      <c r="H82" s="34"/>
+      <c r="I82" s="30"/>
       <c r="J82" s="8"/>
       <c r="K82" s="8"/>
       <c r="L82" s="8"/>
@@ -5442,8 +5448,8 @@
       <c r="Q82" s="8"/>
       <c r="R82" s="8"/>
       <c r="S82" s="8"/>
-      <c r="T82" s="33"/>
-      <c r="U82" s="33"/>
+      <c r="T82" s="32"/>
+      <c r="U82" s="32"/>
       <c r="V82" s="8"/>
       <c r="W82" s="8"/>
     </row>
@@ -5453,10 +5459,10 @@
       <c r="C83" s="16"/>
       <c r="D83" s="23"/>
       <c r="E83" s="17"/>
-      <c r="F83" s="43"/>
+      <c r="F83" s="73"/>
       <c r="G83" s="23"/>
-      <c r="H83" s="35"/>
-      <c r="I83" s="31"/>
+      <c r="H83" s="34"/>
+      <c r="I83" s="30"/>
       <c r="J83" s="8"/>
       <c r="K83" s="8"/>
       <c r="L83" s="8"/>
@@ -5467,8 +5473,8 @@
       <c r="Q83" s="8"/>
       <c r="R83" s="8"/>
       <c r="S83" s="8"/>
-      <c r="T83" s="33"/>
-      <c r="U83" s="33"/>
+      <c r="T83" s="32"/>
+      <c r="U83" s="32"/>
       <c r="V83" s="8"/>
       <c r="W83" s="8"/>
     </row>
@@ -5478,10 +5484,10 @@
       <c r="C84" s="16"/>
       <c r="D84" s="23"/>
       <c r="E84" s="17"/>
-      <c r="F84" s="43"/>
+      <c r="F84" s="73"/>
       <c r="G84" s="23"/>
-      <c r="H84" s="35"/>
-      <c r="I84" s="31"/>
+      <c r="H84" s="34"/>
+      <c r="I84" s="30"/>
       <c r="J84" s="8"/>
       <c r="K84" s="8"/>
       <c r="L84" s="8"/>
@@ -5492,8 +5498,8 @@
       <c r="Q84" s="8"/>
       <c r="R84" s="8"/>
       <c r="S84" s="8"/>
-      <c r="T84" s="33"/>
-      <c r="U84" s="33"/>
+      <c r="T84" s="32"/>
+      <c r="U84" s="32"/>
       <c r="V84" s="8"/>
       <c r="W84" s="8"/>
     </row>
@@ -5503,10 +5509,10 @@
       <c r="C85" s="16"/>
       <c r="D85" s="23"/>
       <c r="E85" s="17"/>
-      <c r="F85" s="43"/>
+      <c r="F85" s="73"/>
       <c r="G85" s="23"/>
-      <c r="H85" s="35"/>
-      <c r="I85" s="31"/>
+      <c r="H85" s="34"/>
+      <c r="I85" s="30"/>
       <c r="J85" s="8"/>
       <c r="K85" s="8"/>
       <c r="L85" s="8"/>
@@ -5517,8 +5523,8 @@
       <c r="Q85" s="8"/>
       <c r="R85" s="8"/>
       <c r="S85" s="8"/>
-      <c r="T85" s="33"/>
-      <c r="U85" s="33"/>
+      <c r="T85" s="32"/>
+      <c r="U85" s="32"/>
       <c r="V85" s="8"/>
       <c r="W85" s="8"/>
     </row>
@@ -5528,10 +5534,10 @@
       <c r="C86" s="16"/>
       <c r="D86" s="23"/>
       <c r="E86" s="17"/>
-      <c r="F86" s="43"/>
+      <c r="F86" s="73"/>
       <c r="G86" s="23"/>
-      <c r="H86" s="35"/>
-      <c r="I86" s="31"/>
+      <c r="H86" s="34"/>
+      <c r="I86" s="30"/>
       <c r="J86" s="8"/>
       <c r="K86" s="8"/>
       <c r="L86" s="8"/>
@@ -5542,8 +5548,8 @@
       <c r="Q86" s="8"/>
       <c r="R86" s="8"/>
       <c r="S86" s="8"/>
-      <c r="T86" s="33"/>
-      <c r="U86" s="33"/>
+      <c r="T86" s="32"/>
+      <c r="U86" s="32"/>
       <c r="V86" s="8"/>
       <c r="W86" s="8"/>
     </row>
@@ -5553,10 +5559,10 @@
       <c r="C87" s="16"/>
       <c r="D87" s="23"/>
       <c r="E87" s="17"/>
-      <c r="F87" s="43"/>
+      <c r="F87" s="73"/>
       <c r="G87" s="23"/>
-      <c r="H87" s="35"/>
-      <c r="I87" s="31"/>
+      <c r="H87" s="34"/>
+      <c r="I87" s="30"/>
       <c r="J87" s="8"/>
       <c r="K87" s="8"/>
       <c r="L87" s="8"/>
@@ -5567,8 +5573,8 @@
       <c r="Q87" s="8"/>
       <c r="R87" s="8"/>
       <c r="S87" s="8"/>
-      <c r="T87" s="33"/>
-      <c r="U87" s="33"/>
+      <c r="T87" s="32"/>
+      <c r="U87" s="32"/>
       <c r="V87" s="8"/>
       <c r="W87" s="8"/>
     </row>
@@ -5578,10 +5584,10 @@
       <c r="C88" s="16"/>
       <c r="D88" s="23"/>
       <c r="E88" s="17"/>
-      <c r="F88" s="43"/>
+      <c r="F88" s="73"/>
       <c r="G88" s="23"/>
-      <c r="H88" s="35"/>
-      <c r="I88" s="31"/>
+      <c r="H88" s="34"/>
+      <c r="I88" s="30"/>
       <c r="J88" s="8"/>
       <c r="K88" s="8"/>
       <c r="L88" s="8"/>
@@ -5592,8 +5598,8 @@
       <c r="Q88" s="8"/>
       <c r="R88" s="8"/>
       <c r="S88" s="8"/>
-      <c r="T88" s="33"/>
-      <c r="U88" s="33"/>
+      <c r="T88" s="32"/>
+      <c r="U88" s="32"/>
       <c r="V88" s="8"/>
       <c r="W88" s="8"/>
     </row>
@@ -5603,10 +5609,10 @@
       <c r="C89" s="16"/>
       <c r="D89" s="23"/>
       <c r="E89" s="17"/>
-      <c r="F89" s="43"/>
+      <c r="F89" s="73"/>
       <c r="G89" s="23"/>
-      <c r="H89" s="35"/>
-      <c r="I89" s="31"/>
+      <c r="H89" s="34"/>
+      <c r="I89" s="30"/>
       <c r="J89" s="8"/>
       <c r="K89" s="8"/>
       <c r="L89" s="8"/>
@@ -5617,8 +5623,8 @@
       <c r="Q89" s="8"/>
       <c r="R89" s="8"/>
       <c r="S89" s="8"/>
-      <c r="T89" s="33"/>
-      <c r="U89" s="33"/>
+      <c r="T89" s="32"/>
+      <c r="U89" s="32"/>
       <c r="V89" s="8"/>
       <c r="W89" s="8"/>
     </row>
@@ -5628,10 +5634,10 @@
       <c r="C90" s="16"/>
       <c r="D90" s="23"/>
       <c r="E90" s="17"/>
-      <c r="F90" s="43"/>
+      <c r="F90" s="73"/>
       <c r="G90" s="23"/>
-      <c r="H90" s="35"/>
-      <c r="I90" s="31"/>
+      <c r="H90" s="34"/>
+      <c r="I90" s="30"/>
       <c r="J90" s="8"/>
       <c r="K90" s="8"/>
       <c r="L90" s="8"/>
@@ -5642,8 +5648,8 @@
       <c r="Q90" s="8"/>
       <c r="R90" s="8"/>
       <c r="S90" s="8"/>
-      <c r="T90" s="33"/>
-      <c r="U90" s="33"/>
+      <c r="T90" s="32"/>
+      <c r="U90" s="32"/>
       <c r="V90" s="8"/>
       <c r="W90" s="8"/>
     </row>
@@ -5653,10 +5659,10 @@
       <c r="C91" s="16"/>
       <c r="D91" s="23"/>
       <c r="E91" s="17"/>
-      <c r="F91" s="43"/>
+      <c r="F91" s="73"/>
       <c r="G91" s="23"/>
-      <c r="H91" s="35"/>
-      <c r="I91" s="31"/>
+      <c r="H91" s="34"/>
+      <c r="I91" s="30"/>
       <c r="J91" s="8"/>
       <c r="K91" s="8"/>
       <c r="L91" s="8"/>
@@ -5667,8 +5673,8 @@
       <c r="Q91" s="8"/>
       <c r="R91" s="8"/>
       <c r="S91" s="8"/>
-      <c r="T91" s="33"/>
-      <c r="U91" s="33"/>
+      <c r="T91" s="32"/>
+      <c r="U91" s="32"/>
       <c r="V91" s="8"/>
       <c r="W91" s="8"/>
     </row>
@@ -5678,10 +5684,10 @@
       <c r="C92" s="16"/>
       <c r="D92" s="23"/>
       <c r="E92" s="17"/>
-      <c r="F92" s="43"/>
+      <c r="F92" s="73"/>
       <c r="G92" s="23"/>
-      <c r="H92" s="35"/>
-      <c r="I92" s="31"/>
+      <c r="H92" s="34"/>
+      <c r="I92" s="30"/>
       <c r="J92" s="8"/>
       <c r="K92" s="8"/>
       <c r="L92" s="8"/>
@@ -5692,8 +5698,8 @@
       <c r="Q92" s="8"/>
       <c r="R92" s="8"/>
       <c r="S92" s="8"/>
-      <c r="T92" s="33"/>
-      <c r="U92" s="33"/>
+      <c r="T92" s="32"/>
+      <c r="U92" s="32"/>
       <c r="V92" s="8"/>
       <c r="W92" s="8"/>
     </row>
@@ -5703,10 +5709,10 @@
       <c r="C93" s="16"/>
       <c r="D93" s="23"/>
       <c r="E93" s="17"/>
-      <c r="F93" s="43"/>
+      <c r="F93" s="73"/>
       <c r="G93" s="23"/>
-      <c r="H93" s="35"/>
-      <c r="I93" s="31"/>
+      <c r="H93" s="34"/>
+      <c r="I93" s="30"/>
       <c r="J93" s="8"/>
       <c r="K93" s="8"/>
       <c r="L93" s="8"/>
@@ -5717,8 +5723,8 @@
       <c r="Q93" s="8"/>
       <c r="R93" s="8"/>
       <c r="S93" s="8"/>
-      <c r="T93" s="33"/>
-      <c r="U93" s="33"/>
+      <c r="T93" s="32"/>
+      <c r="U93" s="32"/>
       <c r="V93" s="8"/>
       <c r="W93" s="8"/>
     </row>
@@ -5728,10 +5734,10 @@
       <c r="C94" s="16"/>
       <c r="D94" s="23"/>
       <c r="E94" s="17"/>
-      <c r="F94" s="43"/>
+      <c r="F94" s="73"/>
       <c r="G94" s="23"/>
-      <c r="H94" s="35"/>
-      <c r="I94" s="31"/>
+      <c r="H94" s="34"/>
+      <c r="I94" s="30"/>
       <c r="J94" s="8"/>
       <c r="K94" s="8"/>
       <c r="L94" s="8"/>
@@ -5742,8 +5748,8 @@
       <c r="Q94" s="8"/>
       <c r="R94" s="8"/>
       <c r="S94" s="8"/>
-      <c r="T94" s="33"/>
-      <c r="U94" s="33"/>
+      <c r="T94" s="32"/>
+      <c r="U94" s="32"/>
       <c r="V94" s="8"/>
       <c r="W94" s="8"/>
     </row>
@@ -5753,10 +5759,10 @@
       <c r="C95" s="16"/>
       <c r="D95" s="23"/>
       <c r="E95" s="17"/>
-      <c r="F95" s="43"/>
+      <c r="F95" s="73"/>
       <c r="G95" s="23"/>
-      <c r="H95" s="35"/>
-      <c r="I95" s="31"/>
+      <c r="H95" s="34"/>
+      <c r="I95" s="30"/>
       <c r="J95" s="8"/>
       <c r="K95" s="8"/>
       <c r="L95" s="8"/>
@@ -5767,8 +5773,8 @@
       <c r="Q95" s="8"/>
       <c r="R95" s="8"/>
       <c r="S95" s="8"/>
-      <c r="T95" s="33"/>
-      <c r="U95" s="33"/>
+      <c r="T95" s="32"/>
+      <c r="U95" s="32"/>
       <c r="V95" s="8"/>
       <c r="W95" s="8"/>
     </row>
@@ -5778,10 +5784,10 @@
       <c r="C96" s="16"/>
       <c r="D96" s="23"/>
       <c r="E96" s="17"/>
-      <c r="F96" s="43"/>
+      <c r="F96" s="73"/>
       <c r="G96" s="23"/>
-      <c r="H96" s="35"/>
-      <c r="I96" s="31"/>
+      <c r="H96" s="34"/>
+      <c r="I96" s="30"/>
       <c r="J96" s="8"/>
       <c r="K96" s="8"/>
       <c r="L96" s="8"/>
@@ -5792,8 +5798,8 @@
       <c r="Q96" s="8"/>
       <c r="R96" s="8"/>
       <c r="S96" s="8"/>
-      <c r="T96" s="33"/>
-      <c r="U96" s="33"/>
+      <c r="T96" s="32"/>
+      <c r="U96" s="32"/>
       <c r="V96" s="8"/>
       <c r="W96" s="8"/>
     </row>
@@ -5803,10 +5809,10 @@
       <c r="C97" s="16"/>
       <c r="D97" s="23"/>
       <c r="E97" s="17"/>
-      <c r="F97" s="43"/>
+      <c r="F97" s="73"/>
       <c r="G97" s="23"/>
-      <c r="H97" s="35"/>
-      <c r="I97" s="31"/>
+      <c r="H97" s="34"/>
+      <c r="I97" s="30"/>
       <c r="J97" s="8"/>
       <c r="K97" s="8"/>
       <c r="L97" s="8"/>
@@ -5817,8 +5823,8 @@
       <c r="Q97" s="8"/>
       <c r="R97" s="8"/>
       <c r="S97" s="8"/>
-      <c r="T97" s="33"/>
-      <c r="U97" s="33"/>
+      <c r="T97" s="32"/>
+      <c r="U97" s="32"/>
       <c r="V97" s="8"/>
       <c r="W97" s="8"/>
     </row>
@@ -5828,10 +5834,10 @@
       <c r="C98" s="16"/>
       <c r="D98" s="23"/>
       <c r="E98" s="17"/>
-      <c r="F98" s="43"/>
+      <c r="F98" s="73"/>
       <c r="G98" s="23"/>
-      <c r="H98" s="35"/>
-      <c r="I98" s="31"/>
+      <c r="H98" s="34"/>
+      <c r="I98" s="30"/>
       <c r="J98" s="8"/>
       <c r="K98" s="8"/>
       <c r="L98" s="8"/>
@@ -5842,8 +5848,8 @@
       <c r="Q98" s="8"/>
       <c r="R98" s="8"/>
       <c r="S98" s="8"/>
-      <c r="T98" s="33"/>
-      <c r="U98" s="33"/>
+      <c r="T98" s="32"/>
+      <c r="U98" s="32"/>
       <c r="V98" s="8"/>
       <c r="W98" s="8"/>
     </row>
@@ -5853,10 +5859,10 @@
       <c r="C99" s="16"/>
       <c r="D99" s="23"/>
       <c r="E99" s="17"/>
-      <c r="F99" s="43"/>
+      <c r="F99" s="73"/>
       <c r="G99" s="23"/>
-      <c r="H99" s="35"/>
-      <c r="I99" s="31"/>
+      <c r="H99" s="34"/>
+      <c r="I99" s="30"/>
       <c r="J99" s="8"/>
       <c r="K99" s="8"/>
       <c r="L99" s="8"/>
@@ -5867,8 +5873,8 @@
       <c r="Q99" s="8"/>
       <c r="R99" s="8"/>
       <c r="S99" s="8"/>
-      <c r="T99" s="33"/>
-      <c r="U99" s="33"/>
+      <c r="T99" s="32"/>
+      <c r="U99" s="32"/>
       <c r="V99" s="8"/>
       <c r="W99" s="8"/>
     </row>
@@ -5878,10 +5884,10 @@
       <c r="C100" s="16"/>
       <c r="D100" s="23"/>
       <c r="E100" s="17"/>
-      <c r="F100" s="43"/>
+      <c r="F100" s="73"/>
       <c r="G100" s="23"/>
-      <c r="H100" s="35"/>
-      <c r="I100" s="31"/>
+      <c r="H100" s="34"/>
+      <c r="I100" s="30"/>
       <c r="J100" s="8"/>
       <c r="K100" s="8"/>
       <c r="L100" s="8"/>
@@ -5892,8 +5898,8 @@
       <c r="Q100" s="8"/>
       <c r="R100" s="8"/>
       <c r="S100" s="8"/>
-      <c r="T100" s="33"/>
-      <c r="U100" s="33"/>
+      <c r="T100" s="32"/>
+      <c r="U100" s="32"/>
       <c r="V100" s="8"/>
       <c r="W100" s="8"/>
     </row>
@@ -5903,10 +5909,10 @@
       <c r="C101" s="16"/>
       <c r="D101" s="23"/>
       <c r="E101" s="17"/>
-      <c r="F101" s="43"/>
+      <c r="F101" s="73"/>
       <c r="G101" s="23"/>
-      <c r="H101" s="35"/>
-      <c r="I101" s="31"/>
+      <c r="H101" s="34"/>
+      <c r="I101" s="30"/>
       <c r="J101" s="8"/>
       <c r="K101" s="8"/>
       <c r="L101" s="8"/>
@@ -5917,8 +5923,8 @@
       <c r="Q101" s="8"/>
       <c r="R101" s="8"/>
       <c r="S101" s="8"/>
-      <c r="T101" s="33"/>
-      <c r="U101" s="33"/>
+      <c r="T101" s="32"/>
+      <c r="U101" s="32"/>
       <c r="V101" s="8"/>
       <c r="W101" s="8"/>
     </row>
@@ -5928,10 +5934,10 @@
       <c r="C102" s="16"/>
       <c r="D102" s="23"/>
       <c r="E102" s="17"/>
-      <c r="F102" s="43"/>
+      <c r="F102" s="73"/>
       <c r="G102" s="23"/>
-      <c r="H102" s="35"/>
-      <c r="I102" s="31"/>
+      <c r="H102" s="34"/>
+      <c r="I102" s="30"/>
       <c r="J102" s="8"/>
       <c r="K102" s="8"/>
       <c r="L102" s="8"/>
@@ -5942,8 +5948,8 @@
       <c r="Q102" s="8"/>
       <c r="R102" s="8"/>
       <c r="S102" s="8"/>
-      <c r="T102" s="33"/>
-      <c r="U102" s="33"/>
+      <c r="T102" s="32"/>
+      <c r="U102" s="32"/>
       <c r="V102" s="8"/>
       <c r="W102" s="8"/>
     </row>
@@ -5953,10 +5959,10 @@
       <c r="C103" s="16"/>
       <c r="D103" s="23"/>
       <c r="E103" s="17"/>
-      <c r="F103" s="43"/>
+      <c r="F103" s="73"/>
       <c r="G103" s="23"/>
-      <c r="H103" s="35"/>
-      <c r="I103" s="31"/>
+      <c r="H103" s="34"/>
+      <c r="I103" s="30"/>
       <c r="J103" s="8"/>
       <c r="K103" s="8"/>
       <c r="L103" s="8"/>
@@ -5967,8 +5973,8 @@
       <c r="Q103" s="8"/>
       <c r="R103" s="8"/>
       <c r="S103" s="8"/>
-      <c r="T103" s="33"/>
-      <c r="U103" s="33"/>
+      <c r="T103" s="32"/>
+      <c r="U103" s="32"/>
       <c r="V103" s="8"/>
       <c r="W103" s="8"/>
     </row>
@@ -5978,10 +5984,10 @@
       <c r="C104" s="16"/>
       <c r="D104" s="23"/>
       <c r="E104" s="17"/>
-      <c r="F104" s="43"/>
+      <c r="F104" s="73"/>
       <c r="G104" s="23"/>
-      <c r="H104" s="35"/>
-      <c r="I104" s="31"/>
+      <c r="H104" s="34"/>
+      <c r="I104" s="30"/>
       <c r="J104" s="8"/>
       <c r="K104" s="8"/>
       <c r="L104" s="8"/>
@@ -5992,8 +5998,8 @@
       <c r="Q104" s="8"/>
       <c r="R104" s="8"/>
       <c r="S104" s="8"/>
-      <c r="T104" s="33"/>
-      <c r="U104" s="33"/>
+      <c r="T104" s="32"/>
+      <c r="U104" s="32"/>
       <c r="V104" s="8"/>
       <c r="W104" s="8"/>
     </row>
@@ -6003,10 +6009,10 @@
       <c r="C105" s="16"/>
       <c r="D105" s="23"/>
       <c r="E105" s="17"/>
-      <c r="F105" s="43"/>
+      <c r="F105" s="73"/>
       <c r="G105" s="23"/>
-      <c r="H105" s="35"/>
-      <c r="I105" s="31"/>
+      <c r="H105" s="34"/>
+      <c r="I105" s="30"/>
       <c r="J105" s="8"/>
       <c r="K105" s="8"/>
       <c r="L105" s="8"/>
@@ -6017,8 +6023,8 @@
       <c r="Q105" s="8"/>
       <c r="R105" s="8"/>
       <c r="S105" s="8"/>
-      <c r="T105" s="33"/>
-      <c r="U105" s="33"/>
+      <c r="T105" s="32"/>
+      <c r="U105" s="32"/>
       <c r="V105" s="8"/>
       <c r="W105" s="8"/>
     </row>
@@ -6028,10 +6034,10 @@
       <c r="C106" s="16"/>
       <c r="D106" s="23"/>
       <c r="E106" s="17"/>
-      <c r="F106" s="43"/>
+      <c r="F106" s="73"/>
       <c r="G106" s="23"/>
-      <c r="H106" s="35"/>
-      <c r="I106" s="31"/>
+      <c r="H106" s="34"/>
+      <c r="I106" s="30"/>
       <c r="J106" s="8"/>
       <c r="K106" s="8"/>
       <c r="L106" s="8"/>
@@ -6042,8 +6048,8 @@
       <c r="Q106" s="8"/>
       <c r="R106" s="8"/>
       <c r="S106" s="8"/>
-      <c r="T106" s="33"/>
-      <c r="U106" s="33"/>
+      <c r="T106" s="32"/>
+      <c r="U106" s="32"/>
       <c r="V106" s="8"/>
       <c r="W106" s="8"/>
     </row>
@@ -6053,10 +6059,10 @@
       <c r="C107" s="16"/>
       <c r="D107" s="23"/>
       <c r="E107" s="17"/>
-      <c r="F107" s="43"/>
+      <c r="F107" s="73"/>
       <c r="G107" s="23"/>
-      <c r="H107" s="35"/>
-      <c r="I107" s="31"/>
+      <c r="H107" s="34"/>
+      <c r="I107" s="30"/>
       <c r="J107" s="8"/>
       <c r="K107" s="8"/>
       <c r="L107" s="8"/>
@@ -6067,8 +6073,8 @@
       <c r="Q107" s="8"/>
       <c r="R107" s="8"/>
       <c r="S107" s="8"/>
-      <c r="T107" s="33"/>
-      <c r="U107" s="33"/>
+      <c r="T107" s="32"/>
+      <c r="U107" s="32"/>
       <c r="V107" s="8"/>
       <c r="W107" s="8"/>
     </row>
@@ -6078,10 +6084,10 @@
       <c r="C108" s="16"/>
       <c r="D108" s="23"/>
       <c r="E108" s="17"/>
-      <c r="F108" s="43"/>
+      <c r="F108" s="73"/>
       <c r="G108" s="23"/>
-      <c r="H108" s="35"/>
-      <c r="I108" s="31"/>
+      <c r="H108" s="34"/>
+      <c r="I108" s="30"/>
       <c r="J108" s="8"/>
       <c r="K108" s="8"/>
       <c r="L108" s="8"/>
@@ -6092,8 +6098,8 @@
       <c r="Q108" s="8"/>
       <c r="R108" s="8"/>
       <c r="S108" s="8"/>
-      <c r="T108" s="33"/>
-      <c r="U108" s="33"/>
+      <c r="T108" s="32"/>
+      <c r="U108" s="32"/>
       <c r="V108" s="8"/>
       <c r="W108" s="8"/>
     </row>
@@ -6103,10 +6109,10 @@
       <c r="C109" s="16"/>
       <c r="D109" s="23"/>
       <c r="E109" s="17"/>
-      <c r="F109" s="43"/>
+      <c r="F109" s="73"/>
       <c r="G109" s="23"/>
-      <c r="H109" s="35"/>
-      <c r="I109" s="31"/>
+      <c r="H109" s="34"/>
+      <c r="I109" s="30"/>
       <c r="J109" s="8"/>
       <c r="K109" s="8"/>
       <c r="L109" s="8"/>
@@ -6117,8 +6123,8 @@
       <c r="Q109" s="8"/>
       <c r="R109" s="8"/>
       <c r="S109" s="8"/>
-      <c r="T109" s="33"/>
-      <c r="U109" s="33"/>
+      <c r="T109" s="32"/>
+      <c r="U109" s="32"/>
       <c r="V109" s="8"/>
       <c r="W109" s="8"/>
     </row>
@@ -6128,10 +6134,10 @@
       <c r="C110" s="16"/>
       <c r="D110" s="23"/>
       <c r="E110" s="17"/>
-      <c r="F110" s="43"/>
+      <c r="F110" s="73"/>
       <c r="G110" s="23"/>
-      <c r="H110" s="35"/>
-      <c r="I110" s="31"/>
+      <c r="H110" s="34"/>
+      <c r="I110" s="30"/>
       <c r="J110" s="8"/>
       <c r="K110" s="8"/>
       <c r="L110" s="8"/>
@@ -6142,8 +6148,8 @@
       <c r="Q110" s="8"/>
       <c r="R110" s="8"/>
       <c r="S110" s="8"/>
-      <c r="T110" s="33"/>
-      <c r="U110" s="33"/>
+      <c r="T110" s="32"/>
+      <c r="U110" s="32"/>
       <c r="V110" s="8"/>
       <c r="W110" s="8"/>
     </row>
@@ -6153,10 +6159,10 @@
       <c r="C111" s="16"/>
       <c r="D111" s="23"/>
       <c r="E111" s="17"/>
-      <c r="F111" s="43"/>
+      <c r="F111" s="73"/>
       <c r="G111" s="23"/>
-      <c r="H111" s="35"/>
-      <c r="I111" s="31"/>
+      <c r="H111" s="34"/>
+      <c r="I111" s="30"/>
       <c r="J111" s="8"/>
       <c r="K111" s="8"/>
       <c r="L111" s="8"/>
@@ -6167,8 +6173,8 @@
       <c r="Q111" s="8"/>
       <c r="R111" s="8"/>
       <c r="S111" s="8"/>
-      <c r="T111" s="33"/>
-      <c r="U111" s="33"/>
+      <c r="T111" s="32"/>
+      <c r="U111" s="32"/>
       <c r="V111" s="8"/>
       <c r="W111" s="8"/>
     </row>
@@ -6178,10 +6184,10 @@
       <c r="C112" s="16"/>
       <c r="D112" s="23"/>
       <c r="E112" s="17"/>
-      <c r="F112" s="43"/>
+      <c r="F112" s="73"/>
       <c r="G112" s="23"/>
-      <c r="H112" s="35"/>
-      <c r="I112" s="31"/>
+      <c r="H112" s="34"/>
+      <c r="I112" s="30"/>
       <c r="J112" s="8"/>
       <c r="K112" s="8"/>
       <c r="L112" s="8"/>
@@ -6192,8 +6198,8 @@
       <c r="Q112" s="8"/>
       <c r="R112" s="8"/>
       <c r="S112" s="8"/>
-      <c r="T112" s="33"/>
-      <c r="U112" s="33"/>
+      <c r="T112" s="32"/>
+      <c r="U112" s="32"/>
       <c r="V112" s="8"/>
       <c r="W112" s="8"/>
     </row>
@@ -6203,10 +6209,10 @@
       <c r="C113" s="16"/>
       <c r="D113" s="23"/>
       <c r="E113" s="17"/>
-      <c r="F113" s="43"/>
+      <c r="F113" s="73"/>
       <c r="G113" s="23"/>
-      <c r="H113" s="35"/>
-      <c r="I113" s="31"/>
+      <c r="H113" s="34"/>
+      <c r="I113" s="30"/>
       <c r="J113" s="8"/>
       <c r="K113" s="8"/>
       <c r="L113" s="8"/>
@@ -6217,8 +6223,8 @@
       <c r="Q113" s="8"/>
       <c r="R113" s="8"/>
       <c r="S113" s="8"/>
-      <c r="T113" s="33"/>
-      <c r="U113" s="33"/>
+      <c r="T113" s="32"/>
+      <c r="U113" s="32"/>
       <c r="V113" s="8"/>
       <c r="W113" s="8"/>
     </row>
@@ -6228,10 +6234,10 @@
       <c r="C114" s="16"/>
       <c r="D114" s="23"/>
       <c r="E114" s="17"/>
-      <c r="F114" s="43"/>
+      <c r="F114" s="73"/>
       <c r="G114" s="23"/>
-      <c r="H114" s="35"/>
-      <c r="I114" s="31"/>
+      <c r="H114" s="34"/>
+      <c r="I114" s="30"/>
       <c r="J114" s="8"/>
       <c r="K114" s="8"/>
       <c r="L114" s="8"/>
@@ -6242,8 +6248,8 @@
       <c r="Q114" s="8"/>
       <c r="R114" s="8"/>
       <c r="S114" s="8"/>
-      <c r="T114" s="33"/>
-      <c r="U114" s="33"/>
+      <c r="T114" s="32"/>
+      <c r="U114" s="32"/>
       <c r="V114" s="8"/>
       <c r="W114" s="8"/>
     </row>
@@ -6253,10 +6259,10 @@
       <c r="C115" s="16"/>
       <c r="D115" s="23"/>
       <c r="E115" s="17"/>
-      <c r="F115" s="43"/>
+      <c r="F115" s="73"/>
       <c r="G115" s="23"/>
-      <c r="H115" s="35"/>
-      <c r="I115" s="31"/>
+      <c r="H115" s="34"/>
+      <c r="I115" s="30"/>
       <c r="J115" s="8"/>
       <c r="K115" s="8"/>
       <c r="L115" s="8"/>
@@ -6267,8 +6273,8 @@
       <c r="Q115" s="8"/>
       <c r="R115" s="8"/>
       <c r="S115" s="8"/>
-      <c r="T115" s="33"/>
-      <c r="U115" s="33"/>
+      <c r="T115" s="32"/>
+      <c r="U115" s="32"/>
       <c r="V115" s="8"/>
       <c r="W115" s="8"/>
     </row>
@@ -6278,10 +6284,10 @@
       <c r="C116" s="16"/>
       <c r="D116" s="23"/>
       <c r="E116" s="17"/>
-      <c r="F116" s="43"/>
+      <c r="F116" s="73"/>
       <c r="G116" s="23"/>
-      <c r="H116" s="35"/>
-      <c r="I116" s="31"/>
+      <c r="H116" s="34"/>
+      <c r="I116" s="30"/>
       <c r="J116" s="8"/>
       <c r="K116" s="8"/>
       <c r="L116" s="8"/>
@@ -6292,8 +6298,8 @@
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
       <c r="S116" s="8"/>
-      <c r="T116" s="33"/>
-      <c r="U116" s="33"/>
+      <c r="T116" s="32"/>
+      <c r="U116" s="32"/>
       <c r="V116" s="8"/>
       <c r="W116" s="8"/>
     </row>
@@ -6303,10 +6309,10 @@
       <c r="C117" s="16"/>
       <c r="D117" s="23"/>
       <c r="E117" s="17"/>
-      <c r="F117" s="43"/>
+      <c r="F117" s="73"/>
       <c r="G117" s="23"/>
-      <c r="H117" s="35"/>
-      <c r="I117" s="31"/>
+      <c r="H117" s="34"/>
+      <c r="I117" s="30"/>
       <c r="J117" s="8"/>
       <c r="K117" s="8"/>
       <c r="L117" s="8"/>
@@ -6317,8 +6323,8 @@
       <c r="Q117" s="8"/>
       <c r="R117" s="8"/>
       <c r="S117" s="8"/>
-      <c r="T117" s="33"/>
-      <c r="U117" s="33"/>
+      <c r="T117" s="32"/>
+      <c r="U117" s="32"/>
       <c r="V117" s="8"/>
       <c r="W117" s="8"/>
     </row>
@@ -6328,10 +6334,10 @@
       <c r="C118" s="16"/>
       <c r="D118" s="23"/>
       <c r="E118" s="17"/>
-      <c r="F118" s="43"/>
+      <c r="F118" s="73"/>
       <c r="G118" s="23"/>
-      <c r="H118" s="35"/>
-      <c r="I118" s="31"/>
+      <c r="H118" s="34"/>
+      <c r="I118" s="30"/>
       <c r="J118" s="8"/>
       <c r="K118" s="8"/>
       <c r="L118" s="8"/>
@@ -6342,8 +6348,8 @@
       <c r="Q118" s="8"/>
       <c r="R118" s="8"/>
       <c r="S118" s="8"/>
-      <c r="T118" s="33"/>
-      <c r="U118" s="33"/>
+      <c r="T118" s="32"/>
+      <c r="U118" s="32"/>
       <c r="V118" s="8"/>
       <c r="W118" s="8"/>
     </row>
@@ -6353,10 +6359,10 @@
       <c r="C119" s="16"/>
       <c r="D119" s="23"/>
       <c r="E119" s="17"/>
-      <c r="F119" s="43"/>
+      <c r="F119" s="73"/>
       <c r="G119" s="23"/>
-      <c r="H119" s="35"/>
-      <c r="I119" s="31"/>
+      <c r="H119" s="34"/>
+      <c r="I119" s="30"/>
       <c r="J119" s="8"/>
       <c r="K119" s="8"/>
       <c r="L119" s="8"/>
@@ -6367,8 +6373,8 @@
       <c r="Q119" s="8"/>
       <c r="R119" s="8"/>
       <c r="S119" s="8"/>
-      <c r="T119" s="33"/>
-      <c r="U119" s="33"/>
+      <c r="T119" s="32"/>
+      <c r="U119" s="32"/>
       <c r="V119" s="8"/>
       <c r="W119" s="8"/>
     </row>
@@ -6378,10 +6384,10 @@
       <c r="C120" s="16"/>
       <c r="D120" s="23"/>
       <c r="E120" s="17"/>
-      <c r="F120" s="43"/>
+      <c r="F120" s="73"/>
       <c r="G120" s="23"/>
-      <c r="H120" s="35"/>
-      <c r="I120" s="31"/>
+      <c r="H120" s="34"/>
+      <c r="I120" s="30"/>
       <c r="J120" s="8"/>
       <c r="K120" s="8"/>
       <c r="L120" s="8"/>
@@ -6392,8 +6398,8 @@
       <c r="Q120" s="8"/>
       <c r="R120" s="8"/>
       <c r="S120" s="8"/>
-      <c r="T120" s="33"/>
-      <c r="U120" s="33"/>
+      <c r="T120" s="32"/>
+      <c r="U120" s="32"/>
       <c r="V120" s="8"/>
       <c r="W120" s="8"/>
     </row>
@@ -6403,10 +6409,10 @@
       <c r="C121" s="16"/>
       <c r="D121" s="23"/>
       <c r="E121" s="17"/>
-      <c r="F121" s="43"/>
+      <c r="F121" s="73"/>
       <c r="G121" s="23"/>
-      <c r="H121" s="35"/>
-      <c r="I121" s="31"/>
+      <c r="H121" s="34"/>
+      <c r="I121" s="30"/>
       <c r="J121" s="8"/>
       <c r="K121" s="8"/>
       <c r="L121" s="8"/>
@@ -6417,8 +6423,8 @@
       <c r="Q121" s="8"/>
       <c r="R121" s="8"/>
       <c r="S121" s="8"/>
-      <c r="T121" s="33"/>
-      <c r="U121" s="33"/>
+      <c r="T121" s="32"/>
+      <c r="U121" s="32"/>
       <c r="V121" s="8"/>
       <c r="W121" s="8"/>
     </row>
@@ -6428,10 +6434,10 @@
       <c r="C122" s="16"/>
       <c r="D122" s="23"/>
       <c r="E122" s="17"/>
-      <c r="F122" s="43"/>
+      <c r="F122" s="73"/>
       <c r="G122" s="23"/>
-      <c r="H122" s="35"/>
-      <c r="I122" s="31"/>
+      <c r="H122" s="34"/>
+      <c r="I122" s="30"/>
       <c r="J122" s="8"/>
       <c r="K122" s="8"/>
       <c r="L122" s="8"/>
@@ -6442,8 +6448,8 @@
       <c r="Q122" s="8"/>
       <c r="R122" s="8"/>
       <c r="S122" s="8"/>
-      <c r="T122" s="33"/>
-      <c r="U122" s="33"/>
+      <c r="T122" s="32"/>
+      <c r="U122" s="32"/>
       <c r="V122" s="8"/>
       <c r="W122" s="8"/>
     </row>
@@ -6453,10 +6459,10 @@
       <c r="C123" s="16"/>
       <c r="D123" s="23"/>
       <c r="E123" s="17"/>
-      <c r="F123" s="43"/>
+      <c r="F123" s="73"/>
       <c r="G123" s="23"/>
-      <c r="H123" s="35"/>
-      <c r="I123" s="31"/>
+      <c r="H123" s="34"/>
+      <c r="I123" s="30"/>
       <c r="J123" s="8"/>
       <c r="K123" s="8"/>
       <c r="L123" s="8"/>
@@ -6467,8 +6473,8 @@
       <c r="Q123" s="8"/>
       <c r="R123" s="8"/>
       <c r="S123" s="8"/>
-      <c r="T123" s="33"/>
-      <c r="U123" s="33"/>
+      <c r="T123" s="32"/>
+      <c r="U123" s="32"/>
       <c r="V123" s="8"/>
       <c r="W123" s="8"/>
     </row>
@@ -6478,10 +6484,10 @@
       <c r="C124" s="16"/>
       <c r="D124" s="23"/>
       <c r="E124" s="17"/>
-      <c r="F124" s="43"/>
+      <c r="F124" s="73"/>
       <c r="G124" s="23"/>
-      <c r="H124" s="35"/>
-      <c r="I124" s="31"/>
+      <c r="H124" s="34"/>
+      <c r="I124" s="30"/>
       <c r="J124" s="8"/>
       <c r="K124" s="8"/>
       <c r="L124" s="8"/>
@@ -6492,8 +6498,8 @@
       <c r="Q124" s="8"/>
       <c r="R124" s="8"/>
       <c r="S124" s="8"/>
-      <c r="T124" s="33"/>
-      <c r="U124" s="33"/>
+      <c r="T124" s="32"/>
+      <c r="U124" s="32"/>
       <c r="V124" s="8"/>
       <c r="W124" s="8"/>
     </row>
@@ -6503,10 +6509,10 @@
       <c r="C125" s="16"/>
       <c r="D125" s="23"/>
       <c r="E125" s="17"/>
-      <c r="F125" s="43"/>
+      <c r="F125" s="73"/>
       <c r="G125" s="23"/>
-      <c r="H125" s="35"/>
-      <c r="I125" s="31"/>
+      <c r="H125" s="34"/>
+      <c r="I125" s="30"/>
       <c r="J125" s="8"/>
       <c r="K125" s="8"/>
       <c r="L125" s="8"/>
@@ -6517,8 +6523,8 @@
       <c r="Q125" s="8"/>
       <c r="R125" s="8"/>
       <c r="S125" s="8"/>
-      <c r="T125" s="33"/>
-      <c r="U125" s="33"/>
+      <c r="T125" s="32"/>
+      <c r="U125" s="32"/>
       <c r="V125" s="8"/>
       <c r="W125" s="8"/>
     </row>
@@ -6528,10 +6534,10 @@
       <c r="C126" s="16"/>
       <c r="D126" s="23"/>
       <c r="E126" s="17"/>
-      <c r="F126" s="43"/>
+      <c r="F126" s="73"/>
       <c r="G126" s="23"/>
-      <c r="H126" s="35"/>
-      <c r="I126" s="31"/>
+      <c r="H126" s="34"/>
+      <c r="I126" s="30"/>
       <c r="J126" s="8"/>
       <c r="K126" s="8"/>
       <c r="L126" s="8"/>
@@ -6542,8 +6548,8 @@
       <c r="Q126" s="8"/>
       <c r="R126" s="8"/>
       <c r="S126" s="8"/>
-      <c r="T126" s="33"/>
-      <c r="U126" s="33"/>
+      <c r="T126" s="32"/>
+      <c r="U126" s="32"/>
       <c r="V126" s="8"/>
       <c r="W126" s="8"/>
     </row>
@@ -6553,10 +6559,10 @@
       <c r="C127" s="16"/>
       <c r="D127" s="23"/>
       <c r="E127" s="17"/>
-      <c r="F127" s="43"/>
+      <c r="F127" s="73"/>
       <c r="G127" s="23"/>
-      <c r="H127" s="35"/>
-      <c r="I127" s="31"/>
+      <c r="H127" s="34"/>
+      <c r="I127" s="30"/>
       <c r="J127" s="8"/>
       <c r="K127" s="8"/>
       <c r="L127" s="8"/>
@@ -6567,8 +6573,8 @@
       <c r="Q127" s="8"/>
       <c r="R127" s="8"/>
       <c r="S127" s="8"/>
-      <c r="T127" s="33"/>
-      <c r="U127" s="33"/>
+      <c r="T127" s="32"/>
+      <c r="U127" s="32"/>
       <c r="V127" s="8"/>
       <c r="W127" s="8"/>
     </row>
@@ -6578,10 +6584,10 @@
       <c r="C128" s="16"/>
       <c r="D128" s="23"/>
       <c r="E128" s="17"/>
-      <c r="F128" s="43"/>
+      <c r="F128" s="73"/>
       <c r="G128" s="23"/>
-      <c r="H128" s="35"/>
-      <c r="I128" s="31"/>
+      <c r="H128" s="34"/>
+      <c r="I128" s="30"/>
       <c r="J128" s="8"/>
       <c r="K128" s="8"/>
       <c r="L128" s="8"/>
@@ -6592,8 +6598,8 @@
       <c r="Q128" s="8"/>
       <c r="R128" s="8"/>
       <c r="S128" s="8"/>
-      <c r="T128" s="33"/>
-      <c r="U128" s="33"/>
+      <c r="T128" s="32"/>
+      <c r="U128" s="32"/>
       <c r="V128" s="8"/>
       <c r="W128" s="8"/>
     </row>
@@ -6603,10 +6609,10 @@
       <c r="C129" s="16"/>
       <c r="D129" s="23"/>
       <c r="E129" s="17"/>
-      <c r="F129" s="43"/>
+      <c r="F129" s="73"/>
       <c r="G129" s="23"/>
-      <c r="H129" s="35"/>
-      <c r="I129" s="31"/>
+      <c r="H129" s="34"/>
+      <c r="I129" s="30"/>
       <c r="J129" s="8"/>
       <c r="K129" s="8"/>
       <c r="L129" s="8"/>
@@ -6617,8 +6623,8 @@
       <c r="Q129" s="8"/>
       <c r="R129" s="8"/>
       <c r="S129" s="8"/>
-      <c r="T129" s="33"/>
-      <c r="U129" s="33"/>
+      <c r="T129" s="32"/>
+      <c r="U129" s="32"/>
       <c r="V129" s="8"/>
       <c r="W129" s="8"/>
     </row>
@@ -6628,10 +6634,10 @@
       <c r="C130" s="16"/>
       <c r="D130" s="23"/>
       <c r="E130" s="17"/>
-      <c r="F130" s="43"/>
+      <c r="F130" s="73"/>
       <c r="G130" s="23"/>
-      <c r="H130" s="35"/>
-      <c r="I130" s="31"/>
+      <c r="H130" s="34"/>
+      <c r="I130" s="30"/>
       <c r="J130" s="8"/>
       <c r="K130" s="8"/>
       <c r="L130" s="8"/>
@@ -6642,8 +6648,8 @@
       <c r="Q130" s="8"/>
       <c r="R130" s="8"/>
       <c r="S130" s="8"/>
-      <c r="T130" s="33"/>
-      <c r="U130" s="33"/>
+      <c r="T130" s="32"/>
+      <c r="U130" s="32"/>
       <c r="V130" s="8"/>
       <c r="W130" s="8"/>
     </row>
@@ -6653,10 +6659,10 @@
       <c r="C131" s="16"/>
       <c r="D131" s="23"/>
       <c r="E131" s="17"/>
-      <c r="F131" s="43"/>
+      <c r="F131" s="73"/>
       <c r="G131" s="23"/>
-      <c r="H131" s="35"/>
-      <c r="I131" s="31"/>
+      <c r="H131" s="34"/>
+      <c r="I131" s="30"/>
       <c r="J131" s="8"/>
       <c r="K131" s="8"/>
       <c r="L131" s="8"/>
@@ -6667,8 +6673,8 @@
       <c r="Q131" s="8"/>
       <c r="R131" s="8"/>
       <c r="S131" s="8"/>
-      <c r="T131" s="33"/>
-      <c r="U131" s="33"/>
+      <c r="T131" s="32"/>
+      <c r="U131" s="32"/>
       <c r="V131" s="8"/>
       <c r="W131" s="8"/>
     </row>
@@ -6678,10 +6684,10 @@
       <c r="C132" s="16"/>
       <c r="D132" s="23"/>
       <c r="E132" s="17"/>
-      <c r="F132" s="43"/>
+      <c r="F132" s="73"/>
       <c r="G132" s="23"/>
-      <c r="H132" s="35"/>
-      <c r="I132" s="31"/>
+      <c r="H132" s="34"/>
+      <c r="I132" s="30"/>
       <c r="J132" s="8"/>
       <c r="K132" s="8"/>
       <c r="L132" s="8"/>
@@ -6692,8 +6698,8 @@
       <c r="Q132" s="8"/>
       <c r="R132" s="8"/>
       <c r="S132" s="8"/>
-      <c r="T132" s="33"/>
-      <c r="U132" s="33"/>
+      <c r="T132" s="32"/>
+      <c r="U132" s="32"/>
       <c r="V132" s="8"/>
       <c r="W132" s="8"/>
     </row>
@@ -6703,10 +6709,10 @@
       <c r="C133" s="16"/>
       <c r="D133" s="23"/>
       <c r="E133" s="17"/>
-      <c r="F133" s="43"/>
+      <c r="F133" s="73"/>
       <c r="G133" s="23"/>
-      <c r="H133" s="35"/>
-      <c r="I133" s="31"/>
+      <c r="H133" s="34"/>
+      <c r="I133" s="30"/>
       <c r="J133" s="8"/>
       <c r="K133" s="8"/>
       <c r="L133" s="8"/>
@@ -6717,8 +6723,8 @@
       <c r="Q133" s="8"/>
       <c r="R133" s="8"/>
       <c r="S133" s="8"/>
-      <c r="T133" s="33"/>
-      <c r="U133" s="33"/>
+      <c r="T133" s="32"/>
+      <c r="U133" s="32"/>
       <c r="V133" s="8"/>
       <c r="W133" s="8"/>
     </row>
@@ -6728,10 +6734,10 @@
       <c r="C134" s="16"/>
       <c r="D134" s="23"/>
       <c r="E134" s="17"/>
-      <c r="F134" s="43"/>
+      <c r="F134" s="73"/>
       <c r="G134" s="23"/>
-      <c r="H134" s="35"/>
-      <c r="I134" s="31"/>
+      <c r="H134" s="34"/>
+      <c r="I134" s="30"/>
       <c r="J134" s="8"/>
       <c r="K134" s="8"/>
       <c r="L134" s="8"/>
@@ -6742,8 +6748,8 @@
       <c r="Q134" s="8"/>
       <c r="R134" s="8"/>
       <c r="S134" s="8"/>
-      <c r="T134" s="33"/>
-      <c r="U134" s="33"/>
+      <c r="T134" s="32"/>
+      <c r="U134" s="32"/>
       <c r="V134" s="8"/>
       <c r="W134" s="8"/>
     </row>
@@ -6753,10 +6759,10 @@
       <c r="C135" s="16"/>
       <c r="D135" s="23"/>
       <c r="E135" s="17"/>
-      <c r="F135" s="43"/>
+      <c r="F135" s="73"/>
       <c r="G135" s="23"/>
-      <c r="H135" s="35"/>
-      <c r="I135" s="31"/>
+      <c r="H135" s="34"/>
+      <c r="I135" s="30"/>
       <c r="J135" s="8"/>
       <c r="K135" s="8"/>
       <c r="L135" s="8"/>
@@ -6767,8 +6773,8 @@
       <c r="Q135" s="8"/>
       <c r="R135" s="8"/>
       <c r="S135" s="8"/>
-      <c r="T135" s="33"/>
-      <c r="U135" s="33"/>
+      <c r="T135" s="32"/>
+      <c r="U135" s="32"/>
       <c r="V135" s="8"/>
       <c r="W135" s="8"/>
     </row>
@@ -6778,10 +6784,10 @@
       <c r="C136" s="16"/>
       <c r="D136" s="23"/>
       <c r="E136" s="17"/>
-      <c r="F136" s="43"/>
+      <c r="F136" s="73"/>
       <c r="G136" s="23"/>
-      <c r="H136" s="35"/>
-      <c r="I136" s="31"/>
+      <c r="H136" s="34"/>
+      <c r="I136" s="30"/>
       <c r="J136" s="8"/>
       <c r="K136" s="8"/>
       <c r="L136" s="8"/>
@@ -6792,8 +6798,8 @@
       <c r="Q136" s="8"/>
       <c r="R136" s="8"/>
       <c r="S136" s="8"/>
-      <c r="T136" s="33"/>
-      <c r="U136" s="33"/>
+      <c r="T136" s="32"/>
+      <c r="U136" s="32"/>
       <c r="V136" s="8"/>
       <c r="W136" s="8"/>
     </row>
@@ -6803,10 +6809,10 @@
       <c r="C137" s="16"/>
       <c r="D137" s="23"/>
       <c r="E137" s="17"/>
-      <c r="F137" s="43"/>
+      <c r="F137" s="73"/>
       <c r="G137" s="23"/>
-      <c r="H137" s="35"/>
-      <c r="I137" s="31"/>
+      <c r="H137" s="34"/>
+      <c r="I137" s="30"/>
       <c r="J137" s="8"/>
       <c r="K137" s="8"/>
       <c r="L137" s="8"/>
@@ -6817,8 +6823,8 @@
       <c r="Q137" s="8"/>
       <c r="R137" s="8"/>
       <c r="S137" s="8"/>
-      <c r="T137" s="33"/>
-      <c r="U137" s="33"/>
+      <c r="T137" s="32"/>
+      <c r="U137" s="32"/>
       <c r="V137" s="8"/>
       <c r="W137" s="8"/>
     </row>
@@ -6828,10 +6834,10 @@
       <c r="C138" s="16"/>
       <c r="D138" s="23"/>
       <c r="E138" s="17"/>
-      <c r="F138" s="43"/>
+      <c r="F138" s="73"/>
       <c r="G138" s="23"/>
-      <c r="H138" s="35"/>
-      <c r="I138" s="31"/>
+      <c r="H138" s="34"/>
+      <c r="I138" s="30"/>
       <c r="J138" s="8"/>
       <c r="K138" s="8"/>
       <c r="L138" s="8"/>
@@ -6842,8 +6848,8 @@
       <c r="Q138" s="8"/>
       <c r="R138" s="8"/>
       <c r="S138" s="8"/>
-      <c r="T138" s="33"/>
-      <c r="U138" s="33"/>
+      <c r="T138" s="32"/>
+      <c r="U138" s="32"/>
       <c r="V138" s="8"/>
       <c r="W138" s="8"/>
     </row>
@@ -6853,10 +6859,10 @@
       <c r="C139" s="16"/>
       <c r="D139" s="23"/>
       <c r="E139" s="17"/>
-      <c r="F139" s="43"/>
+      <c r="F139" s="73"/>
       <c r="G139" s="23"/>
-      <c r="H139" s="35"/>
-      <c r="I139" s="31"/>
+      <c r="H139" s="34"/>
+      <c r="I139" s="30"/>
       <c r="J139" s="8"/>
       <c r="K139" s="8"/>
       <c r="L139" s="8"/>
@@ -6867,8 +6873,8 @@
       <c r="Q139" s="8"/>
       <c r="R139" s="8"/>
       <c r="S139" s="8"/>
-      <c r="T139" s="33"/>
-      <c r="U139" s="33"/>
+      <c r="T139" s="32"/>
+      <c r="U139" s="32"/>
       <c r="V139" s="8"/>
       <c r="W139" s="8"/>
     </row>
@@ -6878,10 +6884,10 @@
       <c r="C140" s="16"/>
       <c r="D140" s="23"/>
       <c r="E140" s="17"/>
-      <c r="F140" s="43"/>
+      <c r="F140" s="73"/>
       <c r="G140" s="23"/>
-      <c r="H140" s="35"/>
-      <c r="I140" s="31"/>
+      <c r="H140" s="34"/>
+      <c r="I140" s="30"/>
       <c r="J140" s="8"/>
       <c r="K140" s="8"/>
       <c r="L140" s="8"/>
@@ -6892,8 +6898,8 @@
       <c r="Q140" s="8"/>
       <c r="R140" s="8"/>
       <c r="S140" s="8"/>
-      <c r="T140" s="33"/>
-      <c r="U140" s="33"/>
+      <c r="T140" s="32"/>
+      <c r="U140" s="32"/>
       <c r="V140" s="8"/>
       <c r="W140" s="8"/>
     </row>
@@ -6903,10 +6909,10 @@
       <c r="C141" s="16"/>
       <c r="D141" s="23"/>
       <c r="E141" s="17"/>
-      <c r="F141" s="43"/>
+      <c r="F141" s="73"/>
       <c r="G141" s="23"/>
-      <c r="H141" s="35"/>
-      <c r="I141" s="31"/>
+      <c r="H141" s="34"/>
+      <c r="I141" s="30"/>
       <c r="J141" s="8"/>
       <c r="K141" s="8"/>
       <c r="L141" s="8"/>
@@ -6917,8 +6923,8 @@
       <c r="Q141" s="8"/>
       <c r="R141" s="8"/>
       <c r="S141" s="8"/>
-      <c r="T141" s="33"/>
-      <c r="U141" s="33"/>
+      <c r="T141" s="32"/>
+      <c r="U141" s="32"/>
       <c r="V141" s="8"/>
       <c r="W141" s="8"/>
     </row>
@@ -6928,10 +6934,10 @@
       <c r="C142" s="16"/>
       <c r="D142" s="23"/>
       <c r="E142" s="17"/>
-      <c r="F142" s="43"/>
+      <c r="F142" s="73"/>
       <c r="G142" s="23"/>
-      <c r="H142" s="35"/>
-      <c r="I142" s="31"/>
+      <c r="H142" s="34"/>
+      <c r="I142" s="30"/>
       <c r="J142" s="8"/>
       <c r="K142" s="8"/>
       <c r="L142" s="8"/>
@@ -6942,8 +6948,8 @@
       <c r="Q142" s="8"/>
       <c r="R142" s="8"/>
       <c r="S142" s="8"/>
-      <c r="T142" s="33"/>
-      <c r="U142" s="33"/>
+      <c r="T142" s="32"/>
+      <c r="U142" s="32"/>
       <c r="V142" s="8"/>
       <c r="W142" s="8"/>
     </row>
@@ -6953,10 +6959,10 @@
       <c r="C143" s="16"/>
       <c r="D143" s="23"/>
       <c r="E143" s="17"/>
-      <c r="F143" s="43"/>
+      <c r="F143" s="73"/>
       <c r="G143" s="23"/>
-      <c r="H143" s="35"/>
-      <c r="I143" s="31"/>
+      <c r="H143" s="34"/>
+      <c r="I143" s="30"/>
       <c r="J143" s="8"/>
       <c r="K143" s="8"/>
       <c r="L143" s="8"/>
@@ -6967,8 +6973,8 @@
       <c r="Q143" s="8"/>
       <c r="R143" s="8"/>
       <c r="S143" s="8"/>
-      <c r="T143" s="33"/>
-      <c r="U143" s="33"/>
+      <c r="T143" s="32"/>
+      <c r="U143" s="32"/>
       <c r="V143" s="8"/>
       <c r="W143" s="8"/>
     </row>
@@ -6978,10 +6984,10 @@
       <c r="C144" s="16"/>
       <c r="D144" s="23"/>
       <c r="E144" s="17"/>
-      <c r="F144" s="43"/>
+      <c r="F144" s="73"/>
       <c r="G144" s="23"/>
-      <c r="H144" s="35"/>
-      <c r="I144" s="31"/>
+      <c r="H144" s="34"/>
+      <c r="I144" s="30"/>
       <c r="J144" s="8"/>
       <c r="K144" s="8"/>
       <c r="L144" s="8"/>
@@ -6992,8 +6998,8 @@
       <c r="Q144" s="8"/>
       <c r="R144" s="8"/>
       <c r="S144" s="8"/>
-      <c r="T144" s="33"/>
-      <c r="U144" s="33"/>
+      <c r="T144" s="32"/>
+      <c r="U144" s="32"/>
       <c r="V144" s="8"/>
       <c r="W144" s="8"/>
     </row>
@@ -7003,10 +7009,10 @@
       <c r="C145" s="16"/>
       <c r="D145" s="23"/>
       <c r="E145" s="17"/>
-      <c r="F145" s="43"/>
+      <c r="F145" s="73"/>
       <c r="G145" s="23"/>
-      <c r="H145" s="35"/>
-      <c r="I145" s="31"/>
+      <c r="H145" s="34"/>
+      <c r="I145" s="30"/>
       <c r="J145" s="8"/>
       <c r="K145" s="8"/>
       <c r="L145" s="8"/>
@@ -7017,8 +7023,8 @@
       <c r="Q145" s="8"/>
       <c r="R145" s="8"/>
       <c r="S145" s="8"/>
-      <c r="T145" s="33"/>
-      <c r="U145" s="33"/>
+      <c r="T145" s="32"/>
+      <c r="U145" s="32"/>
       <c r="V145" s="8"/>
       <c r="W145" s="8"/>
     </row>
@@ -7028,10 +7034,10 @@
       <c r="C146" s="16"/>
       <c r="D146" s="23"/>
       <c r="E146" s="17"/>
-      <c r="F146" s="43"/>
+      <c r="F146" s="73"/>
       <c r="G146" s="23"/>
-      <c r="H146" s="35"/>
-      <c r="I146" s="31"/>
+      <c r="H146" s="34"/>
+      <c r="I146" s="30"/>
       <c r="J146" s="8"/>
       <c r="K146" s="8"/>
       <c r="L146" s="8"/>
@@ -7042,8 +7048,8 @@
       <c r="Q146" s="8"/>
       <c r="R146" s="8"/>
       <c r="S146" s="8"/>
-      <c r="T146" s="33"/>
-      <c r="U146" s="33"/>
+      <c r="T146" s="32"/>
+      <c r="U146" s="32"/>
       <c r="V146" s="8"/>
       <c r="W146" s="8"/>
     </row>
@@ -7053,10 +7059,10 @@
       <c r="C147" s="16"/>
       <c r="D147" s="23"/>
       <c r="E147" s="17"/>
-      <c r="F147" s="43"/>
+      <c r="F147" s="73"/>
       <c r="G147" s="23"/>
-      <c r="H147" s="35"/>
-      <c r="I147" s="31"/>
+      <c r="H147" s="34"/>
+      <c r="I147" s="30"/>
       <c r="J147" s="8"/>
       <c r="K147" s="8"/>
       <c r="L147" s="8"/>
@@ -7067,8 +7073,8 @@
       <c r="Q147" s="8"/>
       <c r="R147" s="8"/>
       <c r="S147" s="8"/>
-      <c r="T147" s="33"/>
-      <c r="U147" s="33"/>
+      <c r="T147" s="32"/>
+      <c r="U147" s="32"/>
       <c r="V147" s="8"/>
       <c r="W147" s="8"/>
     </row>
@@ -7078,10 +7084,10 @@
       <c r="C148" s="16"/>
       <c r="D148" s="23"/>
       <c r="E148" s="17"/>
-      <c r="F148" s="43"/>
+      <c r="F148" s="73"/>
       <c r="G148" s="23"/>
-      <c r="H148" s="35"/>
-      <c r="I148" s="31"/>
+      <c r="H148" s="34"/>
+      <c r="I148" s="30"/>
       <c r="J148" s="8"/>
       <c r="K148" s="8"/>
       <c r="L148" s="8"/>
@@ -7092,8 +7098,8 @@
       <c r="Q148" s="8"/>
       <c r="R148" s="8"/>
       <c r="S148" s="8"/>
-      <c r="T148" s="33"/>
-      <c r="U148" s="33"/>
+      <c r="T148" s="32"/>
+      <c r="U148" s="32"/>
       <c r="V148" s="8"/>
       <c r="W148" s="8"/>
     </row>
@@ -7103,10 +7109,10 @@
       <c r="C149" s="16"/>
       <c r="D149" s="23"/>
       <c r="E149" s="17"/>
-      <c r="F149" s="43"/>
+      <c r="F149" s="73"/>
       <c r="G149" s="23"/>
-      <c r="H149" s="35"/>
-      <c r="I149" s="31"/>
+      <c r="H149" s="34"/>
+      <c r="I149" s="30"/>
       <c r="J149" s="8"/>
       <c r="K149" s="8"/>
       <c r="L149" s="8"/>
@@ -7117,8 +7123,8 @@
       <c r="Q149" s="8"/>
       <c r="R149" s="8"/>
       <c r="S149" s="8"/>
-      <c r="T149" s="33"/>
-      <c r="U149" s="33"/>
+      <c r="T149" s="32"/>
+      <c r="U149" s="32"/>
       <c r="V149" s="8"/>
       <c r="W149" s="8"/>
     </row>
@@ -7128,10 +7134,10 @@
       <c r="C150" s="16"/>
       <c r="D150" s="23"/>
       <c r="E150" s="17"/>
-      <c r="F150" s="43"/>
+      <c r="F150" s="73"/>
       <c r="G150" s="23"/>
-      <c r="H150" s="35"/>
-      <c r="I150" s="31"/>
+      <c r="H150" s="34"/>
+      <c r="I150" s="30"/>
       <c r="J150" s="8"/>
       <c r="K150" s="8"/>
       <c r="L150" s="8"/>
@@ -7142,8 +7148,8 @@
       <c r="Q150" s="8"/>
       <c r="R150" s="8"/>
       <c r="S150" s="8"/>
-      <c r="T150" s="33"/>
-      <c r="U150" s="33"/>
+      <c r="T150" s="32"/>
+      <c r="U150" s="32"/>
       <c r="V150" s="8"/>
       <c r="W150" s="8"/>
     </row>
@@ -7153,10 +7159,10 @@
       <c r="C151" s="16"/>
       <c r="D151" s="23"/>
       <c r="E151" s="17"/>
-      <c r="F151" s="43"/>
+      <c r="F151" s="73"/>
       <c r="G151" s="23"/>
-      <c r="H151" s="35"/>
-      <c r="I151" s="31"/>
+      <c r="H151" s="34"/>
+      <c r="I151" s="30"/>
       <c r="J151" s="8"/>
       <c r="K151" s="8"/>
       <c r="L151" s="8"/>
@@ -7167,8 +7173,8 @@
       <c r="Q151" s="8"/>
       <c r="R151" s="8"/>
       <c r="S151" s="8"/>
-      <c r="T151" s="33"/>
-      <c r="U151" s="33"/>
+      <c r="T151" s="32"/>
+      <c r="U151" s="32"/>
       <c r="V151" s="8"/>
       <c r="W151" s="8"/>
     </row>
@@ -7178,10 +7184,10 @@
       <c r="C152" s="16"/>
       <c r="D152" s="23"/>
       <c r="E152" s="17"/>
-      <c r="F152" s="43"/>
+      <c r="F152" s="73"/>
       <c r="G152" s="23"/>
-      <c r="H152" s="35"/>
-      <c r="I152" s="31"/>
+      <c r="H152" s="34"/>
+      <c r="I152" s="30"/>
       <c r="J152" s="8"/>
       <c r="K152" s="8"/>
       <c r="L152" s="8"/>
@@ -7192,8 +7198,8 @@
       <c r="Q152" s="8"/>
       <c r="R152" s="8"/>
       <c r="S152" s="8"/>
-      <c r="T152" s="33"/>
-      <c r="U152" s="33"/>
+      <c r="T152" s="32"/>
+      <c r="U152" s="32"/>
       <c r="V152" s="8"/>
       <c r="W152" s="8"/>
     </row>
@@ -7203,10 +7209,10 @@
       <c r="C153" s="16"/>
       <c r="D153" s="23"/>
       <c r="E153" s="17"/>
-      <c r="F153" s="43"/>
+      <c r="F153" s="73"/>
       <c r="G153" s="23"/>
-      <c r="H153" s="35"/>
-      <c r="I153" s="31"/>
+      <c r="H153" s="34"/>
+      <c r="I153" s="30"/>
       <c r="J153" s="8"/>
       <c r="K153" s="8"/>
       <c r="L153" s="8"/>
@@ -7217,8 +7223,8 @@
       <c r="Q153" s="8"/>
       <c r="R153" s="8"/>
       <c r="S153" s="8"/>
-      <c r="T153" s="33"/>
-      <c r="U153" s="33"/>
+      <c r="T153" s="32"/>
+      <c r="U153" s="32"/>
       <c r="V153" s="8"/>
       <c r="W153" s="8"/>
     </row>
@@ -7228,10 +7234,10 @@
       <c r="C154" s="16"/>
       <c r="D154" s="23"/>
       <c r="E154" s="17"/>
-      <c r="F154" s="43"/>
+      <c r="F154" s="73"/>
       <c r="G154" s="23"/>
-      <c r="H154" s="35"/>
-      <c r="I154" s="31"/>
+      <c r="H154" s="34"/>
+      <c r="I154" s="30"/>
       <c r="J154" s="8"/>
       <c r="K154" s="8"/>
       <c r="L154" s="8"/>
@@ -7242,8 +7248,8 @@
       <c r="Q154" s="8"/>
       <c r="R154" s="8"/>
       <c r="S154" s="8"/>
-      <c r="T154" s="33"/>
-      <c r="U154" s="33"/>
+      <c r="T154" s="32"/>
+      <c r="U154" s="32"/>
       <c r="V154" s="8"/>
       <c r="W154" s="8"/>
     </row>
@@ -7253,10 +7259,10 @@
       <c r="C155" s="16"/>
       <c r="D155" s="23"/>
       <c r="E155" s="17"/>
-      <c r="F155" s="43"/>
+      <c r="F155" s="73"/>
       <c r="G155" s="23"/>
-      <c r="H155" s="35"/>
-      <c r="I155" s="31"/>
+      <c r="H155" s="34"/>
+      <c r="I155" s="30"/>
       <c r="J155" s="8"/>
       <c r="K155" s="8"/>
       <c r="L155" s="8"/>
@@ -7267,8 +7273,8 @@
       <c r="Q155" s="8"/>
       <c r="R155" s="8"/>
       <c r="S155" s="8"/>
-      <c r="T155" s="33"/>
-      <c r="U155" s="33"/>
+      <c r="T155" s="32"/>
+      <c r="U155" s="32"/>
       <c r="V155" s="8"/>
       <c r="W155" s="8"/>
     </row>
@@ -7278,10 +7284,10 @@
       <c r="C156" s="16"/>
       <c r="D156" s="23"/>
       <c r="E156" s="17"/>
-      <c r="F156" s="43"/>
+      <c r="F156" s="73"/>
       <c r="G156" s="23"/>
-      <c r="H156" s="35"/>
-      <c r="I156" s="31"/>
+      <c r="H156" s="34"/>
+      <c r="I156" s="30"/>
       <c r="J156" s="8"/>
       <c r="K156" s="8"/>
       <c r="L156" s="8"/>
@@ -7292,8 +7298,8 @@
       <c r="Q156" s="8"/>
       <c r="R156" s="8"/>
       <c r="S156" s="8"/>
-      <c r="T156" s="33"/>
-      <c r="U156" s="33"/>
+      <c r="T156" s="32"/>
+      <c r="U156" s="32"/>
       <c r="V156" s="8"/>
       <c r="W156" s="8"/>
     </row>
@@ -7303,10 +7309,10 @@
       <c r="C157" s="16"/>
       <c r="D157" s="23"/>
       <c r="E157" s="17"/>
-      <c r="F157" s="43"/>
+      <c r="F157" s="73"/>
       <c r="G157" s="23"/>
-      <c r="H157" s="35"/>
-      <c r="I157" s="31"/>
+      <c r="H157" s="34"/>
+      <c r="I157" s="30"/>
       <c r="J157" s="8"/>
       <c r="K157" s="8"/>
       <c r="L157" s="8"/>
@@ -7317,8 +7323,8 @@
       <c r="Q157" s="8"/>
       <c r="R157" s="8"/>
       <c r="S157" s="8"/>
-      <c r="T157" s="33"/>
-      <c r="U157" s="33"/>
+      <c r="T157" s="32"/>
+      <c r="U157" s="32"/>
       <c r="V157" s="8"/>
       <c r="W157" s="8"/>
     </row>
@@ -7359,82 +7365,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-    </row>
-    <row r="2" spans="1:23" s="36" customFormat="1" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+    </row>
+    <row r="2" spans="1:23" s="35" customFormat="1" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="G2" s="36" t="s">
+      <c r="G2" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="H2" s="36" t="s">
+      <c r="H2" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="I2" s="36" t="s">
+      <c r="I2" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="36" t="s">
+      <c r="J2" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="L2" s="36" t="s">
+      <c r="L2" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="M2" s="36" t="s">
+      <c r="M2" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="N2" s="36" t="s">
+      <c r="N2" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="O2" s="36" t="s">
+      <c r="O2" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="P2" s="36" t="s">
+      <c r="P2" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="Q2" s="36" t="s">
+      <c r="Q2" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="R2" s="36" t="s">
+      <c r="R2" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="S2" s="36" t="s">
+      <c r="S2" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T2" s="36" t="s">
+      <c r="T2" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="U2" s="36" t="s">
+      <c r="U2" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="V2" s="36" t="s">
+      <c r="V2" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="W2" s="36" t="s">
+      <c r="W2" s="35" t="s">
         <v>118</v>
       </c>
     </row>
@@ -7448,10 +7454,10 @@
       <c r="C3" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="36" t="s">
         <v>43</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -7527,7 +7533,7 @@
   <dimension ref="A2:L39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.85546875" style="47" customWidth="1"/>
+    <col min="1" max="1" width="29.85546875" style="45" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" customWidth="1"/>
     <col min="4" max="5" width="26.7109375" customWidth="1"/>
@@ -7538,507 +7544,507 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="45" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="71"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="52"/>
+      <c r="A3" s="69"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="50"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="61" t="s">
+      <c r="A4" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="47" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="49" t="s">
+      <c r="C4" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="49" t="s">
+      <c r="D4" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="49" t="s">
+      <c r="E4" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="F4" s="49" t="s">
+      <c r="F4" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="G4" s="54"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="55"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="53"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="50" t="s">
+      <c r="C5" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="50" t="s">
+      <c r="D5" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="F5" s="50" t="s">
+      <c r="F5" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="G5" s="50"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="52"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="50"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="G6" s="54"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="55"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="53"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="60" t="s">
+      <c r="A7" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="50" t="s">
+      <c r="D7" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="F7" s="50" t="s">
+      <c r="F7" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="54"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="55"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="53"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="60" t="s">
+      <c r="A8" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="50" t="s">
+      <c r="D8" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="54"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="55"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="53"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="60" t="s">
+      <c r="A9" s="58" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="50" t="s">
+      <c r="D9" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E9" s="50" t="s">
+      <c r="E9" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="F9" s="50" t="s">
+      <c r="F9" s="48" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="54"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="55"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="53"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="60" t="s">
+      <c r="A10" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="50" t="s">
+      <c r="D10" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="50" t="s">
+      <c r="E10" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="G10" s="54"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="55"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="53"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="60" t="s">
+      <c r="A11" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="50" t="s">
+      <c r="D11" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E11" s="50" t="s">
+      <c r="E11" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="F11" s="50" t="s">
+      <c r="F11" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="54"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="55"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="53"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="60" t="s">
+      <c r="A12" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="50" t="s">
+      <c r="C12" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="50" t="s">
+      <c r="D12" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="50" t="s">
+      <c r="E12" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="G12" s="54"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="55"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="53"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="50" t="s">
+      <c r="B13" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="50" t="s">
+      <c r="D13" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E13" s="50" t="s">
+      <c r="E13" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="F13" s="50" t="s">
+      <c r="F13" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="G13" s="54"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="55"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
+      <c r="L13" s="53"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="50" t="s">
+      <c r="B14" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="50" t="s">
+      <c r="C14" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="50" t="s">
+      <c r="D14" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E14" s="50" t="s">
+      <c r="E14" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="F14" s="50" t="s">
+      <c r="F14" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="54"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="55"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="51"/>
+      <c r="L14" s="53"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="50" t="s">
+      <c r="B15" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="50" t="s">
+      <c r="C15" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="50" t="s">
+      <c r="D15" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E15" s="50" t="s">
+      <c r="E15" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="F15" s="50" t="s">
+      <c r="F15" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="G15" s="54"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="53"/>
-      <c r="L15" s="55"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
+      <c r="L15" s="53"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="50" t="s">
+      <c r="C16" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="50" t="s">
+      <c r="D16" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E16" s="50" t="s">
+      <c r="E16" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="F16" s="50" t="s">
+      <c r="F16" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="G16" s="54"/>
-      <c r="H16" s="53"/>
-      <c r="I16" s="53"/>
-      <c r="J16" s="53"/>
-      <c r="K16" s="53"/>
-      <c r="L16" s="55"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="51"/>
+      <c r="L16" s="53"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="60" t="s">
+      <c r="A17" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="50" t="s">
+      <c r="B17" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="50" t="s">
+      <c r="C17" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="50" t="s">
+      <c r="D17" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="50" t="s">
+      <c r="E17" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="F17" s="50" t="s">
+      <c r="F17" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="G17" s="54"/>
-      <c r="H17" s="53"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="53"/>
-      <c r="K17" s="53"/>
-      <c r="L17" s="55"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
+      <c r="L17" s="53"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="60" t="s">
+      <c r="A18" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="50" t="s">
+      <c r="D18" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E18" s="50" t="s">
+      <c r="E18" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="F18" s="50" t="s">
+      <c r="F18" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="G18" s="54"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="53"/>
-      <c r="K18" s="53"/>
-      <c r="L18" s="55"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="53"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="50" t="s">
+      <c r="B19" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="50" t="s">
+      <c r="C19" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="50" t="s">
+      <c r="D19" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E19" s="50" t="s">
+      <c r="E19" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="F19" s="50" t="s">
+      <c r="F19" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="G19" s="54"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="55"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+      <c r="L19" s="53"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="60" t="s">
+      <c r="A20" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="50" t="s">
+      <c r="B20" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="50" t="s">
+      <c r="C20" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="50" t="s">
+      <c r="D20" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E20" s="50" t="s">
+      <c r="E20" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="F20" s="50" t="s">
+      <c r="F20" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="G20" s="54"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="55"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
+      <c r="L20" s="53"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="60" t="s">
+      <c r="A21" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="50" t="s">
+      <c r="B21" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="50" t="s">
+      <c r="C21" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="50" t="s">
+      <c r="D21" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E21" s="50" t="s">
+      <c r="E21" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="F21" s="50" t="s">
+      <c r="F21" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="G21" s="54"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="55"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="53"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="62" t="s">
+      <c r="A22" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="B22" s="63"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="58"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="55"/>
+      <c r="K22" s="55"/>
+      <c r="L22" s="56"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23"/>
@@ -8104,7 +8110,7 @@
   <cols>
     <col min="1" max="2" width="23.140625" customWidth="1"/>
     <col min="3" max="3" width="28.85546875" customWidth="1"/>
-    <col min="4" max="5" width="23.140625" style="45" customWidth="1"/>
+    <col min="4" max="5" width="23.140625" style="43" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="21.42578125" customWidth="1"/>
     <col min="8" max="8" width="25.42578125" customWidth="1"/>
@@ -8113,25 +8119,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="35" t="s">
         <v>91</v>
       </c>
     </row>
@@ -8145,13 +8151,13 @@
       <c r="C2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="35" t="s">
         <v>74</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -8171,13 +8177,13 @@
       <c r="C3" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="46" t="s">
+      <c r="D3" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E3" s="46" t="s">
+      <c r="E3" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F3" s="36" t="s">
+      <c r="F3" s="35" t="s">
         <v>75</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -8197,13 +8203,13 @@
       <c r="C4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="46" t="s">
+      <c r="E4" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>72</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -8223,13 +8229,13 @@
       <c r="C5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="46" t="s">
+      <c r="E5" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="F5" s="35" t="s">
         <v>73</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -8249,13 +8255,13 @@
       <c r="C6" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E6" s="46" t="s">
+      <c r="E6" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="35" t="s">
         <v>88</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -8275,13 +8281,13 @@
       <c r="C7" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E7" s="46" t="s">
+      <c r="E7" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="35" t="s">
         <v>71</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -8301,13 +8307,13 @@
       <c r="C8" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E8" s="46" t="s">
+      <c r="E8" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F8" s="36" t="s">
+      <c r="F8" s="35" t="s">
         <v>60</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -8327,13 +8333,13 @@
       <c r="C9" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="46" t="s">
+      <c r="D9" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E9" s="46" t="s">
+      <c r="E9" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="35" t="s">
         <v>86</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -8353,13 +8359,13 @@
       <c r="C10" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D10" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="46" t="s">
+      <c r="E10" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="F10" s="35" t="s">
         <v>61</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -8379,13 +8385,13 @@
       <c r="C11" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E11" s="46" t="s">
+      <c r="E11" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="35" t="s">
         <v>63</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -8405,13 +8411,13 @@
       <c r="C12" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="46" t="s">
+      <c r="E12" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="35" t="s">
         <v>62</v>
       </c>
       <c r="G12" s="1" t="s">
@@ -8431,13 +8437,13 @@
       <c r="C13" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D13" s="46" t="s">
+      <c r="D13" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E13" s="46" t="s">
+      <c r="E13" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="F13" s="35" t="s">
         <v>64</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -8457,13 +8463,13 @@
       <c r="C14" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E14" s="46" t="s">
+      <c r="E14" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F14" s="36" t="s">
+      <c r="F14" s="35" t="s">
         <v>65</v>
       </c>
       <c r="G14" s="1" t="s">
@@ -8483,13 +8489,13 @@
       <c r="C15" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D15" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E15" s="46" t="s">
+      <c r="E15" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F15" s="36" t="s">
+      <c r="F15" s="35" t="s">
         <v>66</v>
       </c>
       <c r="G15" s="1" t="s">
@@ -8509,13 +8515,13 @@
       <c r="C16" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="46" t="s">
+      <c r="D16" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E16" s="46" t="s">
+      <c r="E16" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F16" s="36" t="s">
+      <c r="F16" s="35" t="s">
         <v>67</v>
       </c>
       <c r="G16" s="1" t="s">
@@ -8535,13 +8541,13 @@
       <c r="C17" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D17" s="46" t="s">
+      <c r="D17" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="46" t="s">
+      <c r="E17" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F17" s="36" t="s">
+      <c r="F17" s="35" t="s">
         <v>68</v>
       </c>
       <c r="G17" s="1" t="s">
@@ -8561,13 +8567,13 @@
       <c r="C18" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="46" t="s">
+      <c r="D18" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E18" s="46" t="s">
+      <c r="E18" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F18" s="36" t="s">
+      <c r="F18" s="35" t="s">
         <v>70</v>
       </c>
       <c r="G18" s="1" t="s">

--- a/owlcms/src/main/resources/templates/registration/SBDE.xlsx
+++ b/owlcms/src/main/resources/templates/registration/SBDE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\registration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523DFECB-C61B-4CC6-89D2-9AEED9DAE477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F831778-0C5A-4E55-A1DD-2EBC0760D14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24390" yWindow="1905" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Athletes" sheetId="1" r:id="rId1"/>
@@ -121,7 +121,7 @@
   </definedNames>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="19" r:id="rId6"/>
+    <pivotCache cacheId="9" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="122">
   <si>
     <t>M/F</t>
   </si>
@@ -639,6 +639,12 @@
   </si>
   <si>
     <t>${g.masters}</t>
+  </si>
+  <si>
+    <t>${t.get("ReserveJury")}</t>
+  </si>
+  <si>
+    <t>${g.reserveJury}</t>
   </si>
 </sst>
 </file>
@@ -1535,14 +1541,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1556,6 +1554,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="36">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -2243,7 +2249,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Jean-François Lamy" refreshedDate="45755.444146296293" createdVersion="8" refreshedVersion="8" recordCount="18" xr:uid="{00000000-000A-0000-FFFF-FFFF09000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Jean-François Lamy" refreshedDate="45810.894106018517" createdVersion="8" refreshedVersion="8" recordCount="18" xr:uid="{00000000-000A-0000-FFFF-FFFF09000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:G598" sheet="Group Data"/>
   </cacheSource>
@@ -2498,7 +2504,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable2" cacheId="19" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" minRefreshableVersion="3" showMemberPropertyTips="0" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable2" cacheId="9" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" minRefreshableVersion="3" showMemberPropertyTips="0" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1">
   <location ref="A3:L22" firstHeaderRow="2" firstDataRow="2" firstDataCol="6"/>
   <pivotFields count="7">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" includeNewItemsInFilter="1" defaultSubtotal="0">
@@ -3383,7 +3389,7 @@
       <c r="E1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="70" t="s">
+      <c r="F1" s="67" t="s">
         <v>32</v>
       </c>
       <c r="G1" s="13"/>
@@ -3410,7 +3416,7 @@
       <c r="E2" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="70" t="s">
+      <c r="F2" s="67" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="13"/>
@@ -3427,7 +3433,7 @@
       <c r="E3" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="70" t="s">
+      <c r="F3" s="67" t="s">
         <v>33</v>
       </c>
       <c r="G3" s="13"/>
@@ -3445,7 +3451,7 @@
       <c r="E4" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="70" t="s">
+      <c r="F4" s="67" t="s">
         <v>34</v>
       </c>
       <c r="G4" s="13"/>
@@ -3457,40 +3463,40 @@
     </row>
     <row r="5" spans="1:23" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:23" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
       <c r="N6" s="64"/>
       <c r="O6" s="64"/>
     </row>
     <row r="7" spans="1:23" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
-      <c r="J7" s="67"/>
-      <c r="K7" s="67"/>
-      <c r="L7" s="67"/>
-      <c r="M7" s="67"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
       <c r="N7" s="64"/>
       <c r="O7" s="64"/>
     </row>
@@ -3500,7 +3506,7 @@
       <c r="C8" s="63"/>
       <c r="D8" s="63"/>
       <c r="E8" s="63"/>
-      <c r="F8" s="71"/>
+      <c r="F8" s="68"/>
       <c r="G8" s="63"/>
       <c r="H8" s="63"/>
       <c r="I8" s="57"/>
@@ -3527,7 +3533,7 @@
       <c r="E9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="72" t="s">
+      <c r="F9" s="69" t="s">
         <v>5</v>
       </c>
       <c r="G9" s="5" t="s">
@@ -3598,7 +3604,7 @@
       <c r="E10" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="73" t="s">
+      <c r="F10" s="70" t="s">
         <v>115</v>
       </c>
       <c r="G10" s="29" t="s">
@@ -3659,7 +3665,7 @@
       <c r="C11" s="16"/>
       <c r="D11" s="23"/>
       <c r="E11" s="17"/>
-      <c r="F11" s="73"/>
+      <c r="F11" s="70"/>
       <c r="G11" s="23"/>
       <c r="H11" s="34"/>
       <c r="I11" s="30"/>
@@ -3684,7 +3690,7 @@
       <c r="C12" s="16"/>
       <c r="D12" s="23"/>
       <c r="E12" s="17"/>
-      <c r="F12" s="73"/>
+      <c r="F12" s="70"/>
       <c r="G12" s="23"/>
       <c r="H12" s="34"/>
       <c r="I12" s="30"/>
@@ -3709,7 +3715,7 @@
       <c r="C13" s="16"/>
       <c r="D13" s="23"/>
       <c r="E13" s="17"/>
-      <c r="F13" s="73"/>
+      <c r="F13" s="70"/>
       <c r="G13" s="23"/>
       <c r="H13" s="34"/>
       <c r="I13" s="30"/>
@@ -3734,7 +3740,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="23"/>
       <c r="E14" s="17"/>
-      <c r="F14" s="73"/>
+      <c r="F14" s="70"/>
       <c r="G14" s="23"/>
       <c r="H14" s="34"/>
       <c r="I14" s="30"/>
@@ -3759,7 +3765,7 @@
       <c r="C15" s="16"/>
       <c r="D15" s="23"/>
       <c r="E15" s="17"/>
-      <c r="F15" s="73"/>
+      <c r="F15" s="70"/>
       <c r="G15" s="23"/>
       <c r="H15" s="34"/>
       <c r="I15" s="30"/>
@@ -3784,7 +3790,7 @@
       <c r="C16" s="16"/>
       <c r="D16" s="23"/>
       <c r="E16" s="17"/>
-      <c r="F16" s="73"/>
+      <c r="F16" s="70"/>
       <c r="G16" s="23"/>
       <c r="H16" s="34"/>
       <c r="I16" s="30"/>
@@ -3809,7 +3815,7 @@
       <c r="C17" s="16"/>
       <c r="D17" s="23"/>
       <c r="E17" s="17"/>
-      <c r="F17" s="73"/>
+      <c r="F17" s="70"/>
       <c r="G17" s="23"/>
       <c r="H17" s="34"/>
       <c r="I17" s="30"/>
@@ -3834,7 +3840,7 @@
       <c r="C18" s="16"/>
       <c r="D18" s="23"/>
       <c r="E18" s="17"/>
-      <c r="F18" s="73"/>
+      <c r="F18" s="70"/>
       <c r="G18" s="23"/>
       <c r="H18" s="34"/>
       <c r="I18" s="30"/>
@@ -3859,7 +3865,7 @@
       <c r="C19" s="16"/>
       <c r="D19" s="23"/>
       <c r="E19" s="17"/>
-      <c r="F19" s="73"/>
+      <c r="F19" s="70"/>
       <c r="G19" s="23"/>
       <c r="H19" s="34"/>
       <c r="I19" s="30"/>
@@ -3884,7 +3890,7 @@
       <c r="C20" s="16"/>
       <c r="D20" s="23"/>
       <c r="E20" s="17"/>
-      <c r="F20" s="73"/>
+      <c r="F20" s="70"/>
       <c r="G20" s="23"/>
       <c r="H20" s="34"/>
       <c r="I20" s="30"/>
@@ -3909,7 +3915,7 @@
       <c r="C21" s="16"/>
       <c r="D21" s="23"/>
       <c r="E21" s="17"/>
-      <c r="F21" s="73"/>
+      <c r="F21" s="70"/>
       <c r="G21" s="23"/>
       <c r="H21" s="34"/>
       <c r="I21" s="30"/>
@@ -3934,7 +3940,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="23"/>
       <c r="E22" s="17"/>
-      <c r="F22" s="73"/>
+      <c r="F22" s="70"/>
       <c r="G22" s="23"/>
       <c r="H22" s="34"/>
       <c r="I22" s="30"/>
@@ -3959,7 +3965,7 @@
       <c r="C23" s="16"/>
       <c r="D23" s="23"/>
       <c r="E23" s="17"/>
-      <c r="F23" s="73"/>
+      <c r="F23" s="70"/>
       <c r="G23" s="23"/>
       <c r="H23" s="34"/>
       <c r="I23" s="30"/>
@@ -3984,7 +3990,7 @@
       <c r="C24" s="16"/>
       <c r="D24" s="23"/>
       <c r="E24" s="17"/>
-      <c r="F24" s="73"/>
+      <c r="F24" s="70"/>
       <c r="G24" s="23"/>
       <c r="H24" s="34"/>
       <c r="I24" s="30"/>
@@ -4009,7 +4015,7 @@
       <c r="C25" s="16"/>
       <c r="D25" s="23"/>
       <c r="E25" s="17"/>
-      <c r="F25" s="73"/>
+      <c r="F25" s="70"/>
       <c r="G25" s="23"/>
       <c r="H25" s="34"/>
       <c r="I25" s="30"/>
@@ -4034,7 +4040,7 @@
       <c r="C26" s="16"/>
       <c r="D26" s="23"/>
       <c r="E26" s="17"/>
-      <c r="F26" s="73"/>
+      <c r="F26" s="70"/>
       <c r="G26" s="23"/>
       <c r="H26" s="34"/>
       <c r="I26" s="30"/>
@@ -4059,7 +4065,7 @@
       <c r="C27" s="16"/>
       <c r="D27" s="23"/>
       <c r="E27" s="17"/>
-      <c r="F27" s="73"/>
+      <c r="F27" s="70"/>
       <c r="G27" s="23"/>
       <c r="H27" s="34"/>
       <c r="I27" s="30"/>
@@ -4084,7 +4090,7 @@
       <c r="C28" s="16"/>
       <c r="D28" s="23"/>
       <c r="E28" s="17"/>
-      <c r="F28" s="73"/>
+      <c r="F28" s="70"/>
       <c r="G28" s="23"/>
       <c r="H28" s="34"/>
       <c r="I28" s="30"/>
@@ -4109,7 +4115,7 @@
       <c r="C29" s="16"/>
       <c r="D29" s="23"/>
       <c r="E29" s="17"/>
-      <c r="F29" s="73"/>
+      <c r="F29" s="70"/>
       <c r="G29" s="23"/>
       <c r="H29" s="34"/>
       <c r="I29" s="30"/>
@@ -4134,7 +4140,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="23"/>
       <c r="E30" s="17"/>
-      <c r="F30" s="73"/>
+      <c r="F30" s="70"/>
       <c r="G30" s="23"/>
       <c r="H30" s="34"/>
       <c r="I30" s="30"/>
@@ -4159,7 +4165,7 @@
       <c r="C31" s="16"/>
       <c r="D31" s="23"/>
       <c r="E31" s="17"/>
-      <c r="F31" s="73"/>
+      <c r="F31" s="70"/>
       <c r="G31" s="23"/>
       <c r="H31" s="34"/>
       <c r="I31" s="30"/>
@@ -4184,7 +4190,7 @@
       <c r="C32" s="16"/>
       <c r="D32" s="23"/>
       <c r="E32" s="17"/>
-      <c r="F32" s="73"/>
+      <c r="F32" s="70"/>
       <c r="G32" s="23"/>
       <c r="H32" s="34"/>
       <c r="I32" s="30"/>
@@ -4209,7 +4215,7 @@
       <c r="C33" s="16"/>
       <c r="D33" s="23"/>
       <c r="E33" s="17"/>
-      <c r="F33" s="73"/>
+      <c r="F33" s="70"/>
       <c r="G33" s="23"/>
       <c r="H33" s="34"/>
       <c r="I33" s="30"/>
@@ -4234,7 +4240,7 @@
       <c r="C34" s="16"/>
       <c r="D34" s="23"/>
       <c r="E34" s="17"/>
-      <c r="F34" s="73"/>
+      <c r="F34" s="70"/>
       <c r="G34" s="23"/>
       <c r="H34" s="34"/>
       <c r="I34" s="30"/>
@@ -4259,7 +4265,7 @@
       <c r="C35" s="16"/>
       <c r="D35" s="23"/>
       <c r="E35" s="17"/>
-      <c r="F35" s="73"/>
+      <c r="F35" s="70"/>
       <c r="G35" s="23"/>
       <c r="H35" s="34"/>
       <c r="I35" s="30"/>
@@ -4284,7 +4290,7 @@
       <c r="C36" s="16"/>
       <c r="D36" s="23"/>
       <c r="E36" s="17"/>
-      <c r="F36" s="73"/>
+      <c r="F36" s="70"/>
       <c r="G36" s="23"/>
       <c r="H36" s="34"/>
       <c r="I36" s="30"/>
@@ -4309,7 +4315,7 @@
       <c r="C37" s="16"/>
       <c r="D37" s="23"/>
       <c r="E37" s="17"/>
-      <c r="F37" s="73"/>
+      <c r="F37" s="70"/>
       <c r="G37" s="23"/>
       <c r="H37" s="34"/>
       <c r="I37" s="30"/>
@@ -4334,7 +4340,7 @@
       <c r="C38" s="16"/>
       <c r="D38" s="23"/>
       <c r="E38" s="17"/>
-      <c r="F38" s="73"/>
+      <c r="F38" s="70"/>
       <c r="G38" s="23"/>
       <c r="H38" s="34"/>
       <c r="I38" s="30"/>
@@ -4359,7 +4365,7 @@
       <c r="C39" s="16"/>
       <c r="D39" s="23"/>
       <c r="E39" s="17"/>
-      <c r="F39" s="73"/>
+      <c r="F39" s="70"/>
       <c r="G39" s="23"/>
       <c r="H39" s="34"/>
       <c r="I39" s="30"/>
@@ -4384,7 +4390,7 @@
       <c r="C40" s="16"/>
       <c r="D40" s="23"/>
       <c r="E40" s="17"/>
-      <c r="F40" s="73"/>
+      <c r="F40" s="70"/>
       <c r="G40" s="23"/>
       <c r="H40" s="34"/>
       <c r="I40" s="30"/>
@@ -4409,7 +4415,7 @@
       <c r="C41" s="16"/>
       <c r="D41" s="23"/>
       <c r="E41" s="17"/>
-      <c r="F41" s="73"/>
+      <c r="F41" s="70"/>
       <c r="G41" s="23"/>
       <c r="H41" s="34"/>
       <c r="I41" s="30"/>
@@ -4434,7 +4440,7 @@
       <c r="C42" s="16"/>
       <c r="D42" s="23"/>
       <c r="E42" s="17"/>
-      <c r="F42" s="73"/>
+      <c r="F42" s="70"/>
       <c r="G42" s="23"/>
       <c r="H42" s="34"/>
       <c r="I42" s="30"/>
@@ -4459,7 +4465,7 @@
       <c r="C43" s="16"/>
       <c r="D43" s="23"/>
       <c r="E43" s="17"/>
-      <c r="F43" s="73"/>
+      <c r="F43" s="70"/>
       <c r="G43" s="23"/>
       <c r="H43" s="34"/>
       <c r="I43" s="30"/>
@@ -4484,7 +4490,7 @@
       <c r="C44" s="16"/>
       <c r="D44" s="23"/>
       <c r="E44" s="17"/>
-      <c r="F44" s="73"/>
+      <c r="F44" s="70"/>
       <c r="G44" s="23"/>
       <c r="H44" s="34"/>
       <c r="I44" s="30"/>
@@ -4509,7 +4515,7 @@
       <c r="C45" s="16"/>
       <c r="D45" s="23"/>
       <c r="E45" s="17"/>
-      <c r="F45" s="73"/>
+      <c r="F45" s="70"/>
       <c r="G45" s="23"/>
       <c r="H45" s="34"/>
       <c r="I45" s="30"/>
@@ -4534,7 +4540,7 @@
       <c r="C46" s="16"/>
       <c r="D46" s="23"/>
       <c r="E46" s="17"/>
-      <c r="F46" s="73"/>
+      <c r="F46" s="70"/>
       <c r="G46" s="23"/>
       <c r="H46" s="34"/>
       <c r="I46" s="30"/>
@@ -4559,7 +4565,7 @@
       <c r="C47" s="16"/>
       <c r="D47" s="23"/>
       <c r="E47" s="17"/>
-      <c r="F47" s="73"/>
+      <c r="F47" s="70"/>
       <c r="G47" s="23"/>
       <c r="H47" s="34"/>
       <c r="I47" s="30"/>
@@ -4584,7 +4590,7 @@
       <c r="C48" s="16"/>
       <c r="D48" s="23"/>
       <c r="E48" s="17"/>
-      <c r="F48" s="73"/>
+      <c r="F48" s="70"/>
       <c r="G48" s="23"/>
       <c r="H48" s="34"/>
       <c r="I48" s="30"/>
@@ -4609,7 +4615,7 @@
       <c r="C49" s="16"/>
       <c r="D49" s="23"/>
       <c r="E49" s="17"/>
-      <c r="F49" s="73"/>
+      <c r="F49" s="70"/>
       <c r="G49" s="23"/>
       <c r="H49" s="34"/>
       <c r="I49" s="30"/>
@@ -4634,7 +4640,7 @@
       <c r="C50" s="16"/>
       <c r="D50" s="23"/>
       <c r="E50" s="17"/>
-      <c r="F50" s="73"/>
+      <c r="F50" s="70"/>
       <c r="G50" s="23"/>
       <c r="H50" s="34"/>
       <c r="I50" s="30"/>
@@ -4659,7 +4665,7 @@
       <c r="C51" s="16"/>
       <c r="D51" s="23"/>
       <c r="E51" s="17"/>
-      <c r="F51" s="73"/>
+      <c r="F51" s="70"/>
       <c r="G51" s="23"/>
       <c r="H51" s="34"/>
       <c r="I51" s="30"/>
@@ -4684,7 +4690,7 @@
       <c r="C52" s="16"/>
       <c r="D52" s="23"/>
       <c r="E52" s="17"/>
-      <c r="F52" s="73"/>
+      <c r="F52" s="70"/>
       <c r="G52" s="23"/>
       <c r="H52" s="34"/>
       <c r="I52" s="30"/>
@@ -4709,7 +4715,7 @@
       <c r="C53" s="16"/>
       <c r="D53" s="23"/>
       <c r="E53" s="17"/>
-      <c r="F53" s="73"/>
+      <c r="F53" s="70"/>
       <c r="G53" s="23"/>
       <c r="H53" s="34"/>
       <c r="I53" s="30"/>
@@ -4734,7 +4740,7 @@
       <c r="C54" s="16"/>
       <c r="D54" s="23"/>
       <c r="E54" s="17"/>
-      <c r="F54" s="73"/>
+      <c r="F54" s="70"/>
       <c r="G54" s="23"/>
       <c r="H54" s="34"/>
       <c r="I54" s="30"/>
@@ -4759,7 +4765,7 @@
       <c r="C55" s="16"/>
       <c r="D55" s="23"/>
       <c r="E55" s="17"/>
-      <c r="F55" s="73"/>
+      <c r="F55" s="70"/>
       <c r="G55" s="23"/>
       <c r="H55" s="34"/>
       <c r="I55" s="30"/>
@@ -4784,7 +4790,7 @@
       <c r="C56" s="16"/>
       <c r="D56" s="23"/>
       <c r="E56" s="17"/>
-      <c r="F56" s="73"/>
+      <c r="F56" s="70"/>
       <c r="G56" s="23"/>
       <c r="H56" s="34"/>
       <c r="I56" s="30"/>
@@ -4809,7 +4815,7 @@
       <c r="C57" s="16"/>
       <c r="D57" s="23"/>
       <c r="E57" s="17"/>
-      <c r="F57" s="73"/>
+      <c r="F57" s="70"/>
       <c r="G57" s="23"/>
       <c r="H57" s="34"/>
       <c r="I57" s="30"/>
@@ -4834,7 +4840,7 @@
       <c r="C58" s="16"/>
       <c r="D58" s="23"/>
       <c r="E58" s="17"/>
-      <c r="F58" s="73"/>
+      <c r="F58" s="70"/>
       <c r="G58" s="23"/>
       <c r="H58" s="34"/>
       <c r="I58" s="30"/>
@@ -4859,7 +4865,7 @@
       <c r="C59" s="16"/>
       <c r="D59" s="23"/>
       <c r="E59" s="17"/>
-      <c r="F59" s="73"/>
+      <c r="F59" s="70"/>
       <c r="G59" s="23"/>
       <c r="H59" s="34"/>
       <c r="I59" s="30"/>
@@ -4884,7 +4890,7 @@
       <c r="C60" s="16"/>
       <c r="D60" s="23"/>
       <c r="E60" s="17"/>
-      <c r="F60" s="73"/>
+      <c r="F60" s="70"/>
       <c r="G60" s="23"/>
       <c r="H60" s="34"/>
       <c r="I60" s="30"/>
@@ -4909,7 +4915,7 @@
       <c r="C61" s="16"/>
       <c r="D61" s="23"/>
       <c r="E61" s="17"/>
-      <c r="F61" s="73"/>
+      <c r="F61" s="70"/>
       <c r="G61" s="23"/>
       <c r="H61" s="34"/>
       <c r="I61" s="30"/>
@@ -4934,7 +4940,7 @@
       <c r="C62" s="16"/>
       <c r="D62" s="23"/>
       <c r="E62" s="17"/>
-      <c r="F62" s="73"/>
+      <c r="F62" s="70"/>
       <c r="G62" s="23"/>
       <c r="H62" s="34"/>
       <c r="I62" s="30"/>
@@ -4959,7 +4965,7 @@
       <c r="C63" s="16"/>
       <c r="D63" s="23"/>
       <c r="E63" s="17"/>
-      <c r="F63" s="73"/>
+      <c r="F63" s="70"/>
       <c r="G63" s="23"/>
       <c r="H63" s="34"/>
       <c r="I63" s="30"/>
@@ -4984,7 +4990,7 @@
       <c r="C64" s="16"/>
       <c r="D64" s="23"/>
       <c r="E64" s="17"/>
-      <c r="F64" s="73"/>
+      <c r="F64" s="70"/>
       <c r="G64" s="23"/>
       <c r="H64" s="34"/>
       <c r="I64" s="30"/>
@@ -5009,7 +5015,7 @@
       <c r="C65" s="16"/>
       <c r="D65" s="23"/>
       <c r="E65" s="17"/>
-      <c r="F65" s="73"/>
+      <c r="F65" s="70"/>
       <c r="G65" s="23"/>
       <c r="H65" s="34"/>
       <c r="I65" s="30"/>
@@ -5034,7 +5040,7 @@
       <c r="C66" s="16"/>
       <c r="D66" s="23"/>
       <c r="E66" s="17"/>
-      <c r="F66" s="73"/>
+      <c r="F66" s="70"/>
       <c r="G66" s="23"/>
       <c r="H66" s="34"/>
       <c r="I66" s="30"/>
@@ -5059,7 +5065,7 @@
       <c r="C67" s="16"/>
       <c r="D67" s="23"/>
       <c r="E67" s="17"/>
-      <c r="F67" s="73"/>
+      <c r="F67" s="70"/>
       <c r="G67" s="23"/>
       <c r="H67" s="34"/>
       <c r="I67" s="30"/>
@@ -5084,7 +5090,7 @@
       <c r="C68" s="16"/>
       <c r="D68" s="23"/>
       <c r="E68" s="17"/>
-      <c r="F68" s="73"/>
+      <c r="F68" s="70"/>
       <c r="G68" s="23"/>
       <c r="H68" s="34"/>
       <c r="I68" s="30"/>
@@ -5109,7 +5115,7 @@
       <c r="C69" s="16"/>
       <c r="D69" s="23"/>
       <c r="E69" s="17"/>
-      <c r="F69" s="73"/>
+      <c r="F69" s="70"/>
       <c r="G69" s="23"/>
       <c r="H69" s="34"/>
       <c r="I69" s="30"/>
@@ -5134,7 +5140,7 @@
       <c r="C70" s="16"/>
       <c r="D70" s="23"/>
       <c r="E70" s="17"/>
-      <c r="F70" s="73"/>
+      <c r="F70" s="70"/>
       <c r="G70" s="23"/>
       <c r="H70" s="34"/>
       <c r="I70" s="30"/>
@@ -5159,7 +5165,7 @@
       <c r="C71" s="16"/>
       <c r="D71" s="23"/>
       <c r="E71" s="17"/>
-      <c r="F71" s="73"/>
+      <c r="F71" s="70"/>
       <c r="G71" s="23"/>
       <c r="H71" s="34"/>
       <c r="I71" s="30"/>
@@ -5184,7 +5190,7 @@
       <c r="C72" s="16"/>
       <c r="D72" s="23"/>
       <c r="E72" s="17"/>
-      <c r="F72" s="73"/>
+      <c r="F72" s="70"/>
       <c r="G72" s="23"/>
       <c r="H72" s="34"/>
       <c r="I72" s="30"/>
@@ -5209,7 +5215,7 @@
       <c r="C73" s="16"/>
       <c r="D73" s="23"/>
       <c r="E73" s="17"/>
-      <c r="F73" s="73"/>
+      <c r="F73" s="70"/>
       <c r="G73" s="23"/>
       <c r="H73" s="34"/>
       <c r="I73" s="30"/>
@@ -5234,7 +5240,7 @@
       <c r="C74" s="16"/>
       <c r="D74" s="23"/>
       <c r="E74" s="17"/>
-      <c r="F74" s="73"/>
+      <c r="F74" s="70"/>
       <c r="G74" s="23"/>
       <c r="H74" s="34"/>
       <c r="I74" s="30"/>
@@ -5259,7 +5265,7 @@
       <c r="C75" s="16"/>
       <c r="D75" s="23"/>
       <c r="E75" s="17"/>
-      <c r="F75" s="73"/>
+      <c r="F75" s="70"/>
       <c r="G75" s="23"/>
       <c r="H75" s="34"/>
       <c r="I75" s="30"/>
@@ -5284,7 +5290,7 @@
       <c r="C76" s="16"/>
       <c r="D76" s="23"/>
       <c r="E76" s="17"/>
-      <c r="F76" s="73"/>
+      <c r="F76" s="70"/>
       <c r="G76" s="23"/>
       <c r="H76" s="34"/>
       <c r="I76" s="30"/>
@@ -5309,7 +5315,7 @@
       <c r="C77" s="16"/>
       <c r="D77" s="23"/>
       <c r="E77" s="17"/>
-      <c r="F77" s="73"/>
+      <c r="F77" s="70"/>
       <c r="G77" s="23"/>
       <c r="H77" s="34"/>
       <c r="I77" s="30"/>
@@ -5334,7 +5340,7 @@
       <c r="C78" s="16"/>
       <c r="D78" s="23"/>
       <c r="E78" s="17"/>
-      <c r="F78" s="73"/>
+      <c r="F78" s="70"/>
       <c r="G78" s="23"/>
       <c r="H78" s="34"/>
       <c r="I78" s="30"/>
@@ -5359,7 +5365,7 @@
       <c r="C79" s="16"/>
       <c r="D79" s="23"/>
       <c r="E79" s="17"/>
-      <c r="F79" s="73"/>
+      <c r="F79" s="70"/>
       <c r="G79" s="23"/>
       <c r="H79" s="34"/>
       <c r="I79" s="30"/>
@@ -5384,7 +5390,7 @@
       <c r="C80" s="16"/>
       <c r="D80" s="23"/>
       <c r="E80" s="17"/>
-      <c r="F80" s="73"/>
+      <c r="F80" s="70"/>
       <c r="G80" s="23"/>
       <c r="H80" s="34"/>
       <c r="I80" s="30"/>
@@ -5409,7 +5415,7 @@
       <c r="C81" s="16"/>
       <c r="D81" s="23"/>
       <c r="E81" s="17"/>
-      <c r="F81" s="73"/>
+      <c r="F81" s="70"/>
       <c r="G81" s="23"/>
       <c r="H81" s="34"/>
       <c r="I81" s="30"/>
@@ -5434,7 +5440,7 @@
       <c r="C82" s="16"/>
       <c r="D82" s="23"/>
       <c r="E82" s="17"/>
-      <c r="F82" s="73"/>
+      <c r="F82" s="70"/>
       <c r="G82" s="23"/>
       <c r="H82" s="34"/>
       <c r="I82" s="30"/>
@@ -5459,7 +5465,7 @@
       <c r="C83" s="16"/>
       <c r="D83" s="23"/>
       <c r="E83" s="17"/>
-      <c r="F83" s="73"/>
+      <c r="F83" s="70"/>
       <c r="G83" s="23"/>
       <c r="H83" s="34"/>
       <c r="I83" s="30"/>
@@ -5484,7 +5490,7 @@
       <c r="C84" s="16"/>
       <c r="D84" s="23"/>
       <c r="E84" s="17"/>
-      <c r="F84" s="73"/>
+      <c r="F84" s="70"/>
       <c r="G84" s="23"/>
       <c r="H84" s="34"/>
       <c r="I84" s="30"/>
@@ -5509,7 +5515,7 @@
       <c r="C85" s="16"/>
       <c r="D85" s="23"/>
       <c r="E85" s="17"/>
-      <c r="F85" s="73"/>
+      <c r="F85" s="70"/>
       <c r="G85" s="23"/>
       <c r="H85" s="34"/>
       <c r="I85" s="30"/>
@@ -5534,7 +5540,7 @@
       <c r="C86" s="16"/>
       <c r="D86" s="23"/>
       <c r="E86" s="17"/>
-      <c r="F86" s="73"/>
+      <c r="F86" s="70"/>
       <c r="G86" s="23"/>
       <c r="H86" s="34"/>
       <c r="I86" s="30"/>
@@ -5559,7 +5565,7 @@
       <c r="C87" s="16"/>
       <c r="D87" s="23"/>
       <c r="E87" s="17"/>
-      <c r="F87" s="73"/>
+      <c r="F87" s="70"/>
       <c r="G87" s="23"/>
       <c r="H87" s="34"/>
       <c r="I87" s="30"/>
@@ -5584,7 +5590,7 @@
       <c r="C88" s="16"/>
       <c r="D88" s="23"/>
       <c r="E88" s="17"/>
-      <c r="F88" s="73"/>
+      <c r="F88" s="70"/>
       <c r="G88" s="23"/>
       <c r="H88" s="34"/>
       <c r="I88" s="30"/>
@@ -5609,7 +5615,7 @@
       <c r="C89" s="16"/>
       <c r="D89" s="23"/>
       <c r="E89" s="17"/>
-      <c r="F89" s="73"/>
+      <c r="F89" s="70"/>
       <c r="G89" s="23"/>
       <c r="H89" s="34"/>
       <c r="I89" s="30"/>
@@ -5634,7 +5640,7 @@
       <c r="C90" s="16"/>
       <c r="D90" s="23"/>
       <c r="E90" s="17"/>
-      <c r="F90" s="73"/>
+      <c r="F90" s="70"/>
       <c r="G90" s="23"/>
       <c r="H90" s="34"/>
       <c r="I90" s="30"/>
@@ -5659,7 +5665,7 @@
       <c r="C91" s="16"/>
       <c r="D91" s="23"/>
       <c r="E91" s="17"/>
-      <c r="F91" s="73"/>
+      <c r="F91" s="70"/>
       <c r="G91" s="23"/>
       <c r="H91" s="34"/>
       <c r="I91" s="30"/>
@@ -5684,7 +5690,7 @@
       <c r="C92" s="16"/>
       <c r="D92" s="23"/>
       <c r="E92" s="17"/>
-      <c r="F92" s="73"/>
+      <c r="F92" s="70"/>
       <c r="G92" s="23"/>
       <c r="H92" s="34"/>
       <c r="I92" s="30"/>
@@ -5709,7 +5715,7 @@
       <c r="C93" s="16"/>
       <c r="D93" s="23"/>
       <c r="E93" s="17"/>
-      <c r="F93" s="73"/>
+      <c r="F93" s="70"/>
       <c r="G93" s="23"/>
       <c r="H93" s="34"/>
       <c r="I93" s="30"/>
@@ -5734,7 +5740,7 @@
       <c r="C94" s="16"/>
       <c r="D94" s="23"/>
       <c r="E94" s="17"/>
-      <c r="F94" s="73"/>
+      <c r="F94" s="70"/>
       <c r="G94" s="23"/>
       <c r="H94" s="34"/>
       <c r="I94" s="30"/>
@@ -5759,7 +5765,7 @@
       <c r="C95" s="16"/>
       <c r="D95" s="23"/>
       <c r="E95" s="17"/>
-      <c r="F95" s="73"/>
+      <c r="F95" s="70"/>
       <c r="G95" s="23"/>
       <c r="H95" s="34"/>
       <c r="I95" s="30"/>
@@ -5784,7 +5790,7 @@
       <c r="C96" s="16"/>
       <c r="D96" s="23"/>
       <c r="E96" s="17"/>
-      <c r="F96" s="73"/>
+      <c r="F96" s="70"/>
       <c r="G96" s="23"/>
       <c r="H96" s="34"/>
       <c r="I96" s="30"/>
@@ -5809,7 +5815,7 @@
       <c r="C97" s="16"/>
       <c r="D97" s="23"/>
       <c r="E97" s="17"/>
-      <c r="F97" s="73"/>
+      <c r="F97" s="70"/>
       <c r="G97" s="23"/>
       <c r="H97" s="34"/>
       <c r="I97" s="30"/>
@@ -5834,7 +5840,7 @@
       <c r="C98" s="16"/>
       <c r="D98" s="23"/>
       <c r="E98" s="17"/>
-      <c r="F98" s="73"/>
+      <c r="F98" s="70"/>
       <c r="G98" s="23"/>
       <c r="H98" s="34"/>
       <c r="I98" s="30"/>
@@ -5859,7 +5865,7 @@
       <c r="C99" s="16"/>
       <c r="D99" s="23"/>
       <c r="E99" s="17"/>
-      <c r="F99" s="73"/>
+      <c r="F99" s="70"/>
       <c r="G99" s="23"/>
       <c r="H99" s="34"/>
       <c r="I99" s="30"/>
@@ -5884,7 +5890,7 @@
       <c r="C100" s="16"/>
       <c r="D100" s="23"/>
       <c r="E100" s="17"/>
-      <c r="F100" s="73"/>
+      <c r="F100" s="70"/>
       <c r="G100" s="23"/>
       <c r="H100" s="34"/>
       <c r="I100" s="30"/>
@@ -5909,7 +5915,7 @@
       <c r="C101" s="16"/>
       <c r="D101" s="23"/>
       <c r="E101" s="17"/>
-      <c r="F101" s="73"/>
+      <c r="F101" s="70"/>
       <c r="G101" s="23"/>
       <c r="H101" s="34"/>
       <c r="I101" s="30"/>
@@ -5934,7 +5940,7 @@
       <c r="C102" s="16"/>
       <c r="D102" s="23"/>
       <c r="E102" s="17"/>
-      <c r="F102" s="73"/>
+      <c r="F102" s="70"/>
       <c r="G102" s="23"/>
       <c r="H102" s="34"/>
       <c r="I102" s="30"/>
@@ -5959,7 +5965,7 @@
       <c r="C103" s="16"/>
       <c r="D103" s="23"/>
       <c r="E103" s="17"/>
-      <c r="F103" s="73"/>
+      <c r="F103" s="70"/>
       <c r="G103" s="23"/>
       <c r="H103" s="34"/>
       <c r="I103" s="30"/>
@@ -5984,7 +5990,7 @@
       <c r="C104" s="16"/>
       <c r="D104" s="23"/>
       <c r="E104" s="17"/>
-      <c r="F104" s="73"/>
+      <c r="F104" s="70"/>
       <c r="G104" s="23"/>
       <c r="H104" s="34"/>
       <c r="I104" s="30"/>
@@ -6009,7 +6015,7 @@
       <c r="C105" s="16"/>
       <c r="D105" s="23"/>
       <c r="E105" s="17"/>
-      <c r="F105" s="73"/>
+      <c r="F105" s="70"/>
       <c r="G105" s="23"/>
       <c r="H105" s="34"/>
       <c r="I105" s="30"/>
@@ -6034,7 +6040,7 @@
       <c r="C106" s="16"/>
       <c r="D106" s="23"/>
       <c r="E106" s="17"/>
-      <c r="F106" s="73"/>
+      <c r="F106" s="70"/>
       <c r="G106" s="23"/>
       <c r="H106" s="34"/>
       <c r="I106" s="30"/>
@@ -6059,7 +6065,7 @@
       <c r="C107" s="16"/>
       <c r="D107" s="23"/>
       <c r="E107" s="17"/>
-      <c r="F107" s="73"/>
+      <c r="F107" s="70"/>
       <c r="G107" s="23"/>
       <c r="H107" s="34"/>
       <c r="I107" s="30"/>
@@ -6084,7 +6090,7 @@
       <c r="C108" s="16"/>
       <c r="D108" s="23"/>
       <c r="E108" s="17"/>
-      <c r="F108" s="73"/>
+      <c r="F108" s="70"/>
       <c r="G108" s="23"/>
       <c r="H108" s="34"/>
       <c r="I108" s="30"/>
@@ -6109,7 +6115,7 @@
       <c r="C109" s="16"/>
       <c r="D109" s="23"/>
       <c r="E109" s="17"/>
-      <c r="F109" s="73"/>
+      <c r="F109" s="70"/>
       <c r="G109" s="23"/>
       <c r="H109" s="34"/>
       <c r="I109" s="30"/>
@@ -6134,7 +6140,7 @@
       <c r="C110" s="16"/>
       <c r="D110" s="23"/>
       <c r="E110" s="17"/>
-      <c r="F110" s="73"/>
+      <c r="F110" s="70"/>
       <c r="G110" s="23"/>
       <c r="H110" s="34"/>
       <c r="I110" s="30"/>
@@ -6159,7 +6165,7 @@
       <c r="C111" s="16"/>
       <c r="D111" s="23"/>
       <c r="E111" s="17"/>
-      <c r="F111" s="73"/>
+      <c r="F111" s="70"/>
       <c r="G111" s="23"/>
       <c r="H111" s="34"/>
       <c r="I111" s="30"/>
@@ -6184,7 +6190,7 @@
       <c r="C112" s="16"/>
       <c r="D112" s="23"/>
       <c r="E112" s="17"/>
-      <c r="F112" s="73"/>
+      <c r="F112" s="70"/>
       <c r="G112" s="23"/>
       <c r="H112" s="34"/>
       <c r="I112" s="30"/>
@@ -6209,7 +6215,7 @@
       <c r="C113" s="16"/>
       <c r="D113" s="23"/>
       <c r="E113" s="17"/>
-      <c r="F113" s="73"/>
+      <c r="F113" s="70"/>
       <c r="G113" s="23"/>
       <c r="H113" s="34"/>
       <c r="I113" s="30"/>
@@ -6234,7 +6240,7 @@
       <c r="C114" s="16"/>
       <c r="D114" s="23"/>
       <c r="E114" s="17"/>
-      <c r="F114" s="73"/>
+      <c r="F114" s="70"/>
       <c r="G114" s="23"/>
       <c r="H114" s="34"/>
       <c r="I114" s="30"/>
@@ -6259,7 +6265,7 @@
       <c r="C115" s="16"/>
       <c r="D115" s="23"/>
       <c r="E115" s="17"/>
-      <c r="F115" s="73"/>
+      <c r="F115" s="70"/>
       <c r="G115" s="23"/>
       <c r="H115" s="34"/>
       <c r="I115" s="30"/>
@@ -6284,7 +6290,7 @@
       <c r="C116" s="16"/>
       <c r="D116" s="23"/>
       <c r="E116" s="17"/>
-      <c r="F116" s="73"/>
+      <c r="F116" s="70"/>
       <c r="G116" s="23"/>
       <c r="H116" s="34"/>
       <c r="I116" s="30"/>
@@ -6309,7 +6315,7 @@
       <c r="C117" s="16"/>
       <c r="D117" s="23"/>
       <c r="E117" s="17"/>
-      <c r="F117" s="73"/>
+      <c r="F117" s="70"/>
       <c r="G117" s="23"/>
       <c r="H117" s="34"/>
       <c r="I117" s="30"/>
@@ -6334,7 +6340,7 @@
       <c r="C118" s="16"/>
       <c r="D118" s="23"/>
       <c r="E118" s="17"/>
-      <c r="F118" s="73"/>
+      <c r="F118" s="70"/>
       <c r="G118" s="23"/>
       <c r="H118" s="34"/>
       <c r="I118" s="30"/>
@@ -6359,7 +6365,7 @@
       <c r="C119" s="16"/>
       <c r="D119" s="23"/>
       <c r="E119" s="17"/>
-      <c r="F119" s="73"/>
+      <c r="F119" s="70"/>
       <c r="G119" s="23"/>
       <c r="H119" s="34"/>
       <c r="I119" s="30"/>
@@ -6384,7 +6390,7 @@
       <c r="C120" s="16"/>
       <c r="D120" s="23"/>
       <c r="E120" s="17"/>
-      <c r="F120" s="73"/>
+      <c r="F120" s="70"/>
       <c r="G120" s="23"/>
       <c r="H120" s="34"/>
       <c r="I120" s="30"/>
@@ -6409,7 +6415,7 @@
       <c r="C121" s="16"/>
       <c r="D121" s="23"/>
       <c r="E121" s="17"/>
-      <c r="F121" s="73"/>
+      <c r="F121" s="70"/>
       <c r="G121" s="23"/>
       <c r="H121" s="34"/>
       <c r="I121" s="30"/>
@@ -6434,7 +6440,7 @@
       <c r="C122" s="16"/>
       <c r="D122" s="23"/>
       <c r="E122" s="17"/>
-      <c r="F122" s="73"/>
+      <c r="F122" s="70"/>
       <c r="G122" s="23"/>
       <c r="H122" s="34"/>
       <c r="I122" s="30"/>
@@ -6459,7 +6465,7 @@
       <c r="C123" s="16"/>
       <c r="D123" s="23"/>
       <c r="E123" s="17"/>
-      <c r="F123" s="73"/>
+      <c r="F123" s="70"/>
       <c r="G123" s="23"/>
       <c r="H123" s="34"/>
       <c r="I123" s="30"/>
@@ -6484,7 +6490,7 @@
       <c r="C124" s="16"/>
       <c r="D124" s="23"/>
       <c r="E124" s="17"/>
-      <c r="F124" s="73"/>
+      <c r="F124" s="70"/>
       <c r="G124" s="23"/>
       <c r="H124" s="34"/>
       <c r="I124" s="30"/>
@@ -6509,7 +6515,7 @@
       <c r="C125" s="16"/>
       <c r="D125" s="23"/>
       <c r="E125" s="17"/>
-      <c r="F125" s="73"/>
+      <c r="F125" s="70"/>
       <c r="G125" s="23"/>
       <c r="H125" s="34"/>
       <c r="I125" s="30"/>
@@ -6534,7 +6540,7 @@
       <c r="C126" s="16"/>
       <c r="D126" s="23"/>
       <c r="E126" s="17"/>
-      <c r="F126" s="73"/>
+      <c r="F126" s="70"/>
       <c r="G126" s="23"/>
       <c r="H126" s="34"/>
       <c r="I126" s="30"/>
@@ -6559,7 +6565,7 @@
       <c r="C127" s="16"/>
       <c r="D127" s="23"/>
       <c r="E127" s="17"/>
-      <c r="F127" s="73"/>
+      <c r="F127" s="70"/>
       <c r="G127" s="23"/>
       <c r="H127" s="34"/>
       <c r="I127" s="30"/>
@@ -6584,7 +6590,7 @@
       <c r="C128" s="16"/>
       <c r="D128" s="23"/>
       <c r="E128" s="17"/>
-      <c r="F128" s="73"/>
+      <c r="F128" s="70"/>
       <c r="G128" s="23"/>
       <c r="H128" s="34"/>
       <c r="I128" s="30"/>
@@ -6609,7 +6615,7 @@
       <c r="C129" s="16"/>
       <c r="D129" s="23"/>
       <c r="E129" s="17"/>
-      <c r="F129" s="73"/>
+      <c r="F129" s="70"/>
       <c r="G129" s="23"/>
       <c r="H129" s="34"/>
       <c r="I129" s="30"/>
@@ -6634,7 +6640,7 @@
       <c r="C130" s="16"/>
       <c r="D130" s="23"/>
       <c r="E130" s="17"/>
-      <c r="F130" s="73"/>
+      <c r="F130" s="70"/>
       <c r="G130" s="23"/>
       <c r="H130" s="34"/>
       <c r="I130" s="30"/>
@@ -6659,7 +6665,7 @@
       <c r="C131" s="16"/>
       <c r="D131" s="23"/>
       <c r="E131" s="17"/>
-      <c r="F131" s="73"/>
+      <c r="F131" s="70"/>
       <c r="G131" s="23"/>
       <c r="H131" s="34"/>
       <c r="I131" s="30"/>
@@ -6684,7 +6690,7 @@
       <c r="C132" s="16"/>
       <c r="D132" s="23"/>
       <c r="E132" s="17"/>
-      <c r="F132" s="73"/>
+      <c r="F132" s="70"/>
       <c r="G132" s="23"/>
       <c r="H132" s="34"/>
       <c r="I132" s="30"/>
@@ -6709,7 +6715,7 @@
       <c r="C133" s="16"/>
       <c r="D133" s="23"/>
       <c r="E133" s="17"/>
-      <c r="F133" s="73"/>
+      <c r="F133" s="70"/>
       <c r="G133" s="23"/>
       <c r="H133" s="34"/>
       <c r="I133" s="30"/>
@@ -6734,7 +6740,7 @@
       <c r="C134" s="16"/>
       <c r="D134" s="23"/>
       <c r="E134" s="17"/>
-      <c r="F134" s="73"/>
+      <c r="F134" s="70"/>
       <c r="G134" s="23"/>
       <c r="H134" s="34"/>
       <c r="I134" s="30"/>
@@ -6759,7 +6765,7 @@
       <c r="C135" s="16"/>
       <c r="D135" s="23"/>
       <c r="E135" s="17"/>
-      <c r="F135" s="73"/>
+      <c r="F135" s="70"/>
       <c r="G135" s="23"/>
       <c r="H135" s="34"/>
       <c r="I135" s="30"/>
@@ -6784,7 +6790,7 @@
       <c r="C136" s="16"/>
       <c r="D136" s="23"/>
       <c r="E136" s="17"/>
-      <c r="F136" s="73"/>
+      <c r="F136" s="70"/>
       <c r="G136" s="23"/>
       <c r="H136" s="34"/>
       <c r="I136" s="30"/>
@@ -6809,7 +6815,7 @@
       <c r="C137" s="16"/>
       <c r="D137" s="23"/>
       <c r="E137" s="17"/>
-      <c r="F137" s="73"/>
+      <c r="F137" s="70"/>
       <c r="G137" s="23"/>
       <c r="H137" s="34"/>
       <c r="I137" s="30"/>
@@ -6834,7 +6840,7 @@
       <c r="C138" s="16"/>
       <c r="D138" s="23"/>
       <c r="E138" s="17"/>
-      <c r="F138" s="73"/>
+      <c r="F138" s="70"/>
       <c r="G138" s="23"/>
       <c r="H138" s="34"/>
       <c r="I138" s="30"/>
@@ -6859,7 +6865,7 @@
       <c r="C139" s="16"/>
       <c r="D139" s="23"/>
       <c r="E139" s="17"/>
-      <c r="F139" s="73"/>
+      <c r="F139" s="70"/>
       <c r="G139" s="23"/>
       <c r="H139" s="34"/>
       <c r="I139" s="30"/>
@@ -6884,7 +6890,7 @@
       <c r="C140" s="16"/>
       <c r="D140" s="23"/>
       <c r="E140" s="17"/>
-      <c r="F140" s="73"/>
+      <c r="F140" s="70"/>
       <c r="G140" s="23"/>
       <c r="H140" s="34"/>
       <c r="I140" s="30"/>
@@ -6909,7 +6915,7 @@
       <c r="C141" s="16"/>
       <c r="D141" s="23"/>
       <c r="E141" s="17"/>
-      <c r="F141" s="73"/>
+      <c r="F141" s="70"/>
       <c r="G141" s="23"/>
       <c r="H141" s="34"/>
       <c r="I141" s="30"/>
@@ -6934,7 +6940,7 @@
       <c r="C142" s="16"/>
       <c r="D142" s="23"/>
       <c r="E142" s="17"/>
-      <c r="F142" s="73"/>
+      <c r="F142" s="70"/>
       <c r="G142" s="23"/>
       <c r="H142" s="34"/>
       <c r="I142" s="30"/>
@@ -6959,7 +6965,7 @@
       <c r="C143" s="16"/>
       <c r="D143" s="23"/>
       <c r="E143" s="17"/>
-      <c r="F143" s="73"/>
+      <c r="F143" s="70"/>
       <c r="G143" s="23"/>
       <c r="H143" s="34"/>
       <c r="I143" s="30"/>
@@ -6984,7 +6990,7 @@
       <c r="C144" s="16"/>
       <c r="D144" s="23"/>
       <c r="E144" s="17"/>
-      <c r="F144" s="73"/>
+      <c r="F144" s="70"/>
       <c r="G144" s="23"/>
       <c r="H144" s="34"/>
       <c r="I144" s="30"/>
@@ -7009,7 +7015,7 @@
       <c r="C145" s="16"/>
       <c r="D145" s="23"/>
       <c r="E145" s="17"/>
-      <c r="F145" s="73"/>
+      <c r="F145" s="70"/>
       <c r="G145" s="23"/>
       <c r="H145" s="34"/>
       <c r="I145" s="30"/>
@@ -7034,7 +7040,7 @@
       <c r="C146" s="16"/>
       <c r="D146" s="23"/>
       <c r="E146" s="17"/>
-      <c r="F146" s="73"/>
+      <c r="F146" s="70"/>
       <c r="G146" s="23"/>
       <c r="H146" s="34"/>
       <c r="I146" s="30"/>
@@ -7059,7 +7065,7 @@
       <c r="C147" s="16"/>
       <c r="D147" s="23"/>
       <c r="E147" s="17"/>
-      <c r="F147" s="73"/>
+      <c r="F147" s="70"/>
       <c r="G147" s="23"/>
       <c r="H147" s="34"/>
       <c r="I147" s="30"/>
@@ -7084,7 +7090,7 @@
       <c r="C148" s="16"/>
       <c r="D148" s="23"/>
       <c r="E148" s="17"/>
-      <c r="F148" s="73"/>
+      <c r="F148" s="70"/>
       <c r="G148" s="23"/>
       <c r="H148" s="34"/>
       <c r="I148" s="30"/>
@@ -7109,7 +7115,7 @@
       <c r="C149" s="16"/>
       <c r="D149" s="23"/>
       <c r="E149" s="17"/>
-      <c r="F149" s="73"/>
+      <c r="F149" s="70"/>
       <c r="G149" s="23"/>
       <c r="H149" s="34"/>
       <c r="I149" s="30"/>
@@ -7134,7 +7140,7 @@
       <c r="C150" s="16"/>
       <c r="D150" s="23"/>
       <c r="E150" s="17"/>
-      <c r="F150" s="73"/>
+      <c r="F150" s="70"/>
       <c r="G150" s="23"/>
       <c r="H150" s="34"/>
       <c r="I150" s="30"/>
@@ -7159,7 +7165,7 @@
       <c r="C151" s="16"/>
       <c r="D151" s="23"/>
       <c r="E151" s="17"/>
-      <c r="F151" s="73"/>
+      <c r="F151" s="70"/>
       <c r="G151" s="23"/>
       <c r="H151" s="34"/>
       <c r="I151" s="30"/>
@@ -7184,7 +7190,7 @@
       <c r="C152" s="16"/>
       <c r="D152" s="23"/>
       <c r="E152" s="17"/>
-      <c r="F152" s="73"/>
+      <c r="F152" s="70"/>
       <c r="G152" s="23"/>
       <c r="H152" s="34"/>
       <c r="I152" s="30"/>
@@ -7209,7 +7215,7 @@
       <c r="C153" s="16"/>
       <c r="D153" s="23"/>
       <c r="E153" s="17"/>
-      <c r="F153" s="73"/>
+      <c r="F153" s="70"/>
       <c r="G153" s="23"/>
       <c r="H153" s="34"/>
       <c r="I153" s="30"/>
@@ -7234,7 +7240,7 @@
       <c r="C154" s="16"/>
       <c r="D154" s="23"/>
       <c r="E154" s="17"/>
-      <c r="F154" s="73"/>
+      <c r="F154" s="70"/>
       <c r="G154" s="23"/>
       <c r="H154" s="34"/>
       <c r="I154" s="30"/>
@@ -7259,7 +7265,7 @@
       <c r="C155" s="16"/>
       <c r="D155" s="23"/>
       <c r="E155" s="17"/>
-      <c r="F155" s="73"/>
+      <c r="F155" s="70"/>
       <c r="G155" s="23"/>
       <c r="H155" s="34"/>
       <c r="I155" s="30"/>
@@ -7284,7 +7290,7 @@
       <c r="C156" s="16"/>
       <c r="D156" s="23"/>
       <c r="E156" s="17"/>
-      <c r="F156" s="73"/>
+      <c r="F156" s="70"/>
       <c r="G156" s="23"/>
       <c r="H156" s="34"/>
       <c r="I156" s="30"/>
@@ -7309,7 +7315,7 @@
       <c r="C157" s="16"/>
       <c r="D157" s="23"/>
       <c r="E157" s="17"/>
-      <c r="F157" s="73"/>
+      <c r="F157" s="70"/>
       <c r="G157" s="23"/>
       <c r="H157" s="34"/>
       <c r="I157" s="30"/>
@@ -7356,7 +7362,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="25.42578125" customWidth="1"/>
@@ -7364,16 +7370,16 @@
     <col min="6" max="21" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
+    <row r="1" spans="1:24" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-    </row>
-    <row r="2" spans="1:23" s="35" customFormat="1" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+    </row>
+    <row r="2" spans="1:24" s="35" customFormat="1" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
         <v>3</v>
       </c>
@@ -7443,8 +7449,11 @@
       <c r="W2" s="35" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="X2" s="35" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>40</v>
       </c>
@@ -7513,6 +7522,9 @@
       </c>
       <c r="W3" s="1" t="s">
         <v>119</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -7549,7 +7561,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="69"/>
+      <c r="A3" s="73"/>
       <c r="B3" s="46"/>
       <c r="C3" s="46"/>
       <c r="D3" s="46"/>

--- a/owlcms/src/main/resources/templates/registration/SBDE.xlsx
+++ b/owlcms/src/main/resources/templates/registration/SBDE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\registration\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\registration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F831778-0C5A-4E55-A1DD-2EBC0760D14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FED4BBD-90F5-4E12-90CF-BF1BC60D8B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -222,7 +222,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>jx:each(items="groups" var="g" lastCell="W3")</t>
+          <t>jx:each(items="groups" var="g" lastCell="Y3")</t>
         </r>
         <r>
           <rPr>
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="124">
   <si>
     <t>M/F</t>
   </si>
@@ -645,6 +645,12 @@
   </si>
   <si>
     <t>${g.reserveJury}</t>
+  </si>
+  <si>
+    <t>${t.get("Doctor")}</t>
+  </si>
+  <si>
+    <t>${g.doctor}</t>
   </si>
 </sst>
 </file>
@@ -1372,7 +1378,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1562,6 +1568,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="36">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -1601,276 +1611,7 @@
     <cellStyle name="Title" xfId="34" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="35" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="83">
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="49"/>
-          <bgColor indexed="40"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thick">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thick">
-          <color theme="4" tint="0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="42">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2249,7 +1990,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Jean-François Lamy" refreshedDate="45810.894106018517" createdVersion="8" refreshedVersion="8" recordCount="18" xr:uid="{00000000-000A-0000-FFFF-FFFF09000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Jean-François Lamy" refreshedDate="45910.521214583336" createdVersion="8" refreshedVersion="8" recordCount="18" xr:uid="{00000000-000A-0000-FFFF-FFFF09000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:G598" sheet="Group Data"/>
   </cacheSource>
@@ -2732,13 +2473,13 @@
     <i/>
   </colItems>
   <formats count="41">
-    <format dxfId="82">
+    <format dxfId="41">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="81">
+    <format dxfId="40">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="80">
+    <format dxfId="39">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2747,7 +2488,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="79">
+    <format dxfId="38">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2756,7 +2497,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="78">
+    <format dxfId="37">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2765,7 +2506,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="77">
+    <format dxfId="36">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2774,7 +2515,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="76">
+    <format dxfId="35">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2783,7 +2524,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="75">
+    <format dxfId="34">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2792,7 +2533,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="74">
+    <format dxfId="33">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2801,7 +2542,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="73">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2810,7 +2551,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="72">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2819,7 +2560,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="71">
+    <format dxfId="30">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2828,7 +2569,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="70">
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2837,7 +2578,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="69">
+    <format dxfId="28">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2846,7 +2587,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="68">
+    <format dxfId="27">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2855,7 +2596,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="67">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2864,7 +2605,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="66">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2873,7 +2614,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="65">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2882,7 +2623,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="64">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2891,7 +2632,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="63">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2900,7 +2641,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="62">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2909,7 +2650,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="61">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2918,7 +2659,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="60">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2927,7 +2668,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="59">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2936,7 +2677,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="58">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2945,7 +2686,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="57">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2954,7 +2695,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="56">
+    <format dxfId="15">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2963,7 +2704,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="55">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2972,7 +2713,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="54">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2981,7 +2722,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="53">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2990,7 +2731,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="52">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2999,7 +2740,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="51">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -3008,7 +2749,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="50">
+    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -3017,7 +2758,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="49">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -3026,7 +2767,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="48">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -3035,7 +2776,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="47">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -3044,19 +2785,19 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="46">
+    <format dxfId="5">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="45">
+    <format dxfId="4">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" offset="A1" fieldPosition="0"/>
     </format>
-    <format dxfId="44">
+    <format dxfId="3">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" offset="A1" fieldPosition="0"/>
     </format>
-    <format dxfId="43">
+    <format dxfId="2">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" offset="A1" fieldPosition="0"/>
     </format>
-    <format dxfId="42">
+    <format dxfId="1">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -3463,40 +3204,40 @@
     </row>
     <row r="5" spans="1:23" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:23" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="74"/>
       <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="71"/>
-      <c r="M6" s="71"/>
+      <c r="J6" s="74"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="74"/>
       <c r="N6" s="64"/>
       <c r="O6" s="64"/>
     </row>
     <row r="7" spans="1:23" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="71"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
       <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="71"/>
-      <c r="L7" s="71"/>
-      <c r="M7" s="71"/>
+      <c r="J7" s="74"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="74"/>
       <c r="N7" s="64"/>
       <c r="O7" s="64"/>
     </row>
@@ -7342,7 +7083,7 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="C10:G157">
-    <cfRule type="expression" dxfId="41" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7362,7 +7103,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="25.42578125" customWidth="1"/>
@@ -7370,7 +7111,7 @@
     <col min="6" max="21" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="72" t="s">
         <v>19</v>
       </c>
@@ -7379,7 +7120,7 @@
       <c r="D1" s="72"/>
       <c r="E1" s="72"/>
     </row>
-    <row r="2" spans="1:24" s="35" customFormat="1" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" s="35" customFormat="1" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
         <v>3</v>
       </c>
@@ -7452,8 +7193,11 @@
       <c r="X2" s="35" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="3" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Y2" s="35" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>40</v>
       </c>
@@ -7525,6 +7269,9 @@
       </c>
       <c r="X3" s="1" t="s">
         <v>121</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/owlcms/src/main/resources/templates/registration/SBDE.xlsx
+++ b/owlcms/src/main/resources/templates/registration/SBDE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\registration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FED4BBD-90F5-4E12-90CF-BF1BC60D8B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0BF85D-8539-4120-80FF-4DFE8A6A2E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -121,7 +121,7 @@
   </definedNames>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId6"/>
+    <pivotCache cacheId="19" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -208,7 +208,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>jx:area(lastCell="W3")</t>
+          <t>jx:area(lastCell="Y3")</t>
         </r>
       </text>
     </comment>
@@ -1561,6 +1561,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1568,10 +1572,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="36">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -1611,7 +1611,276 @@
     <cellStyle name="Title" xfId="34" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="35" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="42">
+  <dxfs count="83">
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="49"/>
+          <bgColor indexed="40"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thick">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thick">
+          <color theme="4" tint="0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1990,7 +2259,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Jean-François Lamy" refreshedDate="45910.521214583336" createdVersion="8" refreshedVersion="8" recordCount="18" xr:uid="{00000000-000A-0000-FFFF-FFFF09000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Jean-François Lamy" refreshedDate="45910.537868981482" createdVersion="8" refreshedVersion="8" recordCount="18" xr:uid="{00000000-000A-0000-FFFF-FFFF09000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:G598" sheet="Group Data"/>
   </cacheSource>
@@ -2245,7 +2514,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable2" cacheId="9" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" minRefreshableVersion="3" showMemberPropertyTips="0" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable2" cacheId="19" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" minRefreshableVersion="3" showMemberPropertyTips="0" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1">
   <location ref="A3:L22" firstHeaderRow="2" firstDataRow="2" firstDataCol="6"/>
   <pivotFields count="7">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" includeNewItemsInFilter="1" defaultSubtotal="0">
@@ -2473,13 +2742,13 @@
     <i/>
   </colItems>
   <formats count="41">
-    <format dxfId="41">
+    <format dxfId="82">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="81">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="39">
+    <format dxfId="80">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2488,7 +2757,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="38">
+    <format dxfId="79">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2497,7 +2766,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="37">
+    <format dxfId="78">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2506,7 +2775,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="36">
+    <format dxfId="77">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2515,7 +2784,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="35">
+    <format dxfId="76">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2524,7 +2793,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="34">
+    <format dxfId="75">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2533,7 +2802,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="33">
+    <format dxfId="74">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2542,7 +2811,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="32">
+    <format dxfId="73">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2551,7 +2820,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="31">
+    <format dxfId="72">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2560,7 +2829,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="30">
+    <format dxfId="71">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2569,7 +2838,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="29">
+    <format dxfId="70">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2578,7 +2847,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="28">
+    <format dxfId="69">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2587,7 +2856,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="27">
+    <format dxfId="68">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2596,7 +2865,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="26">
+    <format dxfId="67">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2605,7 +2874,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="66">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2614,7 +2883,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="24">
+    <format dxfId="65">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2623,7 +2892,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="23">
+    <format dxfId="64">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2632,7 +2901,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="22">
+    <format dxfId="63">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2641,7 +2910,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="21">
+    <format dxfId="62">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2650,7 +2919,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="20">
+    <format dxfId="61">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2659,7 +2928,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="60">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2668,7 +2937,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="18">
+    <format dxfId="59">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2677,7 +2946,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="58">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2686,7 +2955,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="57">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2695,7 +2964,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2704,7 +2973,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="55">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2713,7 +2982,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="54">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2722,7 +2991,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="53">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2731,7 +3000,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="52">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2740,7 +3009,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="10">
+    <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2749,7 +3018,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="9">
+    <format dxfId="50">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2758,7 +3027,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="8">
+    <format dxfId="49">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2767,7 +3036,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
+    <format dxfId="48">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -2776,7 +3045,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="47">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1" countASubtotal="1">
@@ -2785,19 +3054,19 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="5">
+    <format dxfId="46">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="45">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" offset="A1" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="44">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" offset="A1" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="43">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" offset="A1" fieldPosition="0"/>
     </format>
-    <format dxfId="1">
+    <format dxfId="42">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -3204,40 +3473,40 @@
     </row>
     <row r="5" spans="1:23" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:23" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="74" t="s">
+      <c r="A6" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="74"/>
-      <c r="C6" s="74"/>
-      <c r="D6" s="74"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
-      <c r="L6" s="74"/>
-      <c r="M6" s="74"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
       <c r="N6" s="64"/>
       <c r="O6" s="64"/>
     </row>
     <row r="7" spans="1:23" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="74"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="74"/>
-      <c r="H7" s="74"/>
-      <c r="I7" s="71"/>
-      <c r="J7" s="74"/>
-      <c r="K7" s="74"/>
-      <c r="L7" s="74"/>
-      <c r="M7" s="74"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
       <c r="N7" s="64"/>
       <c r="O7" s="64"/>
     </row>
@@ -7083,7 +7352,7 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="C10:G157">
-    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="1" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7107,18 +7376,19 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="25.42578125" customWidth="1"/>
-    <col min="4" max="5" width="16.42578125" style="14" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" style="14" customWidth="1"/>
     <col min="6" max="21" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
     </row>
     <row r="2" spans="1:25" s="35" customFormat="1" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
@@ -7308,7 +7578,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="73"/>
+      <c r="A3" s="74"/>
       <c r="B3" s="46"/>
       <c r="C3" s="46"/>
       <c r="D3" s="46"/>

--- a/owlcms/src/main/resources/templates/registration/SBDE.xlsx
+++ b/owlcms/src/main/resources/templates/registration/SBDE.xlsx
@@ -208,7 +208,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>jx:area(lastCell="Y3")</t>
+          <t>jx:area(lastCell="AD3")</t>
         </r>
       </text>
     </comment>
@@ -222,7 +222,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>jx:each(items="groups" var="g" lastCell="Y3")</t>
+          <t>jx:each(items="groups" var="g" lastCell="AD3")</t>
         </r>
         <r>
           <rPr>
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="134">
   <si>
     <t>M/F</t>
   </si>
@@ -651,6 +651,36 @@
   </si>
   <si>
     <t>${g.doctor}</t>
+  </si>
+  <si>
+    <t>${t.get("TechnicalController3")}</t>
+  </si>
+  <si>
+    <t>${g.technicalController3}</t>
+  </si>
+  <si>
+    <t>${t.get("AccreditationRole.COMPETITION_DIRECTOR")}</t>
+  </si>
+  <si>
+    <t>${g.competitionDirector}</t>
+  </si>
+  <si>
+    <t>${t.get("TIS1")}</t>
+  </si>
+  <si>
+    <t>${g.tis1}</t>
+  </si>
+  <si>
+    <t>${t.get("TIS2")}</t>
+  </si>
+  <si>
+    <t>${g.tis2}</t>
+  </si>
+  <si>
+    <t>${t.get("CJ_BreakDuration")}</t>
+  </si>
+  <si>
+    <t>${g.cleanJerkBreakDuration}</t>
   </si>
 </sst>
 </file>
@@ -7371,9 +7401,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:AD3"/>
+  <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="25.42578125" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" style="14" customWidth="1"/>
@@ -7381,7 +7411,7 @@
     <col min="6" max="21" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="37.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="73" t="s">
         <v>19</v>
       </c>
@@ -7390,7 +7420,7 @@
       <c r="D1" s="73"/>
       <c r="E1" s="73"/>
     </row>
-    <row r="2" spans="1:25" s="35" customFormat="1" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" s="35" customFormat="1" ht="48.6" customHeight="1" ns3:dyDescent="0.25">
       <c r="A2" s="35" t="s">
         <v>3</v>
       </c>
@@ -7430,44 +7460,59 @@
       <c r="M2" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="N2" s="35" t="s">
+      <c r="N2" t="s" s="35">
+        <v>124</v>
+      </c>
+      <c r="O2" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="O2" s="35" t="s">
+      <c r="P2" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="P2" s="35" t="s">
+      <c r="Q2" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="Q2" s="35" t="s">
+      <c r="R2" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="R2" s="35" t="s">
+      <c r="S2" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="S2" s="35" t="s">
+      <c r="T2" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T2" s="35" t="s">
+      <c r="U2" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="U2" s="35" t="s">
+      <c r="V2" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="V2" s="35" t="s">
+      <c r="W2" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="W2" s="35" t="s">
+      <c r="X2" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="X2" s="35" t="s">
+      <c r="Y2" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="Y2" s="35" t="s">
+      <c r="Z2" s="35" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA2" t="s" s="35">
+        <v>126</v>
+      </c>
+      <c r="AB2" t="s" s="35">
+        <v>128</v>
+      </c>
+      <c r="AC2" t="s" s="35">
+        <v>130</v>
+      </c>
+      <c r="AD2" t="s" s="35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" s="1" customFormat="1" ns3:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>40</v>
       </c>
@@ -7507,41 +7552,56 @@
       <c r="M3" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" t="s" s="1">
+        <v>125</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Z3" s="1" t="s">
         <v>123</v>
+      </c>
+      <c r="AA3" t="s" s="1">
+        <v>127</v>
+      </c>
+      <c r="AB3" t="s" s="1">
+        <v>129</v>
+      </c>
+      <c r="AC3" t="s" s="1">
+        <v>131</v>
+      </c>
+      <c r="AD3" t="s" s="1">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
